--- a/results/tscv/consolidated/Stress_Testing.xlsx
+++ b/results/tscv/consolidated/Stress_Testing.xlsx
@@ -155,13 +155,13 @@
     <t xml:space="preserve">sGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">eGARCH</t>
+  </si>
+  <si>
     <t xml:space="preserve">TGARCH</t>
   </si>
   <si>
     <t xml:space="preserve">gjrGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eGARCH</t>
   </si>
   <si>
     <t xml:space="preserve">mean_NF_GARCH_MSE</t>
@@ -2227,10 +2227,10 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" t="n">
-        <v>0.000175197657546854</v>
+        <v>0.000168236202942932</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0100364372227003</v>
+        <v>0.00973990321370637</v>
       </c>
       <c r="I3"/>
       <c r="J3" t="n">
@@ -2253,10 +2253,10 @@
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="n">
-        <v>0.000169514484429503</v>
+        <v>0.000167640967147996</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00978572226750602</v>
+        <v>0.00971983913639813</v>
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
@@ -2271,22 +2271,22 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.0000383706930329234</v>
+        <v>0.000167087857498274</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0047347955004754</v>
+        <v>0.00976006436724071</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -2300,15 +2300,15 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000415206528034477</v>
+        <v>0.0000386153290708182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00490433755275154</v>
+        <v>0.00482244058878759</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2331,10 +2331,10 @@
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>0.0000387601387890835</v>
+        <v>0.0000378023980609803</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00467995987114307</v>
+        <v>0.00471700070626497</v>
       </c>
       <c r="I7"/>
       <c r="J7" t="n">
@@ -2357,10 +2357,10 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8" t="n">
-        <v>0.0000391972652493603</v>
+        <v>0.0000394834407488532</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00469690666362771</v>
+        <v>0.00478814537211979</v>
       </c>
       <c r="I8"/>
       <c r="J8" t="n">
@@ -2372,25 +2372,25 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000921723123921486</v>
+        <v>0.0000394112321290254</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00377287984188388</v>
+        <v>0.00469353212076176</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -2404,15 +2404,15 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.000092463613996914</v>
+        <v>0.0000922956021869149</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0038749286516636</v>
+        <v>0.00378485086983949</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
@@ -2430,15 +2430,15 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11" t="n">
-        <v>0.0000919938056935769</v>
+        <v>0.0000907506172258539</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00377620142226785</v>
+        <v>0.00367630682558506</v>
       </c>
       <c r="I11"/>
       <c r="J11" t="n">
@@ -2453,18 +2453,18 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.000211267661193807</v>
+        <v>0.0000914684156053927</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00386650206787291</v>
+        <v>0.00368087774282922</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="n">
@@ -2479,18 +2479,18 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13" t="n">
-        <v>0.000212229932357972</v>
+        <v>0.0000913645256547515</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00400096486087243</v>
+        <v>0.00368213840455138</v>
       </c>
       <c r="I13"/>
       <c r="J13" t="n">
@@ -2508,15 +2508,15 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000211157572998677</v>
+        <v>0.000211350394932267</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00388526746891844</v>
+        <v>0.003921862825395</v>
       </c>
       <c r="I14"/>
       <c r="J14" t="n">
@@ -2531,18 +2531,18 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.0000233604183465833</v>
+        <v>0.000210728933767226</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00352832506160715</v>
+        <v>0.00381014909457183</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
@@ -2557,18 +2557,18 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16" t="n">
-        <v>0.0000246694263638505</v>
+        <v>0.000210393678860455</v>
       </c>
       <c r="H16" t="n">
-        <v>0.003689278337073</v>
+        <v>0.00382824735651945</v>
       </c>
       <c r="I16"/>
       <c r="J16" t="n">
@@ -2583,18 +2583,18 @@
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17" t="n">
-        <v>0.0000227721440578893</v>
+        <v>0.000211427416628283</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00353285750178016</v>
+        <v>0.00389796200836763</v>
       </c>
       <c r="I17"/>
       <c r="J17" t="n">
@@ -2609,7 +2609,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
         <v>45</v>
@@ -2617,10 +2617,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000240138901726636</v>
+        <v>0.0000232088540785513</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00364202207562074</v>
+        <v>0.0036058099865878</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2635,7 +2635,7 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -2643,10 +2643,10 @@
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19" t="n">
-        <v>0.0000245324900841164</v>
+        <v>0.0000226511844505215</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00367829421587031</v>
+        <v>0.00348437769626201</v>
       </c>
       <c r="I19"/>
       <c r="J19" t="n">
@@ -2661,7 +2661,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
         <v>47</v>
@@ -2669,10 +2669,10 @@
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20" t="n">
-        <v>0.0000232005996074502</v>
+        <v>0.0000229900222081848</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00356085892177904</v>
+        <v>0.00352809482603687</v>
       </c>
       <c r="I20"/>
       <c r="J20" t="n">
@@ -2687,22 +2687,22 @@
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.000118748462308523</v>
+        <v>0.0000231494220959247</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0099355007062569</v>
+        <v>0.00355056968881877</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="22">
@@ -2713,22 +2713,22 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.000120030626268868</v>
+        <v>0.0000233571602049009</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00995957008905722</v>
+        <v>0.00354930995829314</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="23">
@@ -2739,178 +2739,178 @@
         <v>18</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23" t="n">
-        <v>0.000118060061416755</v>
+        <v>0.0000223940601573486</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00994996218757649</v>
+        <v>0.00346981488964342</v>
       </c>
       <c r="I23"/>
       <c r="J23" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.0002368757378546</v>
+        <v>0.0000224510731310887</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0116577353446716</v>
+        <v>0.00347652432655019</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25" t="n">
-        <v>0.000236780601255557</v>
+        <v>0.0000232720939810087</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0117436403552003</v>
+        <v>0.00357471577159604</v>
       </c>
       <c r="I25"/>
       <c r="J25" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.00023804152653248</v>
+        <v>0.000120540652121086</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0116986907979943</v>
+        <v>0.0100232398421714</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="n">
-        <v>143</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.0000938935394977727</v>
+        <v>0.000106296848924159</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00730871499026225</v>
+        <v>0.00934027628530819</v>
       </c>
       <c r="I27"/>
       <c r="J27" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.897504599709912</v>
+        <v>0.000116967864819721</v>
       </c>
       <c r="H28" t="n">
-        <v>0.133475966553874</v>
+        <v>0.00990176833993203</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29" t="n">
-        <v>0.0000984254749136008</v>
+        <v>0.000118315173643447</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0076022610903451</v>
+        <v>0.00993426682254106</v>
       </c>
       <c r="I29"/>
       <c r="J29" t="n">
-        <v>59</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30">
@@ -2921,22 +2921,22 @@
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.0000944594432361034</v>
+        <v>0.000236804905302296</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00735169603729355</v>
+        <v>0.0116563082193521</v>
       </c>
       <c r="I30"/>
       <c r="J30" t="n">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31">
@@ -2944,25 +2944,25 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.00010515009197202</v>
+        <v>0.000237904404177027</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00464302391062246</v>
+        <v>0.0116763635278883</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32">
@@ -2970,25 +2970,25 @@
         <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32" t="n">
-        <v>0.000104342297000528</v>
+        <v>0.000237017374322692</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00469287159662177</v>
+        <v>0.0116726757098799</v>
       </c>
       <c r="I32"/>
       <c r="J32" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
@@ -2996,25 +2996,25 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33" t="n">
-        <v>0.000104235647546412</v>
+        <v>0.000238000343978433</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00462240002114805</v>
+        <v>0.0116452030309526</v>
       </c>
       <c r="I33"/>
       <c r="J33" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34">
@@ -3022,10 +3022,10 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
         <v>45</v>
@@ -3033,14 +3033,14 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.000223714738420618</v>
+        <v>0.0000999825289280912</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00479781520423939</v>
+        <v>0.00755927944562779</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -3048,10 +3048,10 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
@@ -3059,14 +3059,14 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35" t="n">
-        <v>0.000224312528424597</v>
+        <v>0.0000974047982652119</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00482525558417828</v>
+        <v>0.00741560260665682</v>
       </c>
       <c r="I35"/>
       <c r="J35" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36">
@@ -3074,10 +3074,10 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
         <v>47</v>
@@ -3085,14 +3085,14 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36" t="n">
-        <v>0.00022292721179916</v>
+        <v>0.0000951585798623853</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00476532156430856</v>
+        <v>0.00737769734665302</v>
       </c>
       <c r="I36"/>
       <c r="J36" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
@@ -3100,25 +3100,25 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.0000364322874451837</v>
+        <v>0.0000993925629937166</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00441689274973309</v>
+        <v>0.00751358060098026</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38">
@@ -3129,18 +3129,18 @@
         <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.0000366011961291037</v>
+        <v>0.000104702579344837</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0044590218681012</v>
+        <v>0.00463123764796006</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="n">
@@ -3155,18 +3155,18 @@
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39" t="n">
-        <v>0.0000361159131178423</v>
+        <v>0.00010389585641762</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00439932662434743</v>
+        <v>0.00455391891663834</v>
       </c>
       <c r="I39"/>
       <c r="J39" t="n">
@@ -3181,18 +3181,18 @@
         <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.0000360487422899257</v>
+        <v>0.000103372509090942</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00437546252357947</v>
+        <v>0.00456723159661185</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="n">
@@ -3207,18 +3207,18 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41" t="n">
-        <v>0.0000369613719476833</v>
+        <v>0.000104424051995499</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00453007351232506</v>
+        <v>0.00462734696647701</v>
       </c>
       <c r="I41"/>
       <c r="J41" t="n">
@@ -3233,18 +3233,18 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.0000365784171004833</v>
+        <v>0.000223442459273849</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00444962671292132</v>
+        <v>0.00472879138096696</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="n">
@@ -3259,22 +3259,22 @@
         <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000131992712571129</v>
+        <v>0.000223270431163083</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0101487305607979</v>
+        <v>0.0047173388039747</v>
       </c>
       <c r="I43"/>
       <c r="J43" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="44">
@@ -3285,22 +3285,22 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000120888813878174</v>
+        <v>0.000223024977418473</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00959281992930843</v>
+        <v>0.0047873471827905</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="45">
@@ -3311,22 +3311,22 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45" t="n">
-        <v>0.000130157879688222</v>
+        <v>0.000222930889382302</v>
       </c>
       <c r="H45" t="n">
-        <v>0.010002234611563</v>
+        <v>0.00474581917642731</v>
       </c>
       <c r="I45"/>
       <c r="J45" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="46">
@@ -3337,111 +3337,111 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.00013055002850866</v>
+        <v>0.0000359746919818899</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0101174942722742</v>
+        <v>0.00438240347630471</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.000505646959794117</v>
+        <v>0.000035235966439632</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0162924247494033</v>
+        <v>0.00432894530812585</v>
       </c>
       <c r="I47"/>
       <c r="J47" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48" t="n">
-        <v>0.000513573267866266</v>
+        <v>0.0000356361541387039</v>
       </c>
       <c r="H48" t="n">
-        <v>0.016402319868845</v>
+        <v>0.00436759379794043</v>
       </c>
       <c r="I48"/>
       <c r="J48" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49" t="n">
-        <v>0.000514491181975626</v>
+        <v>0.0000354904021115412</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0164839361212555</v>
+        <v>0.00436297947203369</v>
       </c>
       <c r="I49"/>
       <c r="J49" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
         <v>45</v>
@@ -3449,25 +3449,25 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.000253418419341189</v>
+        <v>0.0000362362044807949</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0120588741682676</v>
+        <v>0.00443177269633432</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
@@ -3475,25 +3475,25 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51" t="n">
-        <v>0.00025967515946057</v>
+        <v>0.0000355853632810226</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0119457736828565</v>
+        <v>0.00435922847561209</v>
       </c>
       <c r="I51"/>
       <c r="J51" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
         <v>47</v>
@@ -3501,36 +3501,36 @@
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52" t="n">
-        <v>0.000247284313089496</v>
+        <v>0.0000356033391908351</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0118803525409422</v>
+        <v>0.00435646065481362</v>
       </c>
       <c r="I52"/>
       <c r="J52" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.000164643549537579</v>
+        <v>0.000035982894150643</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00779329382454499</v>
+        <v>0.00439722824158237</v>
       </c>
       <c r="I53"/>
       <c r="J53" t="n">
@@ -3539,106 +3539,106 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
         <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000162637652199163</v>
+        <v>0.000133937324975609</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00777215942595275</v>
+        <v>0.0102200584145401</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55" t="n">
-        <v>0.000163193998649328</v>
+        <v>0.000121180774813075</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00779026352675311</v>
+        <v>0.00964956235694822</v>
       </c>
       <c r="I55"/>
       <c r="J55" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
         <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000284395099265626</v>
+        <v>0.000129859286215571</v>
       </c>
       <c r="H56" t="n">
-        <v>0.00795834788417435</v>
+        <v>0.0100765075196595</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57" t="n">
-        <v>0.000283642068083742</v>
+        <v>0.000130091906556003</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00798406331771871</v>
+        <v>0.0100991634425751</v>
       </c>
       <c r="I57"/>
       <c r="J57" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="58">
@@ -3646,25 +3646,25 @@
         <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000285928385826636</v>
+        <v>0.000512935534977831</v>
       </c>
       <c r="H58" t="n">
-        <v>0.00795735944260824</v>
+        <v>0.0164555057095175</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
@@ -3672,25 +3672,25 @@
         <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000096809740066673</v>
+        <v>0.000511654546906692</v>
       </c>
       <c r="H59" t="n">
-        <v>0.00762532246888613</v>
+        <v>0.0164046040155046</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60">
@@ -3698,25 +3698,25 @@
         <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000095098338653391</v>
+        <v>0.000519041305054462</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00758968686041287</v>
+        <v>0.0165044597835108</v>
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61">
@@ -3724,25 +3724,25 @@
         <v>30</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.0000944424408628766</v>
+        <v>0.000512448589273347</v>
       </c>
       <c r="H61" t="n">
-        <v>0.00756317149316512</v>
+        <v>0.0163613939816283</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62">
@@ -3750,10 +3750,10 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
         <v>45</v>
@@ -3761,14 +3761,14 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.0000955351346516677</v>
+        <v>0.000248075866297095</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00756197870983014</v>
+        <v>0.0118051946360816</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -3776,10 +3776,10 @@
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D63" t="s">
         <v>46</v>
@@ -3787,14 +3787,14 @@
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.0000955711098457589</v>
+        <v>0.000257183328146995</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00759610544000117</v>
+        <v>0.0120355614314482</v>
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
@@ -3802,10 +3802,10 @@
         <v>30</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
         <v>47</v>
@@ -3813,14 +3813,14 @@
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.0000951361434616421</v>
+        <v>0.000257443841003865</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00752606305855805</v>
+        <v>0.0120066819635446</v>
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -3828,25 +3828,25 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000217915322953736</v>
+        <v>0.000270249309905327</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0123402024647025</v>
+        <v>0.0122733800799607</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
@@ -3857,22 +3857,22 @@
         <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.0002148466387815</v>
+        <v>0.000161957040681193</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0122457057829872</v>
+        <v>0.00772500689816771</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="67">
@@ -3883,226 +3883,226 @@
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67" t="n">
-        <v>0.000218503397070144</v>
+        <v>1663.09973067643</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0123527731901972</v>
+        <v>12.6840802122295</v>
       </c>
       <c r="I67"/>
       <c r="J67" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.00359069664257162</v>
+        <v>0.000163578182170081</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0488688358829847</v>
+        <v>0.00775203402117957</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.00364728337145096</v>
+        <v>0.000164470142479517</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0498203599629567</v>
+        <v>0.00777749603931179</v>
       </c>
       <c r="I69"/>
       <c r="J69" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.00353299040217608</v>
+        <v>0.000285131891584473</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0487475759646339</v>
+        <v>0.0080224320049326</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>0.00345938235435174</v>
+        <v>1564.3795283474</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0452338770238611</v>
+        <v>11.9711109062993</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>3.62524857144282</v>
+        <v>0.000282639004577642</v>
       </c>
       <c r="H72" t="n">
-        <v>1.90082163002137</v>
+        <v>0.00789756356496828</v>
       </c>
       <c r="I72"/>
       <c r="J72" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.00367341817214177</v>
+        <v>0.00028155166371426</v>
       </c>
       <c r="H73" t="n">
-        <v>0.045992973302281</v>
+        <v>0.00796701951373207</v>
       </c>
       <c r="I73"/>
       <c r="J73" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.00347955706251862</v>
+        <v>0.0000958246169292301</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0456856142762144</v>
+        <v>0.00763734644735006</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>0.00129391231079436</v>
+        <v>1466.71053284717</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0257183805592015</v>
+        <v>11.4991303173457</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4111,24 +4111,24 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
         <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.00141390288035645</v>
+        <v>0.0000948734599761424</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0278038048054066</v>
+        <v>0.0075493703811761</v>
       </c>
       <c r="I76"/>
       <c r="J76" t="n">
@@ -4137,24 +4137,24 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.00132408688475188</v>
+        <v>0.0000946296577866486</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0259713163799206</v>
+        <v>0.00752994079255258</v>
       </c>
       <c r="I77"/>
       <c r="J77" t="n">
@@ -4163,24 +4163,24 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
         <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.00127311179937606</v>
+        <v>0.0000955474004635864</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0253790018217059</v>
+        <v>0.00760449763704258</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4189,24 +4189,24 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>0.00143103686987792</v>
+        <v>1588.34526170424</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0257407710654456</v>
+        <v>12.1781456887244</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4215,24 +4215,24 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B80" t="s">
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.00154220152751991</v>
+        <v>0.0000947829313999953</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0277085125269503</v>
+        <v>0.00753189187385555</v>
       </c>
       <c r="I80"/>
       <c r="J80" t="n">
@@ -4241,24 +4241,24 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B81" t="s">
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.00147474175529187</v>
+        <v>0.0000946462708001455</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0264311809271429</v>
+        <v>0.00761112959337621</v>
       </c>
       <c r="I81"/>
       <c r="J81" t="n">
@@ -4267,106 +4267,106 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.0014159154651178</v>
+        <v>0.000216789997276877</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0257075561642772</v>
+        <v>0.012301206468053</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.00121605871868021</v>
+        <v>0.000213509334404182</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0254686948054272</v>
+        <v>0.0121511012997335</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.00137027314439076</v>
+        <v>0.000214053087882048</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0275297529092298</v>
+        <v>0.0122106716400761</v>
       </c>
       <c r="I84"/>
       <c r="J84" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.00122864232078964</v>
+        <v>0.00021738260783654</v>
       </c>
       <c r="H85" t="n">
-        <v>0.025708849425932</v>
+        <v>0.0123246217175259</v>
       </c>
       <c r="I85"/>
       <c r="J85" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="86">
@@ -4374,25 +4374,25 @@
         <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00118861689677564</v>
+        <v>0.00369352599892388</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0251200614426146</v>
+        <v>0.0497580197898968</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87">
@@ -4400,25 +4400,25 @@
         <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00121349167714572</v>
+        <v>0.00354772992768419</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0255936436076384</v>
+        <v>0.0491210230233158</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="88">
@@ -4426,25 +4426,25 @@
         <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00137919372342571</v>
+        <v>0.00355271394535845</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0276173744876084</v>
+        <v>0.0491085012441402</v>
       </c>
       <c r="I88"/>
       <c r="J88" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="89">
@@ -4452,25 +4452,25 @@
         <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00124599452563373</v>
+        <v>0.00353421669524982</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0260040972729383</v>
+        <v>0.0490565975738826</v>
       </c>
       <c r="I89"/>
       <c r="J89" t="n">
-        <v>1356</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90">
@@ -4478,25 +4478,25 @@
         <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00119930626937206</v>
+        <v>0.00355270279557635</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0253113192392128</v>
+        <v>0.0460753129578416</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
-        <v>1356</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
@@ -4504,25 +4504,25 @@
         <v>31</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00108014370426329</v>
+        <v>0.00343804634900417</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0231509039742768</v>
+        <v>0.045094578317627</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
@@ -4530,25 +4530,25 @@
         <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.00107756026377597</v>
+        <v>0.00343959241065118</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0232336872825112</v>
+        <v>0.0453659749178632</v>
       </c>
       <c r="I92"/>
       <c r="J92" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -4556,36 +4556,36 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.00106208570402891</v>
+        <v>0.00350663983150039</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0227873996116075</v>
+        <v>0.0457573133402959</v>
       </c>
       <c r="I93"/>
       <c r="J93" t="n">
-        <v>904</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D94" t="s">
         <v>45</v>
@@ -4593,25 +4593,25 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00167789232178844</v>
+        <v>0.00129035044303019</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0309109639943413</v>
+        <v>0.0256395260221728</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D95" t="s">
         <v>46</v>
@@ -4619,25 +4619,25 @@
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.001660893539918</v>
+        <v>0.00127436514713176</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0306279399299139</v>
+        <v>0.0254600435622212</v>
       </c>
       <c r="I95"/>
       <c r="J95" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D96" t="s">
         <v>47</v>
@@ -4645,114 +4645,114 @@
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00164876101432005</v>
+        <v>0.00128060708435289</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0304937199611671</v>
+        <v>0.0255234208821561</v>
       </c>
       <c r="I96"/>
       <c r="J96" t="n">
-        <v>143</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00222261284279495</v>
+        <v>0.00128192663492686</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0352178418533837</v>
+        <v>0.0255157186909293</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00223614715554743</v>
+        <v>0.00143579095474943</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0349775228414502</v>
+        <v>0.0261568613012915</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.00221583518268389</v>
+        <v>0.00140124320033395</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0349906329749506</v>
+        <v>0.0255765391737544</v>
       </c>
       <c r="I99"/>
       <c r="J99" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
         <v>18</v>
       </c>
       <c r="C100" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.000441927760227341</v>
+        <v>0.00140475795566244</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0139150027527031</v>
+        <v>0.0255241783256353</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -4761,24 +4761,24 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B101" t="s">
         <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.000447509106971129</v>
+        <v>0.00140091531708612</v>
       </c>
       <c r="H101" t="n">
-        <v>0.013996928878383</v>
+        <v>0.025542591428094</v>
       </c>
       <c r="I101"/>
       <c r="J101" t="n">
@@ -4787,24 +4787,24 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B102" t="s">
         <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.000441475467976453</v>
+        <v>0.00120380258915943</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0138792726026101</v>
+        <v>0.025350748529651</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -4813,24 +4813,24 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B103" t="s">
         <v>18</v>
       </c>
       <c r="C103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.000559618022065061</v>
+        <v>0.00118910009996879</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0140835307102651</v>
+        <v>0.0251760878001323</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -4839,24 +4839,24 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B104" t="s">
         <v>18</v>
       </c>
       <c r="C104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00056798127743037</v>
+        <v>0.00119455660986713</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0141228671256927</v>
+        <v>0.0252563211160035</v>
       </c>
       <c r="I104"/>
       <c r="J104" t="n">
@@ -4865,24 +4865,24 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B105" t="s">
         <v>18</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.000557605154897508</v>
+        <v>0.00119823918618116</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0140007229765211</v>
+        <v>0.0253014571575711</v>
       </c>
       <c r="I105"/>
       <c r="J105" t="n">
@@ -4891,13 +4891,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B106" t="s">
         <v>18</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
         <v>45</v>
@@ -4905,10 +4905,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.000373298970546439</v>
+        <v>0.00121763751794577</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0136370345784917</v>
+        <v>0.025625397910974</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -4917,13 +4917,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B107" t="s">
         <v>18</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D107" t="s">
         <v>46</v>
@@ -4931,10 +4931,10 @@
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.000379371963570518</v>
+        <v>0.00119840434109664</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0137709264124833</v>
+        <v>0.0252798115904623</v>
       </c>
       <c r="I107"/>
       <c r="J107" t="n">
@@ -4943,13 +4943,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B108" t="s">
         <v>18</v>
       </c>
       <c r="C108" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
         <v>47</v>
@@ -4957,10 +4957,10 @@
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.000372896358715946</v>
+        <v>0.00119017417691742</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0136578183822364</v>
+        <v>0.0251711302816443</v>
       </c>
       <c r="I108"/>
       <c r="J108" t="n">
@@ -4969,7 +4969,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B109" t="s">
         <v>18</v>
@@ -4978,15 +4978,15 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.000372081781689767</v>
+        <v>0.0012053431965726</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0136621687801431</v>
+        <v>0.0252768974756966</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -4995,59 +4995,59 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B110" t="s">
         <v>18</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.000376558468588636</v>
+        <v>0.00108197780049487</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0137403574011858</v>
+        <v>0.0230963740660201</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.000372629905391833</v>
+        <v>0.00105407380759895</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0136460896926819</v>
+        <v>0.0226763546446701</v>
       </c>
       <c r="I111"/>
       <c r="J111" t="n">
-        <v>1356</v>
+        <v>904</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B112" t="s">
         <v>18</v>
@@ -5056,15 +5056,15 @@
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.000433740733429641</v>
+        <v>0.00106003589548525</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0145855379491701</v>
+        <v>0.0227862202339599</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5073,7 +5073,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
@@ -5087,10 +5087,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.328906399075266</v>
+        <v>0.00105220992570386</v>
       </c>
       <c r="H113" t="n">
-        <v>0.572723421263809</v>
+        <v>0.0227001500533439</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5102,25 +5102,25 @@
         <v>32</v>
       </c>
       <c r="B114" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.000435016166200496</v>
+        <v>0.00165502619576309</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0147070750506672</v>
+        <v>0.0305528222442102</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
-        <v>904</v>
+        <v>143</v>
       </c>
     </row>
     <row r="115">
@@ -5128,30 +5128,30 @@
         <v>32</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.000426477280145614</v>
+        <v>0.00166359505222445</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0144046041233698</v>
+        <v>0.0308437990252989</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
-        <v>904</v>
+        <v>143</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
@@ -5160,15 +5160,15 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00275098786635208</v>
+        <v>0.00166100913752892</v>
       </c>
       <c r="H116" t="n">
-        <v>0.040509051213018</v>
+        <v>0.0306082060158772</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5177,7 +5177,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
@@ -5186,15 +5186,15 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.00278714219219696</v>
+        <v>0.00165684377203145</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0412283091335756</v>
+        <v>0.0304732562987995</v>
       </c>
       <c r="I117"/>
       <c r="J117" t="n">
@@ -5203,33 +5203,33 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.00266774733134832</v>
+        <v>0.00222253296534883</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0400124101619155</v>
+        <v>0.035264455681476</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
@@ -5238,15 +5238,15 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00107503135226478</v>
+        <v>0.00222319933563074</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0246577500975989</v>
+        <v>0.0351416885485996</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5255,7 +5255,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
@@ -5264,15 +5264,15 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>1947308914478094197288422048044464620028408444</v>
+        <v>0.00220320085094273</v>
       </c>
       <c r="H120" t="n">
-        <v>9950663672129378058440</v>
+        <v>0.0348386740287209</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5281,7 +5281,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
@@ -5290,15 +5290,15 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00128672153245856</v>
+        <v>0.00221809193670733</v>
       </c>
       <c r="H121" t="n">
-        <v>0.027350081911536</v>
+        <v>0.0350474210916605</v>
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
@@ -5307,33 +5307,33 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.00111241781546877</v>
+        <v>0.000440119886170392</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0255625258530323</v>
+        <v>0.0139405819358338</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
-        <v>59</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s">
         <v>18</v>
@@ -5342,15 +5342,15 @@
         <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000616863641694971</v>
+        <v>0.000445903984119878</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0170314337420444</v>
+        <v>0.0139926558046294</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5359,7 +5359,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B124" t="s">
         <v>18</v>
@@ -5368,15 +5368,15 @@
         <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000644409746794179</v>
+        <v>0.000442636324440099</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0178063839778164</v>
+        <v>0.0138867340452424</v>
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
@@ -5385,7 +5385,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B125" t="s">
         <v>18</v>
@@ -5394,15 +5394,15 @@
         <v>19</v>
       </c>
       <c r="D125" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000586093874357738</v>
+        <v>0.000439709052166203</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0164863656926363</v>
+        <v>0.013875833694454</v>
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
@@ -5411,7 +5411,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s">
         <v>18</v>
@@ -5425,10 +5425,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000713815480597498</v>
+        <v>0.000560115011666399</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0169784026806706</v>
+        <v>0.0140881155061466</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5437,7 +5437,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B127" t="s">
         <v>18</v>
@@ -5451,10 +5451,10 @@
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000784281588537692</v>
+        <v>0.000559558929536151</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0183460473212515</v>
+        <v>0.0140403875404967</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -5463,7 +5463,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B128" t="s">
         <v>18</v>
@@ -5477,10 +5477,10 @@
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000703183145814685</v>
+        <v>0.000558394037696748</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0166683864810988</v>
+        <v>0.0140000347577634</v>
       </c>
       <c r="I128"/>
       <c r="J128" t="n">
@@ -5489,24 +5489,24 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B129" t="s">
         <v>18</v>
       </c>
       <c r="C129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000532976895204563</v>
+        <v>0.000559021170580466</v>
       </c>
       <c r="H129" t="n">
-        <v>0.01660396937179</v>
+        <v>0.0139640831077842</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -5515,7 +5515,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
         <v>18</v>
@@ -5524,15 +5524,15 @@
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000586172215852165</v>
+        <v>0.000371453106856845</v>
       </c>
       <c r="H130" t="n">
-        <v>0.017626692418154</v>
+        <v>0.0136160226452815</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -5541,7 +5541,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B131" t="s">
         <v>18</v>
@@ -5550,15 +5550,15 @@
         <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000514954593598192</v>
+        <v>0.000373848327756974</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0162287582730835</v>
+        <v>0.013680312990796</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -5567,24 +5567,24 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
         <v>18</v>
       </c>
       <c r="C132" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000538378980874487</v>
+        <v>0.000374836588957323</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0166200285656392</v>
+        <v>0.0136626597154048</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -5593,24 +5593,24 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
         <v>18</v>
       </c>
       <c r="C133" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000587081427712954</v>
+        <v>0.000374532232784796</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0177659091273415</v>
+        <v>0.0136589524247012</v>
       </c>
       <c r="I133"/>
       <c r="J133" t="n">
@@ -5619,7 +5619,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
         <v>18</v>
@@ -5628,15 +5628,15 @@
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.00052455401478502</v>
+        <v>0.000372521783392687</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0163464734411901</v>
+        <v>0.0136799771878366</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -5645,79 +5645,911 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135" t="s">
         <v>18</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000505836171465302</v>
+        <v>0.000374723936197941</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0167700671843686</v>
+        <v>0.0136647583598699</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136" t="s">
         <v>18</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000557030554627641</v>
+        <v>0.000374580873066442</v>
       </c>
       <c r="H136" t="n">
-        <v>0.017443020926262</v>
+        <v>0.0137190504733313</v>
       </c>
       <c r="I136"/>
       <c r="J136" t="n">
-        <v>904</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B137" t="s">
         <v>18</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000501370984699036</v>
+        <v>0.000375107026987081</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0165765979973764</v>
+        <v>0.013687605946763</v>
       </c>
       <c r="I137"/>
       <c r="J137" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>32</v>
+      </c>
+      <c r="B138" t="s">
+        <v>18</v>
+      </c>
+      <c r="C138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138" t="s">
+        <v>45</v>
+      </c>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138" t="n">
+        <v>0.000426436809752057</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.0143845633893955</v>
+      </c>
+      <c r="I138"/>
+      <c r="J138" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>32</v>
+      </c>
+      <c r="B139" t="s">
+        <v>18</v>
+      </c>
+      <c r="C139" t="s">
+        <v>27</v>
+      </c>
+      <c r="D139" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139" t="n">
+        <v>0.000427552535229091</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.0144086472176001</v>
+      </c>
+      <c r="I139"/>
+      <c r="J139" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>32</v>
+      </c>
+      <c r="B140" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140" t="s">
+        <v>27</v>
+      </c>
+      <c r="D140" t="s">
+        <v>47</v>
+      </c>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140" t="n">
+        <v>0.000430007975387303</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.0144203292809099</v>
+      </c>
+      <c r="I140"/>
+      <c r="J140" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>32</v>
+      </c>
+      <c r="B141" t="s">
+        <v>18</v>
+      </c>
+      <c r="C141" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141" t="n">
+        <v>0.000428206548610281</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.0144581726169688</v>
+      </c>
+      <c r="I141"/>
+      <c r="J141" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>33</v>
+      </c>
+      <c r="B142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" t="s">
+        <v>45</v>
+      </c>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142" t="n">
+        <v>0.00267877352127038</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.0401637450653961</v>
+      </c>
+      <c r="I142"/>
+      <c r="J142" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>33</v>
+      </c>
+      <c r="B143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143" t="s">
+        <v>46</v>
+      </c>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143" t="n">
+        <v>0.00265931995726425</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.0398537793948801</v>
+      </c>
+      <c r="I143"/>
+      <c r="J143" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>33</v>
+      </c>
+      <c r="B144" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" t="s">
+        <v>47</v>
+      </c>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144" t="n">
+        <v>0.002659339442807</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.0396123016401896</v>
+      </c>
+      <c r="I144"/>
+      <c r="J144" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>33</v>
+      </c>
+      <c r="B145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" t="s">
+        <v>48</v>
+      </c>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145" t="n">
+        <v>0.00264267762783412</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.0397137216065568</v>
+      </c>
+      <c r="I145"/>
+      <c r="J145" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>33</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146" t="s">
+        <v>45</v>
+      </c>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146" t="n">
+        <v>0.00110424017501015</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.0249465338842973</v>
+      </c>
+      <c r="I146"/>
+      <c r="J146" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>33</v>
+      </c>
+      <c r="B147" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" t="s">
+        <v>16</v>
+      </c>
+      <c r="D147" t="s">
+        <v>46</v>
+      </c>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147" t="n">
+        <v>0.00108590195176701</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.0250318041867535</v>
+      </c>
+      <c r="I147"/>
+      <c r="J147" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>33</v>
+      </c>
+      <c r="B148" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" t="s">
+        <v>16</v>
+      </c>
+      <c r="D148" t="s">
+        <v>47</v>
+      </c>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148" t="n">
+        <v>0.0010877502492548</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.0249108810621583</v>
+      </c>
+      <c r="I148"/>
+      <c r="J148" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>33</v>
+      </c>
+      <c r="B149" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" t="s">
+        <v>16</v>
+      </c>
+      <c r="D149" t="s">
+        <v>48</v>
+      </c>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149" t="n">
+        <v>0.00111955008512846</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.025272163028466</v>
+      </c>
+      <c r="I149"/>
+      <c r="J149" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>33</v>
+      </c>
+      <c r="B150" t="s">
+        <v>18</v>
+      </c>
+      <c r="C150" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" t="s">
+        <v>45</v>
+      </c>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150" t="n">
+        <v>0.000602491605634867</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.0168121152571472</v>
+      </c>
+      <c r="I150"/>
+      <c r="J150" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>33</v>
+      </c>
+      <c r="B151" t="s">
+        <v>18</v>
+      </c>
+      <c r="C151" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151" t="n">
+        <v>0.000585815177060615</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.0164628841768857</v>
+      </c>
+      <c r="I151"/>
+      <c r="J151" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" t="s">
+        <v>18</v>
+      </c>
+      <c r="C152" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" t="s">
+        <v>47</v>
+      </c>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152" t="n">
+        <v>0.000586602158042034</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.0164976815877205</v>
+      </c>
+      <c r="I152"/>
+      <c r="J152" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>33</v>
+      </c>
+      <c r="B153" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" t="s">
+        <v>48</v>
+      </c>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153" t="n">
+        <v>0.00058962233807739</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.0165761279652862</v>
+      </c>
+      <c r="I153"/>
+      <c r="J153" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>33</v>
+      </c>
+      <c r="B154" t="s">
+        <v>18</v>
+      </c>
+      <c r="C154" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" t="s">
+        <v>45</v>
+      </c>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154" t="n">
+        <v>0.000723351660238384</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.0171328568079931</v>
+      </c>
+      <c r="I154"/>
+      <c r="J154" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>33</v>
+      </c>
+      <c r="B155" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155"/>
+      <c r="F155"/>
+      <c r="G155" t="n">
+        <v>0.000701524917890142</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.0165958984521632</v>
+      </c>
+      <c r="I155"/>
+      <c r="J155" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>33</v>
+      </c>
+      <c r="B156" t="s">
+        <v>18</v>
+      </c>
+      <c r="C156" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" t="s">
+        <v>47</v>
+      </c>
+      <c r="E156"/>
+      <c r="F156"/>
+      <c r="G156" t="n">
+        <v>0.000704039205843003</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.0166165324423514</v>
+      </c>
+      <c r="I156"/>
+      <c r="J156" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>33</v>
+      </c>
+      <c r="B157" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157" t="n">
+        <v>0.00070606048086045</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.0166046670898993</v>
+      </c>
+      <c r="I157"/>
+      <c r="J157" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>33</v>
+      </c>
+      <c r="B158" t="s">
+        <v>18</v>
+      </c>
+      <c r="C158" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" t="s">
+        <v>45</v>
+      </c>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158" t="n">
+        <v>0.000533448217989059</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.0166916016629204</v>
+      </c>
+      <c r="I158"/>
+      <c r="J158" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>33</v>
+      </c>
+      <c r="B159" t="s">
+        <v>18</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" t="s">
+        <v>46</v>
+      </c>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159" t="n">
+        <v>0.000516836420673964</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.0162639579890522</v>
+      </c>
+      <c r="I159"/>
+      <c r="J159" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>33</v>
+      </c>
+      <c r="B160" t="s">
+        <v>18</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" t="s">
+        <v>47</v>
+      </c>
+      <c r="E160"/>
+      <c r="F160"/>
+      <c r="G160" t="n">
+        <v>0.000520164256586935</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.0163647933196485</v>
+      </c>
+      <c r="I160"/>
+      <c r="J160" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>33</v>
+      </c>
+      <c r="B161" t="s">
+        <v>18</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" t="s">
+        <v>48</v>
+      </c>
+      <c r="E161"/>
+      <c r="F161"/>
+      <c r="G161" t="n">
+        <v>0.000521548730298579</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.0163256004887565</v>
+      </c>
+      <c r="I161"/>
+      <c r="J161" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>33</v>
+      </c>
+      <c r="B162" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" t="s">
+        <v>25</v>
+      </c>
+      <c r="D162" t="s">
+        <v>45</v>
+      </c>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162" t="n">
+        <v>0.000543047865706622</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.0167317897776475</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>33</v>
+      </c>
+      <c r="B163" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" t="s">
+        <v>25</v>
+      </c>
+      <c r="D163" t="s">
+        <v>46</v>
+      </c>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163" t="n">
+        <v>0.000519475009195057</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.0162470793639288</v>
+      </c>
+      <c r="I163"/>
+      <c r="J163" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>33</v>
+      </c>
+      <c r="B164" t="s">
+        <v>18</v>
+      </c>
+      <c r="C164" t="s">
+        <v>25</v>
+      </c>
+      <c r="D164" t="s">
+        <v>47</v>
+      </c>
+      <c r="E164"/>
+      <c r="F164"/>
+      <c r="G164" t="n">
+        <v>0.000513500452242757</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.0161850742445635</v>
+      </c>
+      <c r="I164"/>
+      <c r="J164" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>33</v>
+      </c>
+      <c r="B165" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" t="s">
+        <v>25</v>
+      </c>
+      <c r="D165" t="s">
+        <v>48</v>
+      </c>
+      <c r="E165"/>
+      <c r="F165"/>
+      <c r="G165" t="n">
+        <v>0.00052094797713985</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.0162668611844715</v>
+      </c>
+      <c r="I165"/>
+      <c r="J165" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>33</v>
+      </c>
+      <c r="B166" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" t="s">
+        <v>27</v>
+      </c>
+      <c r="D166" t="s">
+        <v>45</v>
+      </c>
+      <c r="E166"/>
+      <c r="F166"/>
+      <c r="G166" t="n">
+        <v>0.000507669397587191</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.0167009611072887</v>
+      </c>
+      <c r="I166"/>
+      <c r="J166" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>33</v>
+      </c>
+      <c r="B167" t="s">
+        <v>18</v>
+      </c>
+      <c r="C167" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167" t="s">
+        <v>46</v>
+      </c>
+      <c r="E167"/>
+      <c r="F167"/>
+      <c r="G167" t="n">
+        <v>0.000483696791996774</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.0160660592549197</v>
+      </c>
+      <c r="I167"/>
+      <c r="J167" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>33</v>
+      </c>
+      <c r="B168" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" t="s">
+        <v>47</v>
+      </c>
+      <c r="E168"/>
+      <c r="F168"/>
+      <c r="G168" t="n">
+        <v>0.000476913884827927</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.0160363987489717</v>
+      </c>
+      <c r="I168"/>
+      <c r="J168" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>33</v>
+      </c>
+      <c r="B169" t="s">
+        <v>18</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" t="s">
+        <v>48</v>
+      </c>
+      <c r="E169"/>
+      <c r="F169"/>
+      <c r="G169" t="n">
+        <v>0.000499716019817916</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.01660320782108</v>
+      </c>
+      <c r="I169"/>
+      <c r="J169" t="n">
         <v>904</v>
       </c>
     </row>
@@ -5757,7 +6589,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -5766,7 +6598,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00126552460555184</v>
+        <v>0.00118710489541064</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -5777,16 +6609,16 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>486827228619523549322688062066646480082602666</v>
+        <v>0.00118992302681252</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -5797,7 +6629,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
@@ -5806,7 +6638,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119812518037437</v>
+        <v>0.00120888915972737</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -5826,7 +6658,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00119045153354722</v>
+        <v>0.00121102494337189</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -5837,7 +6669,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
@@ -5846,7 +6678,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00150347843837243</v>
+        <v>0.00146612702870325</v>
       </c>
       <c r="F6" t="e">
         <v>#NUM!</v>
@@ -5857,7 +6689,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -5866,7 +6698,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00146192432346368</v>
+        <v>0.00146474001519992</v>
       </c>
       <c r="F7" t="e">
         <v>#NUM!</v>
@@ -5877,7 +6709,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -5886,7 +6718,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00148846437765503</v>
+        <v>0.00145854581431091</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -5894,10 +6726,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
@@ -5906,7 +6738,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00042244035489045</v>
+        <v>0.00149095881563447</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -5917,16 +6749,16 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.164513643944572</v>
+        <v>0.000404639665769637</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -5937,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
@@ -5946,7 +6778,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000409507909311519</v>
+        <v>0.000401051682161039</v>
       </c>
       <c r="F11" t="e">
         <v>#NUM!</v>
@@ -5957,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
@@ -5966,7 +6798,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000414729517831938</v>
+        <v>0.000407653697028009</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -5974,10 +6806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
@@ -5986,7 +6818,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000462574883618965</v>
+        <v>0.000414558663701281</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -5997,16 +6829,16 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D14" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00141390288035645</v>
+        <v>0.00044471077895024</v>
       </c>
       <c r="F14" t="e">
         <v>#NUM!</v>
@@ -6017,7 +6849,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
@@ -6026,7 +6858,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>0.000443350765599928</v>
+        <v>277.183705234536</v>
       </c>
       <c r="F15" t="e">
         <v>#NUM!</v>
@@ -6037,7 +6869,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
@@ -6046,7 +6878,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000452444944436403</v>
+        <v>0.00044525279088337</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6054,10 +6886,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
@@ -6066,7 +6898,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000591198191687707</v>
+        <v>0.000448652859508066</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -6077,16 +6909,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00154220152751991</v>
+        <v>0.000563874810009794</v>
       </c>
       <c r="F18" t="e">
         <v>#NUM!</v>
@@ -6097,7 +6929,7 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
@@ -6106,7 +6938,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000566119489409078</v>
+        <v>260.730437445636</v>
       </c>
       <c r="F19" t="e">
         <v>#NUM!</v>
@@ -6117,7 +6949,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
@@ -6126,7 +6958,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000570641311903422</v>
+        <v>0.000563651156375314</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6134,10 +6966,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" t="n">
         <v>6</v>
@@ -6146,7 +6978,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000391759243559779</v>
+        <v>0.000573197062074134</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -6157,16 +6989,16 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D22" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00137027314439076</v>
+        <v>0.000373842848622404</v>
       </c>
       <c r="F22" t="e">
         <v>#NUM!</v>
@@ -6177,7 +7009,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="n">
         <v>6</v>
@@ -6186,7 +7018,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000371633057854731</v>
+        <v>244.452111753195</v>
       </c>
       <c r="F23" t="e">
         <v>#NUM!</v>
@@ -6197,7 +7029,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C24" t="n">
         <v>6</v>
@@ -6206,7 +7038,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000379822838381609</v>
+        <v>0.000374598271876442</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -6214,10 +7046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" t="n">
         <v>6</v>
@@ -6226,7 +7058,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000394449898968812</v>
+        <v>0.000377285346165833</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -6237,16 +7069,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00137919372342571</v>
+        <v>0.00037184880765809</v>
       </c>
       <c r="F26" t="e">
         <v>#NUM!</v>
@@ -6257,7 +7089,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" t="n">
         <v>6</v>
@@ -6266,7 +7098,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000375234224953082</v>
+        <v>264.724568714491</v>
       </c>
       <c r="F27" t="e">
         <v>#NUM!</v>
@@ -6277,7 +7109,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C28" t="n">
         <v>6</v>
@@ -6286,9 +7118,29 @@
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000379925034470706</v>
+        <v>0.000375883243271889</v>
       </c>
       <c r="F28" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.000381391322032393</v>
+      </c>
+      <c r="F29" t="e">
         <v>#NUM!</v>
       </c>
     </row>

--- a/results/tscv/consolidated/Stress_Testing.xlsx
+++ b/results/tscv/consolidated/Stress_Testing.xlsx
@@ -2201,10 +2201,10 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.000168686737569334</v>
+        <v>0.000166739674733316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00970426437855947</v>
+        <v>0.00971732808060449</v>
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
@@ -2227,10 +2227,10 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" t="n">
-        <v>0.000168236202942932</v>
+        <v>0.000167175330738123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00973990321370637</v>
+        <v>0.00969679997595236</v>
       </c>
       <c r="I3"/>
       <c r="J3" t="n">
@@ -2253,10 +2253,10 @@
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="n">
-        <v>0.000167640967147996</v>
+        <v>0.000168581205434697</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00971983913639813</v>
+        <v>0.00975243476012632</v>
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
@@ -2279,10 +2279,10 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5" t="n">
-        <v>0.000167087857498274</v>
+        <v>0.000165946196747117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00976006436724071</v>
+        <v>0.00968779503037587</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
@@ -2305,10 +2305,10 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6" t="n">
-        <v>0.0000386153290708182</v>
+        <v>0.0000389508304105256</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00482244058878759</v>
+        <v>0.00479221654974713</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
@@ -2331,10 +2331,10 @@
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7" t="n">
-        <v>0.0000378023980609803</v>
+        <v>0.0000400318637141898</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00471700070626497</v>
+        <v>0.00483614225363564</v>
       </c>
       <c r="I7"/>
       <c r="J7" t="n">
@@ -2357,10 +2357,10 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8" t="n">
-        <v>0.0000394834407488532</v>
+        <v>0.000039395853483857</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00478814537211979</v>
+        <v>0.00482974473923613</v>
       </c>
       <c r="I8"/>
       <c r="J8" t="n">
@@ -2383,10 +2383,10 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>0.0000394112321290254</v>
+        <v>0.0000409458523869202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00469353212076176</v>
+        <v>0.00487411691263711</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="n">
@@ -2409,10 +2409,10 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>0.0000922956021869149</v>
+        <v>0.0000908171867866898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00378485086983949</v>
+        <v>0.00366519621067291</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
@@ -2435,10 +2435,10 @@
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11" t="n">
-        <v>0.0000907506172258539</v>
+        <v>0.0000911173378568578</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00367630682558506</v>
+        <v>0.00368329611257963</v>
       </c>
       <c r="I11"/>
       <c r="J11" t="n">
@@ -2461,10 +2461,10 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>0.0000914684156053927</v>
+        <v>0.0000905535712653308</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00368087774282922</v>
+        <v>0.00366131247505962</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="n">
@@ -2487,10 +2487,10 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13" t="n">
-        <v>0.0000913645256547515</v>
+        <v>0.0000909296862838701</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00368213840455138</v>
+        <v>0.00369546173378378</v>
       </c>
       <c r="I13"/>
       <c r="J13" t="n">
@@ -2513,10 +2513,10 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>0.000211350394932267</v>
+        <v>0.000210323748351391</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003921862825395</v>
+        <v>0.00381801617738811</v>
       </c>
       <c r="I14"/>
       <c r="J14" t="n">
@@ -2539,10 +2539,10 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15" t="n">
-        <v>0.000210728933767226</v>
+        <v>0.00021131422926976</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00381014909457183</v>
+        <v>0.0038231289768156</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
@@ -2565,10 +2565,10 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16" t="n">
-        <v>0.000210393678860455</v>
+        <v>0.000210821777926766</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00382824735651945</v>
+        <v>0.00379901350243081</v>
       </c>
       <c r="I16"/>
       <c r="J16" t="n">
@@ -2591,10 +2591,10 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17" t="n">
-        <v>0.000211427416628283</v>
+        <v>0.000210327126665955</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00389796200836763</v>
+        <v>0.00384210305857647</v>
       </c>
       <c r="I17"/>
       <c r="J17" t="n">
@@ -2617,10 +2617,10 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18" t="n">
-        <v>0.0000232088540785513</v>
+        <v>0.0000220711242461332</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0036058099865878</v>
+        <v>0.00344949018560108</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="n">
@@ -2643,10 +2643,10 @@
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19" t="n">
-        <v>0.0000226511844505215</v>
+        <v>0.000022179574728979</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00348437769626201</v>
+        <v>0.00344940609590205</v>
       </c>
       <c r="I19"/>
       <c r="J19" t="n">
@@ -2669,10 +2669,10 @@
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20" t="n">
-        <v>0.0000229900222081848</v>
+        <v>0.0000221576876840921</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00352809482603687</v>
+        <v>0.00344994502646059</v>
       </c>
       <c r="I20"/>
       <c r="J20" t="n">
@@ -2695,10 +2695,10 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21" t="n">
-        <v>0.0000231494220959247</v>
+        <v>0.0000227032859694928</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00355056968881877</v>
+        <v>0.00350208639245075</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="n">
@@ -2721,10 +2721,10 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>0.0000233571602049009</v>
+        <v>0.0000221932204066097</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00354930995829314</v>
+        <v>0.00344464200490092</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="n">
@@ -2747,10 +2747,10 @@
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23" t="n">
-        <v>0.0000223940601573486</v>
+        <v>0.0000223488776437385</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00346981488964342</v>
+        <v>0.00346957300140853</v>
       </c>
       <c r="I23"/>
       <c r="J23" t="n">
@@ -2773,10 +2773,10 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>0.0000224510731310887</v>
+        <v>0.0000221176829550244</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00347652432655019</v>
+        <v>0.00343953476475697</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="n">
@@ -2799,10 +2799,10 @@
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25" t="n">
-        <v>0.0000232720939810087</v>
+        <v>0.0000228410825216375</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00357471577159604</v>
+        <v>0.0035227248423214</v>
       </c>
       <c r="I25"/>
       <c r="J25" t="n">
@@ -2825,10 +2825,10 @@
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>0.000120540652121086</v>
+        <v>0.000119559917594589</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0100232398421714</v>
+        <v>0.0100392337062433</v>
       </c>
       <c r="I26"/>
       <c r="J26" t="n">
@@ -2851,10 +2851,10 @@
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>0.000106296848924159</v>
+        <v>0.000126102572491251</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00934027628530819</v>
+        <v>0.0103505519399723</v>
       </c>
       <c r="I27"/>
       <c r="J27" t="n">
@@ -2877,10 +2877,10 @@
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28" t="n">
-        <v>0.000116967864819721</v>
+        <v>0.000118149298394823</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00990176833993203</v>
+        <v>0.00998068235862</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="n">
@@ -2903,10 +2903,10 @@
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29" t="n">
-        <v>0.000118315173643447</v>
+        <v>0.000119268811863974</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00993426682254106</v>
+        <v>0.0100062668000053</v>
       </c>
       <c r="I29"/>
       <c r="J29" t="n">
@@ -2929,10 +2929,10 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30" t="n">
-        <v>0.000236804905302296</v>
+        <v>0.000237024151559849</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0116563082193521</v>
+        <v>0.0116382393245931</v>
       </c>
       <c r="I30"/>
       <c r="J30" t="n">
@@ -2955,10 +2955,10 @@
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31" t="n">
-        <v>0.000237904404177027</v>
+        <v>0.00023852208040406</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0116763635278883</v>
+        <v>0.0117123382470976</v>
       </c>
       <c r="I31"/>
       <c r="J31" t="n">
@@ -2981,10 +2981,10 @@
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32" t="n">
-        <v>0.000237017374322692</v>
+        <v>0.000237499926222673</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0116726757098799</v>
+        <v>0.011678521418508</v>
       </c>
       <c r="I32"/>
       <c r="J32" t="n">
@@ -3007,10 +3007,10 @@
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33" t="n">
-        <v>0.000238000343978433</v>
+        <v>0.00023873183209257</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0116452030309526</v>
+        <v>0.011675248076978</v>
       </c>
       <c r="I33"/>
       <c r="J33" t="n">
@@ -3033,10 +3033,10 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34" t="n">
-        <v>0.0000999825289280912</v>
+        <v>0.0000968264802807851</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00755927944562779</v>
+        <v>0.00737437235015226</v>
       </c>
       <c r="I34"/>
       <c r="J34" t="n">
@@ -3059,10 +3059,10 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35" t="n">
-        <v>0.0000974047982652119</v>
+        <v>0.0000956232853216208</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00741560260665682</v>
+        <v>0.00737383150229211</v>
       </c>
       <c r="I35"/>
       <c r="J35" t="n">
@@ -3085,10 +3085,10 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36" t="n">
-        <v>0.0000951585798623853</v>
+        <v>0.0000951271634404866</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00737769734665302</v>
+        <v>0.0072793287018844</v>
       </c>
       <c r="I36"/>
       <c r="J36" t="n">
@@ -3111,10 +3111,10 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37" t="n">
-        <v>0.0000993925629937166</v>
+        <v>0.0000962687695955398</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00751358060098026</v>
+        <v>0.00745593004436244</v>
       </c>
       <c r="I37"/>
       <c r="J37" t="n">
@@ -3137,10 +3137,10 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38" t="n">
-        <v>0.000104702579344837</v>
+        <v>0.000103575565856709</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00463123764796006</v>
+        <v>0.004551842318293</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="n">
@@ -3163,10 +3163,10 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39" t="n">
-        <v>0.00010389585641762</v>
+        <v>0.000103719350853209</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00455391891663834</v>
+        <v>0.00458193897051283</v>
       </c>
       <c r="I39"/>
       <c r="J39" t="n">
@@ -3189,10 +3189,10 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40" t="n">
-        <v>0.000103372509090942</v>
+        <v>0.000103265523226432</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00456723159661185</v>
+        <v>0.00455632580972199</v>
       </c>
       <c r="I40"/>
       <c r="J40" t="n">
@@ -3215,10 +3215,10 @@
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41" t="n">
-        <v>0.000104424051995499</v>
+        <v>0.000104232883771404</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00462734696647701</v>
+        <v>0.00460177075401775</v>
       </c>
       <c r="I41"/>
       <c r="J41" t="n">
@@ -3241,10 +3241,10 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42" t="n">
-        <v>0.000223442459273849</v>
+        <v>0.000222942591649192</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00472879138096696</v>
+        <v>0.00471176308168258</v>
       </c>
       <c r="I42"/>
       <c r="J42" t="n">
@@ -3267,10 +3267,10 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43" t="n">
-        <v>0.000223270431163083</v>
+        <v>0.000222865076190597</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0047173388039747</v>
+        <v>0.00471187698067763</v>
       </c>
       <c r="I43"/>
       <c r="J43" t="n">
@@ -3293,10 +3293,10 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44" t="n">
-        <v>0.000223024977418473</v>
+        <v>0.000222898724811435</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0047873471827905</v>
+        <v>0.00469845482594636</v>
       </c>
       <c r="I44"/>
       <c r="J44" t="n">
@@ -3319,10 +3319,10 @@
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45" t="n">
-        <v>0.000222930889382302</v>
+        <v>0.00022348319959687</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00474581917642731</v>
+        <v>0.00476126434005401</v>
       </c>
       <c r="I45"/>
       <c r="J45" t="n">
@@ -3345,10 +3345,10 @@
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46" t="n">
-        <v>0.0000359746919818899</v>
+        <v>0.0000351995643943563</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00438240347630471</v>
+        <v>0.00432602359521006</v>
       </c>
       <c r="I46"/>
       <c r="J46" t="n">
@@ -3371,10 +3371,10 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47" t="n">
-        <v>0.000035235966439632</v>
+        <v>0.0000354932123842432</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00432894530812585</v>
+        <v>0.0043457973205701</v>
       </c>
       <c r="I47"/>
       <c r="J47" t="n">
@@ -3397,10 +3397,10 @@
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48" t="n">
-        <v>0.0000356361541387039</v>
+        <v>0.0000352290908133938</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00436759379794043</v>
+        <v>0.00433441473027599</v>
       </c>
       <c r="I48"/>
       <c r="J48" t="n">
@@ -3423,10 +3423,10 @@
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49" t="n">
-        <v>0.0000354904021115412</v>
+        <v>0.0000353256814976408</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00436297947203369</v>
+        <v>0.00433976327562276</v>
       </c>
       <c r="I49"/>
       <c r="J49" t="n">
@@ -3449,10 +3449,10 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50" t="n">
-        <v>0.0000362362044807949</v>
+        <v>0.0000353661460515132</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00443177269633432</v>
+        <v>0.00434047603229454</v>
       </c>
       <c r="I50"/>
       <c r="J50" t="n">
@@ -3475,10 +3475,10 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51" t="n">
-        <v>0.0000355853632810226</v>
+        <v>0.0000353996572259399</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00435922847561209</v>
+        <v>0.00435014343138524</v>
       </c>
       <c r="I51"/>
       <c r="J51" t="n">
@@ -3501,10 +3501,10 @@
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52" t="n">
-        <v>0.0000356033391908351</v>
+        <v>0.0000354204932749904</v>
       </c>
       <c r="H52" t="n">
-        <v>0.00435646065481362</v>
+        <v>0.00434479800363271</v>
       </c>
       <c r="I52"/>
       <c r="J52" t="n">
@@ -3527,10 +3527,10 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53" t="n">
-        <v>0.000035982894150643</v>
+        <v>0.0000354165973363969</v>
       </c>
       <c r="H53" t="n">
-        <v>0.00439722824158237</v>
+        <v>0.0043683154994951</v>
       </c>
       <c r="I53"/>
       <c r="J53" t="n">
@@ -3553,10 +3553,10 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54" t="n">
-        <v>0.000133937324975609</v>
+        <v>0.00013173125919463</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0102200584145401</v>
+        <v>0.0101683370068564</v>
       </c>
       <c r="I54"/>
       <c r="J54" t="n">
@@ -3579,10 +3579,10 @@
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55" t="n">
-        <v>0.000121180774813075</v>
+        <v>0.00013721539361702</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00964956235694822</v>
+        <v>0.0104372712014222</v>
       </c>
       <c r="I55"/>
       <c r="J55" t="n">
@@ -3605,10 +3605,10 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56" t="n">
-        <v>0.000129859286215571</v>
+        <v>0.000131895909839568</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0100765075196595</v>
+        <v>0.0101787870098288</v>
       </c>
       <c r="I56"/>
       <c r="J56" t="n">
@@ -3631,10 +3631,10 @@
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57" t="n">
-        <v>0.000130091906556003</v>
+        <v>0.000131999591766133</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0100991634425751</v>
+        <v>0.010191526874584</v>
       </c>
       <c r="I57"/>
       <c r="J57" t="n">
@@ -3657,10 +3657,10 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000512935534977831</v>
+        <v>0.000514871623255834</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0164555057095175</v>
+        <v>0.0163596111610899</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -3683,10 +3683,10 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000511654546906692</v>
+        <v>0.000515581267172311</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0164046040155046</v>
+        <v>0.0162963363513796</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3709,10 +3709,10 @@
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000519041305054462</v>
+        <v>0.000510962126007053</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0165044597835108</v>
+        <v>0.0163684629636016</v>
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
@@ -3735,10 +3735,10 @@
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.000512448589273347</v>
+        <v>0.000518031264874855</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0163613939816283</v>
+        <v>0.0164481290485706</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
@@ -3761,10 +3761,10 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000248075866297095</v>
+        <v>0.000260188711618463</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0118051946360816</v>
+        <v>0.0121258593927602</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -3787,10 +3787,10 @@
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.000257183328146995</v>
+        <v>0.000259065133200994</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0120355614314482</v>
+        <v>0.0121220291895014</v>
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
@@ -3813,10 +3813,10 @@
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.000257443841003865</v>
+        <v>0.000259318123429544</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0120066819635446</v>
+        <v>0.0121009912602446</v>
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
@@ -3839,10 +3839,10 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000270249309905327</v>
+        <v>0.000256894238556425</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0122733800799607</v>
+        <v>0.0120941920059368</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -3865,10 +3865,10 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000161957040681193</v>
+        <v>0.000162586279202364</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00772500689816771</v>
+        <v>0.00770558800555955</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -3891,10 +3891,10 @@
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67" t="n">
-        <v>1663.09973067643</v>
+        <v>1213.74285915808</v>
       </c>
       <c r="H67" t="n">
-        <v>12.6840802122295</v>
+        <v>7.76426077312173</v>
       </c>
       <c r="I67"/>
       <c r="J67" t="n">
@@ -3917,10 +3917,10 @@
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.000163578182170081</v>
+        <v>0.000162611247765157</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00775203402117957</v>
+        <v>0.00772844257661858</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -3943,10 +3943,10 @@
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.000164470142479517</v>
+        <v>0.000164737133869094</v>
       </c>
       <c r="H69" t="n">
-        <v>0.00777749603931179</v>
+        <v>0.00778915638572289</v>
       </c>
       <c r="I69"/>
       <c r="J69" t="n">
@@ -3969,10 +3969,10 @@
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.000285131891584473</v>
+        <v>0.000281960284267101</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0080224320049326</v>
+        <v>0.00783862267199919</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -3995,10 +3995,10 @@
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>1564.3795283474</v>
+        <v>1305.59381848702</v>
       </c>
       <c r="H71" t="n">
-        <v>11.9711109062993</v>
+        <v>8.42261251279047</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4021,10 +4021,10 @@
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>0.000282639004577642</v>
+        <v>0.000282410295172309</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00789756356496828</v>
+        <v>0.0078770578332271</v>
       </c>
       <c r="I72"/>
       <c r="J72" t="n">
@@ -4047,10 +4047,10 @@
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.00028155166371426</v>
+        <v>0.000280795607591805</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00796701951373207</v>
+        <v>0.00787537753172</v>
       </c>
       <c r="I73"/>
       <c r="J73" t="n">
@@ -4073,10 +4073,10 @@
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.0000958246169292301</v>
+        <v>0.0000940433060653965</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00763734644735006</v>
+        <v>0.00750967045408458</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4099,10 +4099,10 @@
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>1466.71053284717</v>
+        <v>1309.0573790592</v>
       </c>
       <c r="H75" t="n">
-        <v>11.4991303173457</v>
+        <v>8.50789169517494</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4125,10 +4125,10 @@
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.0000948734599761424</v>
+        <v>0.0000938119979712337</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0075493703811761</v>
+        <v>0.00752160542967396</v>
       </c>
       <c r="I76"/>
       <c r="J76" t="n">
@@ -4151,10 +4151,10 @@
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.0000946296577866486</v>
+        <v>0.0000948789136557377</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00752994079255258</v>
+        <v>0.00758009648366493</v>
       </c>
       <c r="I77"/>
       <c r="J77" t="n">
@@ -4177,10 +4177,10 @@
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.0000955474004635864</v>
+        <v>0.0000937679823806852</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00760449763704258</v>
+        <v>0.00748359730946349</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4203,10 +4203,10 @@
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>1588.34526170424</v>
+        <v>988.789718931182</v>
       </c>
       <c r="H79" t="n">
-        <v>12.1781456887244</v>
+        <v>6.80298988814467</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4229,10 +4229,10 @@
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.0000947829313999953</v>
+        <v>0.0000940730250249333</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00753189187385555</v>
+        <v>0.00750398603015387</v>
       </c>
       <c r="I80"/>
       <c r="J80" t="n">
@@ -4255,10 +4255,10 @@
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.0000946462708001455</v>
+        <v>0.0000950396415045482</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00761112959337621</v>
+        <v>0.00757004383527859</v>
       </c>
       <c r="I81"/>
       <c r="J81" t="n">
@@ -4281,10 +4281,10 @@
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000216789997276877</v>
+        <v>0.000206902778904061</v>
       </c>
       <c r="H82" t="n">
-        <v>0.012301206468053</v>
+        <v>0.0119538641845173</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4307,10 +4307,10 @@
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.000213509334404182</v>
+        <v>0.000213787473182652</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0121511012997335</v>
+        <v>0.0121913586574552</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4333,10 +4333,10 @@
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.000214053087882048</v>
+        <v>0.000213071141908161</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0122106716400761</v>
+        <v>0.0121255161008157</v>
       </c>
       <c r="I84"/>
       <c r="J84" t="n">
@@ -4359,10 +4359,10 @@
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.00021738260783654</v>
+        <v>0.000216909117864017</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0123246217175259</v>
+        <v>0.0123069544453788</v>
       </c>
       <c r="I85"/>
       <c r="J85" t="n">
@@ -4385,10 +4385,10 @@
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00369352599892388</v>
+        <v>0.00356709287518203</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0497580197898968</v>
+        <v>0.0492007849855877</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4411,10 +4411,10 @@
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00354772992768419</v>
+        <v>0.00361467683447758</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0491210230233158</v>
+        <v>0.0496728683521829</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4437,10 +4437,10 @@
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00355271394535845</v>
+        <v>0.00359154994380956</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0491085012441402</v>
+        <v>0.0491321379267671</v>
       </c>
       <c r="I88"/>
       <c r="J88" t="n">
@@ -4463,10 +4463,10 @@
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00353421669524982</v>
+        <v>0.00357367400960657</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0490565975738826</v>
+        <v>0.0494550331160037</v>
       </c>
       <c r="I89"/>
       <c r="J89" t="n">
@@ -4489,10 +4489,10 @@
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00355270279557635</v>
+        <v>0.00347343413176563</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0460753129578416</v>
+        <v>0.0455677016188068</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -4515,10 +4515,10 @@
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00343804634900417</v>
+        <v>0.00349043678651564</v>
       </c>
       <c r="H91" t="n">
-        <v>0.045094578317627</v>
+        <v>0.0456121639974128</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4541,10 +4541,10 @@
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.00343959241065118</v>
+        <v>0.0034556929213981</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0453659749178632</v>
+        <v>0.0452045464056649</v>
       </c>
       <c r="I92"/>
       <c r="J92" t="n">
@@ -4567,10 +4567,10 @@
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.00350663983150039</v>
+        <v>0.00350824349449575</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0457573133402959</v>
+        <v>0.0455409538236593</v>
       </c>
       <c r="I93"/>
       <c r="J93" t="n">
@@ -4593,10 +4593,10 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00129035044303019</v>
+        <v>0.00126524291543443</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0256395260221728</v>
+        <v>0.0253375134652221</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4619,10 +4619,10 @@
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.00127436514713176</v>
+        <v>0.00127711952409654</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0254600435622212</v>
+        <v>0.0254814280930115</v>
       </c>
       <c r="I95"/>
       <c r="J95" t="n">
@@ -4645,10 +4645,10 @@
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00128060708435289</v>
+        <v>0.00126738530947306</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0255234208821561</v>
+        <v>0.0253654245953917</v>
       </c>
       <c r="I96"/>
       <c r="J96" t="n">
@@ -4671,10 +4671,10 @@
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00128192663492686</v>
+        <v>0.00126866914403079</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0255157186909293</v>
+        <v>0.0253719531646511</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -4697,10 +4697,10 @@
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00143579095474943</v>
+        <v>0.00139699309507506</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0261568613012915</v>
+        <v>0.0255469344955213</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -4723,10 +4723,10 @@
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.00140124320033395</v>
+        <v>0.00139789893744094</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0255765391737544</v>
+        <v>0.0255180572916646</v>
       </c>
       <c r="I99"/>
       <c r="J99" t="n">
@@ -4749,10 +4749,10 @@
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00140475795566244</v>
+        <v>0.00139856072290935</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0255241783256353</v>
+        <v>0.0255102068619735</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -4775,10 +4775,10 @@
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.00140091531708612</v>
+        <v>0.0013970158963728</v>
       </c>
       <c r="H101" t="n">
-        <v>0.025542591428094</v>
+        <v>0.0254483740475441</v>
       </c>
       <c r="I101"/>
       <c r="J101" t="n">
@@ -4801,10 +4801,10 @@
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00120380258915943</v>
+        <v>0.00118888995517411</v>
       </c>
       <c r="H102" t="n">
-        <v>0.025350748529651</v>
+        <v>0.0251469497211458</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -4827,10 +4827,10 @@
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.00118910009996879</v>
+        <v>0.0011922663691207</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0251760878001323</v>
+        <v>0.0252102347187435</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -4853,10 +4853,10 @@
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00119455660986713</v>
+        <v>0.00119073380143728</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0252563211160035</v>
+        <v>0.0251662408435151</v>
       </c>
       <c r="I104"/>
       <c r="J104" t="n">
@@ -4879,10 +4879,10 @@
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.00119823918618116</v>
+        <v>0.00119554228152484</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0253014571575711</v>
+        <v>0.0252196956628167</v>
       </c>
       <c r="I105"/>
       <c r="J105" t="n">
@@ -4905,10 +4905,10 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00121763751794577</v>
+        <v>0.00119266728566019</v>
       </c>
       <c r="H106" t="n">
-        <v>0.025625397910974</v>
+        <v>0.0251880273764967</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -4931,10 +4931,10 @@
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.00119840434109664</v>
+        <v>0.00119907927963404</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0252798115904623</v>
+        <v>0.0252650970235112</v>
       </c>
       <c r="I107"/>
       <c r="J107" t="n">
@@ -4957,10 +4957,10 @@
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.00119017417691742</v>
+        <v>0.00119286974617785</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0251711302816443</v>
+        <v>0.0251750369276858</v>
       </c>
       <c r="I108"/>
       <c r="J108" t="n">
@@ -4983,10 +4983,10 @@
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.0012053431965726</v>
+        <v>0.00119224520621769</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0252768974756966</v>
+        <v>0.0251990886329344</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5009,10 +5009,10 @@
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.00108197780049487</v>
+        <v>0.00105190919406783</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0230963740660201</v>
+        <v>0.0226437487805914</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5035,10 +5035,10 @@
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.00105407380759895</v>
+        <v>0.00104880333000164</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0226763546446701</v>
+        <v>0.0225643052973476</v>
       </c>
       <c r="I111"/>
       <c r="J111" t="n">
@@ -5061,10 +5061,10 @@
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.00106003589548525</v>
+        <v>0.00105118426391401</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0227862202339599</v>
+        <v>0.0226355189916163</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5087,10 +5087,10 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.00105220992570386</v>
+        <v>0.00105929170646389</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0227001500533439</v>
+        <v>0.0227374738466541</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5113,10 +5113,10 @@
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00165502619576309</v>
+        <v>0.00166657826440175</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0305528222442102</v>
+        <v>0.0306961695852543</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5139,10 +5139,10 @@
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.00166359505222445</v>
+        <v>0.00167355487426778</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0308437990252989</v>
+        <v>0.0308007466693071</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
@@ -5165,10 +5165,10 @@
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.00166100913752892</v>
+        <v>0.0016679229279071</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0306082060158772</v>
+        <v>0.0306488592878618</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5191,10 +5191,10 @@
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.00165684377203145</v>
+        <v>0.00166336609497293</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0304732562987995</v>
+        <v>0.0306152304432491</v>
       </c>
       <c r="I117"/>
       <c r="J117" t="n">
@@ -5217,10 +5217,10 @@
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.00222253296534883</v>
+        <v>0.0022097436548237</v>
       </c>
       <c r="H118" t="n">
-        <v>0.035264455681476</v>
+        <v>0.035050748939306</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5243,10 +5243,10 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00222319933563074</v>
+        <v>0.00221710847752892</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0351416885485996</v>
+        <v>0.0350879420045787</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5269,10 +5269,10 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00220320085094273</v>
+        <v>0.00223248760201288</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0348386740287209</v>
+        <v>0.0352798684248624</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5295,10 +5295,10 @@
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00221809193670733</v>
+        <v>0.00220302886527406</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0350474210916605</v>
+        <v>0.0349619618279106</v>
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
@@ -5321,10 +5321,10 @@
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.000440119886170392</v>
+        <v>0.00044022273608923</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0139405819358338</v>
+        <v>0.0138252451802776</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5347,10 +5347,10 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000445903984119878</v>
+        <v>0.000439897445163341</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0139926558046294</v>
+        <v>0.0138770372669694</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5373,10 +5373,10 @@
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000442636324440099</v>
+        <v>0.000440413564673099</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0138867340452424</v>
+        <v>0.0138447314947511</v>
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
@@ -5399,10 +5399,10 @@
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000439709052166203</v>
+        <v>0.000438793509147836</v>
       </c>
       <c r="H125" t="n">
-        <v>0.013875833694454</v>
+        <v>0.0138041252317179</v>
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
@@ -5425,10 +5425,10 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000560115011666399</v>
+        <v>0.000561507988559075</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0140881155061466</v>
+        <v>0.0140052168487452</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5451,10 +5451,10 @@
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000559558929536151</v>
+        <v>0.000561454361354745</v>
       </c>
       <c r="H127" t="n">
-        <v>0.0140403875404967</v>
+        <v>0.014025753891243</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -5477,10 +5477,10 @@
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000558394037696748</v>
+        <v>0.000557896256776269</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0140000347577634</v>
+        <v>0.0139729587331149</v>
       </c>
       <c r="I128"/>
       <c r="J128" t="n">
@@ -5503,10 +5503,10 @@
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000559021170580466</v>
+        <v>0.000556402491690548</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0139640831077842</v>
+        <v>0.013994148780252</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -5529,10 +5529,10 @@
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000371453106856845</v>
+        <v>0.000372328070510838</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0136160226452815</v>
+        <v>0.013628839874028</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -5555,10 +5555,10 @@
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000373848327756974</v>
+        <v>0.000372776889516162</v>
       </c>
       <c r="H131" t="n">
-        <v>0.013680312990796</v>
+        <v>0.0136249609336273</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -5581,10 +5581,10 @@
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000374836588957323</v>
+        <v>0.000373195497273434</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0136626597154048</v>
+        <v>0.0136120071781038</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -5607,10 +5607,10 @@
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000374532232784796</v>
+        <v>0.000373069837619335</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0136589524247012</v>
+        <v>0.0136225126161665</v>
       </c>
       <c r="I133"/>
       <c r="J133" t="n">
@@ -5633,10 +5633,10 @@
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000372521783392687</v>
+        <v>0.000372794714475328</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0136799771878366</v>
+        <v>0.0136085662090615</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -5659,10 +5659,10 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000374723936197941</v>
+        <v>0.000375706967440677</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0136647583598699</v>
+        <v>0.0136523246886673</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -5685,10 +5685,10 @@
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000374580873066442</v>
+        <v>0.000371812999795075</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0137190504733313</v>
+        <v>0.0136239618090333</v>
       </c>
       <c r="I136"/>
       <c r="J136" t="n">
@@ -5711,10 +5711,10 @@
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000375107026987081</v>
+        <v>0.000373071949175921</v>
       </c>
       <c r="H137" t="n">
-        <v>0.013687605946763</v>
+        <v>0.013642436151581</v>
       </c>
       <c r="I137"/>
       <c r="J137" t="n">
@@ -5737,10 +5737,10 @@
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.000426436809752057</v>
+        <v>0.000426298441099335</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0143845633893955</v>
+        <v>0.0143954509505574</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -5763,10 +5763,10 @@
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139" t="n">
-        <v>0.000427552535229091</v>
+        <v>0.000426961747789713</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0144086472176001</v>
+        <v>0.0144382224623116</v>
       </c>
       <c r="I139"/>
       <c r="J139" t="n">
@@ -5789,10 +5789,10 @@
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140" t="n">
-        <v>0.000430007975387303</v>
+        <v>0.00042556844247673</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0144203292809099</v>
+        <v>0.0143859614426913</v>
       </c>
       <c r="I140"/>
       <c r="J140" t="n">
@@ -5815,10 +5815,10 @@
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141" t="n">
-        <v>0.000428206548610281</v>
+        <v>0.000426453714080303</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0144581726169688</v>
+        <v>0.0143987429518154</v>
       </c>
       <c r="I141"/>
       <c r="J141" t="n">
@@ -5841,10 +5841,10 @@
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00267877352127038</v>
+        <v>0.00266189274448004</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0401637450653961</v>
+        <v>0.0395332494639327</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -5867,10 +5867,10 @@
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143" t="n">
-        <v>0.00265931995726425</v>
+        <v>0.00264407450488645</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0398537793948801</v>
+        <v>0.0395308620255686</v>
       </c>
       <c r="I143"/>
       <c r="J143" t="n">
@@ -5893,10 +5893,10 @@
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144" t="n">
-        <v>0.002659339442807</v>
+        <v>0.00264094073260641</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0396123016401896</v>
+        <v>0.0395708532395442</v>
       </c>
       <c r="I144"/>
       <c r="J144" t="n">
@@ -5919,10 +5919,10 @@
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145" t="n">
-        <v>0.00264267762783412</v>
+        <v>0.00264900354608587</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0397137216065568</v>
+        <v>0.0397517171495199</v>
       </c>
       <c r="I145"/>
       <c r="J145" t="n">
@@ -5945,10 +5945,10 @@
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00110424017501015</v>
+        <v>0.00109660996556027</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0249465338842973</v>
+        <v>0.0250020115801956</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -5971,10 +5971,10 @@
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147" t="n">
-        <v>0.00108590195176701</v>
+        <v>0.00109240580509464</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0250318041867535</v>
+        <v>0.0251838339596461</v>
       </c>
       <c r="I147"/>
       <c r="J147" t="n">
@@ -5997,10 +5997,10 @@
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148" t="n">
-        <v>0.0010877502492548</v>
+        <v>0.00110657037146525</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0249108810621583</v>
+        <v>0.025247114266781</v>
       </c>
       <c r="I148"/>
       <c r="J148" t="n">
@@ -6023,10 +6023,10 @@
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149" t="n">
-        <v>0.00111955008512846</v>
+        <v>0.00109186411368117</v>
       </c>
       <c r="H149" t="n">
-        <v>0.025272163028466</v>
+        <v>0.0250789892918997</v>
       </c>
       <c r="I149"/>
       <c r="J149" t="n">
@@ -6049,10 +6049,10 @@
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.000602491605634867</v>
+        <v>0.00058163298147872</v>
       </c>
       <c r="H150" t="n">
-        <v>0.0168121152571472</v>
+        <v>0.016436389149377</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6075,10 +6075,10 @@
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151" t="n">
-        <v>0.000585815177060615</v>
+        <v>0.000581864447813023</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0164628841768857</v>
+        <v>0.016404261896359</v>
       </c>
       <c r="I151"/>
       <c r="J151" t="n">
@@ -6101,10 +6101,10 @@
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152" t="n">
-        <v>0.000586602158042034</v>
+        <v>0.000584543883198312</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0164976815877205</v>
+        <v>0.0163803862295117</v>
       </c>
       <c r="I152"/>
       <c r="J152" t="n">
@@ -6127,10 +6127,10 @@
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153" t="n">
-        <v>0.00058962233807739</v>
+        <v>0.000581818645006164</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0165761279652862</v>
+        <v>0.0164240756376304</v>
       </c>
       <c r="I153"/>
       <c r="J153" t="n">
@@ -6153,10 +6153,10 @@
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.000723351660238384</v>
+        <v>0.000704502166220318</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0171328568079931</v>
+        <v>0.0165653600492239</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6179,10 +6179,10 @@
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155" t="n">
-        <v>0.000701524917890142</v>
+        <v>0.000700754734122636</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0165958984521632</v>
+        <v>0.0165200377477486</v>
       </c>
       <c r="I155"/>
       <c r="J155" t="n">
@@ -6205,10 +6205,10 @@
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156" t="n">
-        <v>0.000704039205843003</v>
+        <v>0.000702709578892673</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0166165324423514</v>
+        <v>0.0165307045727206</v>
       </c>
       <c r="I156"/>
       <c r="J156" t="n">
@@ -6231,10 +6231,10 @@
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157" t="n">
-        <v>0.00070606048086045</v>
+        <v>0.000704768889545307</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0166046670898993</v>
+        <v>0.0165235072709543</v>
       </c>
       <c r="I157"/>
       <c r="J157" t="n">
@@ -6257,10 +6257,10 @@
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000533448217989059</v>
+        <v>0.000514879860652079</v>
       </c>
       <c r="H158" t="n">
-        <v>0.0166916016629204</v>
+        <v>0.016186575928726</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -6283,10 +6283,10 @@
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159" t="n">
-        <v>0.000516836420673964</v>
+        <v>0.0005174780349884</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0162639579890522</v>
+        <v>0.0161996287580614</v>
       </c>
       <c r="I159"/>
       <c r="J159" t="n">
@@ -6309,10 +6309,10 @@
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160" t="n">
-        <v>0.000520164256586935</v>
+        <v>0.000515251300566603</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0163647933196485</v>
+        <v>0.0161738179102516</v>
       </c>
       <c r="I160"/>
       <c r="J160" t="n">
@@ -6335,10 +6335,10 @@
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161" t="n">
-        <v>0.000521548730298579</v>
+        <v>0.00051515569079851</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0163256004887565</v>
+        <v>0.0162050688203587</v>
       </c>
       <c r="I161"/>
       <c r="J161" t="n">
@@ -6361,10 +6361,10 @@
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000543047865706622</v>
+        <v>0.000515975483538925</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0167317897776475</v>
+        <v>0.0162143467350227</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -6387,10 +6387,10 @@
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163" t="n">
-        <v>0.000519475009195057</v>
+        <v>0.000515249399204647</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0162470793639288</v>
+        <v>0.0161837631667627</v>
       </c>
       <c r="I163"/>
       <c r="J163" t="n">
@@ -6413,10 +6413,10 @@
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164" t="n">
-        <v>0.000513500452242757</v>
+        <v>0.000517974044082233</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0161850742445635</v>
+        <v>0.0162550329107774</v>
       </c>
       <c r="I164"/>
       <c r="J164" t="n">
@@ -6439,10 +6439,10 @@
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165" t="n">
-        <v>0.00052094797713985</v>
+        <v>0.000514517663048894</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0162668611844715</v>
+        <v>0.0161573997755607</v>
       </c>
       <c r="I165"/>
       <c r="J165" t="n">
@@ -6465,10 +6465,10 @@
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000507669397587191</v>
+        <v>0.000472414088593065</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0167009611072887</v>
+        <v>0.0158472107195783</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -6491,10 +6491,10 @@
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167" t="n">
-        <v>0.000483696791996774</v>
+        <v>0.000474557244125652</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0160660592549197</v>
+        <v>0.0159164374511597</v>
       </c>
       <c r="I167"/>
       <c r="J167" t="n">
@@ -6517,10 +6517,10 @@
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168" t="n">
-        <v>0.000476913884827927</v>
+        <v>0.000473096321388058</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0160363987489717</v>
+        <v>0.0158568789536106</v>
       </c>
       <c r="I168"/>
       <c r="J168" t="n">
@@ -6543,10 +6543,10 @@
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169" t="n">
-        <v>0.000499716019817916</v>
+        <v>0.000498501614556952</v>
       </c>
       <c r="H169" t="n">
-        <v>0.01660320782108</v>
+        <v>0.0163844868958091</v>
       </c>
       <c r="I169"/>
       <c r="J169" t="n">
@@ -6598,7 +6598,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00118710489541064</v>
+        <v>0.00119809867253835</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -6618,7 +6618,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00118992302681252</v>
+        <v>0.001199111891896</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -6638,7 +6638,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00120888915972737</v>
+        <v>0.00119954088899831</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -6658,7 +6658,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00121102494337189</v>
+        <v>0.0011959589624099</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6678,7 +6678,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146612702870325</v>
+        <v>0.00146957614366458</v>
       </c>
       <c r="F6" t="e">
         <v>#NUM!</v>
@@ -6698,7 +6698,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00146474001519992</v>
+        <v>0.00147559748199105</v>
       </c>
       <c r="F7" t="e">
         <v>#NUM!</v>
@@ -6718,7 +6718,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00145854581431091</v>
+        <v>0.00146812549072999</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6738,7 +6738,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00149095881563447</v>
+        <v>0.0014690332222688</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -6758,7 +6758,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000404639665769637</v>
+        <v>0.000402160896320226</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6778,7 +6778,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000401051682161039</v>
+        <v>0.000404571293534656</v>
       </c>
       <c r="F11" t="e">
         <v>#NUM!</v>
@@ -6798,7 +6798,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000407653697028009</v>
+        <v>0.000408737426099211</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6818,7 +6818,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000414558663701281</v>
+        <v>0.000401469279908919</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -6838,7 +6838,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00044471077895024</v>
+        <v>0.000441462183266898</v>
       </c>
       <c r="F14" t="e">
         <v>#NUM!</v>
@@ -6858,7 +6858,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>277.183705234536</v>
+        <v>202.290892146031</v>
       </c>
       <c r="F15" t="e">
         <v>#NUM!</v>
@@ -6878,7 +6878,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00044525279088337</v>
+        <v>0.000441530167018193</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6898,7 +6898,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000448652859508066</v>
+        <v>0.000440679610808023</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -6918,7 +6918,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000563874810009794</v>
+        <v>0.0005625495594148</v>
       </c>
       <c r="F18" t="e">
         <v>#NUM!</v>
@@ -6938,7 +6938,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>260.730437445636</v>
+        <v>217.599485462393</v>
       </c>
       <c r="F19" t="e">
         <v>#NUM!</v>
@@ -6958,7 +6958,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000563651156375314</v>
+        <v>0.000562132201910548</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6978,7 +6978,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000573197062074134</v>
+        <v>0.000563038312353689</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -6998,7 +6998,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000373842848622404</v>
+        <v>0.000371729895957673</v>
       </c>
       <c r="F22" t="e">
         <v>#NUM!</v>
@@ -7018,7 +7018,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>244.452111753195</v>
+        <v>218.176586542214</v>
       </c>
       <c r="F23" t="e">
         <v>#NUM!</v>
@@ -7038,7 +7038,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.000374598271876442</v>
+        <v>0.00037277928184426</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -7058,7 +7058,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000377285346165833</v>
+        <v>0.000371235313507152</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7078,7 +7078,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00037184880765809</v>
+        <v>0.000372377998551685</v>
       </c>
       <c r="F26" t="e">
         <v>#NUM!</v>
@@ -7098,7 +7098,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>264.724568714491</v>
+        <v>164.798644452561</v>
       </c>
       <c r="F27" t="e">
         <v>#NUM!</v>
@@ -7118,7 +7118,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000375883243271889</v>
+        <v>0.000372188689967515</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>
@@ -7138,7 +7138,7 @@
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000381391322032393</v>
+        <v>0.000372127472085542</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>

--- a/results/tscv/consolidated/Stress_Testing.xlsx
+++ b/results/tscv/consolidated/Stress_Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">Asset</t>
   </si>
@@ -107,13 +107,31 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
   <si>
     <t xml:space="preserve">NVDA</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
   </si>
   <si>
     <t xml:space="preserve">AMZN</t>
@@ -1036,13 +1054,13 @@
         <v>143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0015892701912177</v>
+        <v>-0.00168768228375898</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0227080418990508</v>
+        <v>0.0142640687995322</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0171284654480273</v>
+        <v>-0.287783695478577</v>
       </c>
       <c r="I16" s="1" t="n">
         <v>39692</v>
@@ -1070,13 +1088,13 @@
         <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00332104828859296</v>
+        <v>-0.000449403652009031</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0158928496727706</v>
+        <v>0.00939792799821303</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.00551177711009121</v>
+        <v>-0.115076533623953</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>43862</v>
@@ -1104,21 +1122,21 @@
         <v>4515</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000156399423326306</v>
+        <v>-0.000163252538452272</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0117581471857289</v>
+        <v>0.00760528643800944</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.928245353333001</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L18" t="n">
-        <v>8.41718729183222</v>
+        <v>23.1703189354394</v>
       </c>
     </row>
     <row r="19">
@@ -1138,21 +1156,21 @@
         <v>4515</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000112102634843471</v>
+        <v>-0.000207549326935107</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0131969077962237</v>
+        <v>0.00965048327462749</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-1.128245353333</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L19" t="n">
-        <v>21.6834252553647</v>
+        <v>56.293009146425</v>
       </c>
     </row>
     <row r="20">
@@ -1172,21 +1190,21 @@
         <v>4515</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00022172692270406</v>
+        <v>-0.0000964639149448077</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0108460828307998</v>
+        <v>0.00617474445800522</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.626694718196798</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00740551000706102</v>
+        <v>0.00218274966114383</v>
       </c>
     </row>
     <row r="21">
@@ -1206,21 +1224,21 @@
         <v>4515</v>
       </c>
       <c r="F21" t="n">
-        <v>0.000220609239357562</v>
+        <v>-0.0000961204741615955</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0108474058914536</v>
+        <v>0.00617496547555279</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0824320966326846</v>
+        <v>-0.625144083060595</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0196049247992935</v>
+        <v>0.00576220745622006</v>
       </c>
     </row>
     <row r="22">
@@ -1240,21 +1258,21 @@
         <v>4515</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.00177937023337358</v>
+        <v>-0.00209902219515216</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0115666353334669</v>
+        <v>0.00732567829467671</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.30653212324354</v>
+        <v>-9.668245353333</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" t="n">
-        <v>0.0108452796825276</v>
+        <v>0.00617460968173331</v>
       </c>
       <c r="L22" t="n">
-        <v>6.65133285683264</v>
+        <v>18.6419656022739</v>
       </c>
     </row>
     <row r="23">
@@ -1274,13 +1292,13 @@
         <v>143</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.00173692405004033</v>
+        <v>0.0015892701912177</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0600037655773047</v>
+        <v>0.0227080418990508</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.761914216320698</v>
+        <v>0.0171284654480273</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>39692</v>
@@ -1308,13 +1326,13 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00360437391869047</v>
+        <v>0.00332104828859296</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0593766543117209</v>
+        <v>0.0158928496727706</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.184901076210231</v>
+        <v>-0.00551177711009121</v>
       </c>
       <c r="I24" s="1" t="n">
         <v>43862</v>
@@ -1342,21 +1360,21 @@
         <v>4515</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00131551872274189</v>
+        <v>0.000156399423326306</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0319688553700037</v>
+        <v>0.0117581471857289</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L25" t="n">
-        <v>1.24890533785161</v>
+        <v>8.41718729183222</v>
       </c>
     </row>
     <row r="26">
@@ -1376,21 +1394,21 @@
         <v>4515</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00127122193425906</v>
+        <v>0.000112102634843471</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0325708621645964</v>
+        <v>0.0131969077962237</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L26" t="n">
-        <v>3.15552752538385</v>
+        <v>21.6834252553647</v>
       </c>
     </row>
     <row r="27">
@@ -1410,21 +1428,21 @@
         <v>4515</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00137373208548086</v>
+        <v>0.00022172692270406</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0315894131475975</v>
+        <v>0.0108460828307998</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0471697982790727</v>
+        <v>0.00740551000706102</v>
       </c>
     </row>
     <row r="28">
@@ -1444,21 +1462,21 @@
         <v>4515</v>
       </c>
       <c r="F28" t="n">
-        <v>0.00136550026549557</v>
+        <v>0.000220609239357562</v>
       </c>
       <c r="G28" t="n">
-        <v>0.031613978907004</v>
+        <v>0.0108474058914536</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.52796478289278</v>
+        <v>-0.0824320966326846</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L28" t="n">
-        <v>0.124972278846902</v>
+        <v>0.0196049247992935</v>
       </c>
     </row>
     <row r="29">
@@ -1478,21 +1496,21 @@
         <v>4515</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000620250933957998</v>
+        <v>-0.00177937023337358</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0317960636689187</v>
+        <v>0.0115666353334669</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.15014392888351</v>
+        <v>-8.30653212324354</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" t="n">
-        <v>0.0315745195104368</v>
+        <v>0.0108452796825276</v>
       </c>
       <c r="L29" t="n">
-        <v>0.701654884751606</v>
+        <v>6.65133285683264</v>
       </c>
     </row>
     <row r="30">
@@ -1512,13 +1530,13 @@
         <v>143</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00267284478763177</v>
+        <v>-0.000145880188868083</v>
       </c>
       <c r="G30" t="n">
-        <v>0.040824434557733</v>
+        <v>0.0203172529977707</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.574935410071788</v>
+        <v>-0.0423297413962951</v>
       </c>
       <c r="I30" s="1" t="n">
         <v>39692</v>
@@ -1546,13 +1564,13 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>0.000917551723869295</v>
+        <v>0.00243810149932368</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0474722084419535</v>
+        <v>0.0153982668526188</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.226041856388705</v>
+        <v>-0.0184549942125036</v>
       </c>
       <c r="I31" s="1" t="n">
         <v>43862</v>
@@ -1580,21 +1598,21 @@
         <v>4515</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000614706511249609</v>
+        <v>0.0000885072892771528</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0183313329363614</v>
+        <v>0.0108917430605193</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L32" t="n">
-        <v>3.1603110105459</v>
+        <v>10.0541731254635</v>
       </c>
     </row>
     <row r="33">
@@ -1614,21 +1632,21 @@
         <v>4515</v>
       </c>
       <c r="F33" t="n">
-        <v>0.000570409722766774</v>
+        <v>0.0000442105007943178</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0192795724598222</v>
+        <v>0.0124325614718848</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L33" t="n">
-        <v>8.49656694415932</v>
+        <v>25.6231683962021</v>
       </c>
     </row>
     <row r="34">
@@ -1648,21 +1666,21 @@
         <v>4515</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000680735893112593</v>
+        <v>0.000153734351268748</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0177698353056321</v>
+        <v>0.00989774521518639</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L34" t="n">
-        <v>0.000460582930751</v>
+        <v>0.0104537364947315</v>
       </c>
     </row>
     <row r="35">
@@ -1682,21 +1700,21 @@
         <v>4515</v>
       </c>
       <c r="F35" t="n">
-        <v>0.000680320092251323</v>
+        <v>0.00015251623053609</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0177699610778231</v>
+        <v>0.00989945645438926</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.528576950473443</v>
+        <v>-0.122313887313489</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L35" t="n">
-        <v>0.00116837097772216</v>
+        <v>0.0277447260494053</v>
       </c>
     </row>
     <row r="36">
@@ -1716,21 +1734,21 @@
         <v>4515</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.00132106314545028</v>
+        <v>-0.00184726236742274</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0181294029721542</v>
+        <v>0.0106584328003218</v>
       </c>
       <c r="H36" t="n">
-        <v>-6.71300507381684</v>
+        <v>-8.55755385140675</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" t="n">
-        <v>0.0177697534611809</v>
+        <v>0.00989671063913453</v>
       </c>
       <c r="L36" t="n">
-        <v>2.02394204150917</v>
+        <v>7.69672054647357</v>
       </c>
     </row>
     <row r="37">
@@ -1750,13 +1768,13 @@
         <v>143</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.000668755477129844</v>
+        <v>0.000855059820899094</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0516086445981722</v>
+        <v>0.0185981575347543</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.835895917643519</v>
+        <v>-0.0116456112114705</v>
       </c>
       <c r="I37" s="1" t="n">
         <v>39692</v>
@@ -1784,13 +1802,13 @@
         <v>59</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00353116230135348</v>
+        <v>0.00309357759226879</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0333217516794831</v>
+        <v>0.016123117157863</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.180723802802995</v>
+        <v>-0.016586722556549</v>
       </c>
       <c r="I38" s="1" t="n">
         <v>43862</v>
@@ -1818,21 +1836,21 @@
         <v>4515</v>
       </c>
       <c r="F39" t="n">
-        <v>0.000906900416826371</v>
+        <v>0.00013473880658215</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0248429145425335</v>
+        <v>0.0106892234803598</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L39" t="n">
-        <v>1.66986953078478</v>
+        <v>10.6617579782835</v>
       </c>
     </row>
     <row r="40">
@@ -1852,21 +1870,21 @@
         <v>4515</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000862603628343536</v>
+        <v>0.0000904420180993153</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0255484513481067</v>
+        <v>0.0122628979548098</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L40" t="n">
-        <v>4.55728577371331</v>
+        <v>26.9534543908585</v>
       </c>
     </row>
     <row r="41">
@@ -1886,21 +1904,21 @@
         <v>4515</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000973272412611131</v>
+        <v>0.000199524583687079</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0244348882628391</v>
+        <v>0.00966133064052844</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0000180103184551862</v>
+        <v>0.0203461977151037</v>
       </c>
     </row>
     <row r="42">
@@ -1920,21 +1938,21 @@
         <v>4515</v>
       </c>
       <c r="F42" t="n">
-        <v>0.000973199225671638</v>
+        <v>0.000197865178067756</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0244348936533635</v>
+        <v>0.00966458205115081</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.488483500073341</v>
+        <v>-0.0969705226408606</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" t="n">
-        <v>0.0244348838620387</v>
+        <v>0.00965936532696099</v>
       </c>
       <c r="L42" t="n">
-        <v>0.0000400710923272578</v>
+        <v>0.0540069043175879</v>
       </c>
     </row>
     <row r="43">
@@ -1954,20 +1972,1448 @@
         <v>4515</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.00102886923987352</v>
+        <v>-0.00180103085011774</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0247051764559909</v>
+        <v>0.0104321377356863</v>
       </c>
       <c r="H43" t="n">
-        <v>-5.37325111779614</v>
+        <v>-8.3582040250076</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" t="n">
+        <v>0.00965936532696099</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8.00024000094873</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>143</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.00173692405004033</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0600037655773047</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.761914216320698</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>59</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.00360437391869047</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0593766543117209</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.184901076210231</v>
+      </c>
+      <c r="I45" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.00131551872274189</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0319688553700037</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.24890533785161</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.00127122193425906</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0325708621645964</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.15552752538385</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.00137373208548086</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0315894131475975</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0471697982790727</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.00136550026549557</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.031613978907004</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.52796478289278</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.124972278846902</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.000620250933957998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0317960636689187</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-5.15014392888351</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" t="n">
+        <v>0.0315745195104368</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.701654884751606</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="n">
+        <v>143</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.00267284478763177</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.040824434557733</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.574935410071788</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>59</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.000917551723869295</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0474722084419535</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.226041856388705</v>
+      </c>
+      <c r="I52" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.000614706511249609</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0183313329363614</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.1603110105459</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.000570409722766774</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0192795724598222</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L54" t="n">
+        <v>8.49656694415932</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.000680735893112593</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0177698353056321</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.000460582930751</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.000680320092251323</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0177699610778231</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.528576950473443</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.00116837097772216</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.00132106314545028</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0181294029721542</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-6.71300507381684</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" t="n">
+        <v>0.0177697534611809</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.02394204150917</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" t="n">
+        <v>143</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.00265580653071438</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0258816893587691</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.443569210481156</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K58"/>
+      <c r="L58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" t="n">
+        <v>59</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.000831184477237403</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0386220238465276</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-0.243367763399513</v>
+      </c>
+      <c r="I59" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K59"/>
+      <c r="L59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.000300132055082567</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0125883369741618</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L60" t="n">
+        <v>6.93230749718272</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.000255835266599732</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.0139236567481399</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L61" t="n">
+        <v>18.2752533502508</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.000366747012457679</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0117722598048185</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.0000959594102858226</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.000366916787108538</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0117722821559868</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.149166972628565</v>
+      </c>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.000285822614863924</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-0.00163563760161732</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0123771848355655</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-7.80277632641529</v>
+      </c>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" t="n">
+        <v>0.0117722485082383</v>
+      </c>
+      <c r="L64" t="n">
+        <v>5.13866426540301</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="n">
+        <v>143</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-0.00634495437900691</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0468467284865782</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-1.13936337177743</v>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K65"/>
+      <c r="L65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="n">
+        <v>59</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.00189603239762552</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0437057350558554</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0.357708936154046</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K66"/>
+      <c r="L66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.000457592631473954</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0212385071530903</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.73586229719154</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.000413295842991119</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0221139210000307</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L68" t="n">
+        <v>6.9704535414842</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.000517870559328579</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0206855391368875</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.0610205318136251</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.000511703304458951</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0207064413049087</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0.810667123199772</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.162129439330862</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-0.00147817702522594</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0210381640802695</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-7.59473794910994</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" t="n">
+        <v>0.020672924408472</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.76675377213622</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="n">
+        <v>143</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-0.00080850778442218</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0266591556099799</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.236676515342039</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K72"/>
+      <c r="L72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" t="n">
+        <v>59</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0010890390904826</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.034586899612162</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.0956159934404295</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J73" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K73"/>
+      <c r="L73"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.000381042160821637</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0138335058163006</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5.45359157348412</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" t="s">
+        <v>18</v>
+      </c>
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.000336745372338802</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0150455485323512</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L75" t="n">
+        <v>14.6930612527761</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.000448673172354497</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.013118783917016</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.0052264044052213</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.000449859001163105</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0131199534103939</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0.0616072319806151</v>
+      </c>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.0141415180904541</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-0.00155472749587825</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.013650802977163</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-7.71426012896369</v>
+      </c>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" t="n">
+        <v>0.0131180983121479</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4.06083757217903</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="n">
+        <v>143</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-0.000668755477129844</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.0516086445981722</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.835895917643519</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>39692</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>39903</v>
+      </c>
+      <c r="K79"/>
+      <c r="L79"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" t="n">
+        <v>59</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.00353116230135348</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0333217516794831</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.180723802802995</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="K80"/>
+      <c r="L80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.000906900416826371</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0248429145425335</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" t="n">
         <v>0.0244348838620387</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L81" t="n">
+        <v>1.66986953078478</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.000862603628343536</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0255484513481067</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4.55728577371331</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.000973272412611131</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0244348882628391</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.0000180103184551862</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.000973199225671638</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0244348936533635</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.488483500073341</v>
+      </c>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.0000400710923272578</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4515</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-0.00102886923987352</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0247051764559909</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-5.37325111779614</v>
+      </c>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" t="n">
+        <v>0.0244348838620387</v>
+      </c>
+      <c r="L85" t="n">
         <v>1.1061750711741</v>
       </c>
     </row>
@@ -1990,16 +3436,16 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -2010,13 +3456,13 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0287032721053359</v>
+        <v>0.0275044669296046</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.126414368878323</v>
+        <v>-0.133774763054744</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -2030,13 +3476,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0339078955736443</v>
+        <v>0.0296678688524375</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.436763186145276</v>
+        <v>-0.398495605213219</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -2050,16 +3496,16 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>0.016789867869449</v>
+        <v>0.0146851339950314</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.39673848505614</v>
+        <v>-7.83968404538109</v>
       </c>
       <c r="F4" t="n">
-        <v>8.06269664673822</v>
+        <v>7.80678013665365</v>
       </c>
     </row>
     <row r="5">
@@ -2070,16 +3516,16 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0170222126831937</v>
+        <v>0.014914989918467</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.497492666111511</v>
+        <v>-0.429493923980447</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6198221788595</v>
+        <v>10.2272453733501</v>
       </c>
     </row>
     <row r="6">
@@ -2090,16 +3536,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0183291187815318</v>
+        <v>0.0162836484725862</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.564159332778177</v>
+        <v>-0.479493923980447</v>
       </c>
       <c r="F6" t="n">
-        <v>25.8500082410277</v>
+        <v>25.3257041270136</v>
       </c>
     </row>
     <row r="7">
@@ -2110,16 +3556,16 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0161457183757358</v>
+        <v>0.0140153927855714</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.399119991836927</v>
+        <v>-0.355178367248472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0164924466629534</v>
+        <v>0.016523354956486</v>
       </c>
     </row>
     <row r="8">
@@ -2130,16 +3576,16 @@
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0161507920007042</v>
+        <v>0.0140202027380506</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.400747317562343</v>
+        <v>-0.355862810516496</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0438298885422007</v>
+        <v>0.0439208290927164</v>
       </c>
     </row>
   </sheetData>
@@ -2164,25 +3610,25 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -2196,7 +3642,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -2222,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E3"/>
       <c r="F3"/>
@@ -2248,7 +3694,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4"/>
       <c r="F4"/>
@@ -2274,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E5"/>
       <c r="F5"/>
@@ -2300,7 +3746,7 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E6"/>
       <c r="F6"/>
@@ -2326,7 +3772,7 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -2352,7 +3798,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8"/>
       <c r="F8"/>
@@ -2378,7 +3824,7 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -2404,7 +3850,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -2430,7 +3876,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -2456,7 +3902,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -2482,7 +3928,7 @@
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -2508,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -2534,7 +3980,7 @@
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -2560,7 +4006,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -2586,7 +4032,7 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -2612,7 +4058,7 @@
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -2638,7 +4084,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -2664,7 +4110,7 @@
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -2690,7 +4136,7 @@
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -2716,7 +4162,7 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -2742,7 +4188,7 @@
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -2768,7 +4214,7 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -2794,7 +4240,7 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -2820,7 +4266,7 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -2846,7 +4292,7 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -2872,7 +4318,7 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -2898,7 +4344,7 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
@@ -2924,7 +4370,7 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E30"/>
       <c r="F30"/>
@@ -2950,7 +4396,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E31"/>
       <c r="F31"/>
@@ -2976,7 +4422,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E32"/>
       <c r="F32"/>
@@ -3002,7 +4448,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E33"/>
       <c r="F33"/>
@@ -3028,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E34"/>
       <c r="F34"/>
@@ -3054,7 +4500,7 @@
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E35"/>
       <c r="F35"/>
@@ -3080,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E36"/>
       <c r="F36"/>
@@ -3106,7 +4552,7 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E37"/>
       <c r="F37"/>
@@ -3132,7 +4578,7 @@
         <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E38"/>
       <c r="F38"/>
@@ -3158,7 +4604,7 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E39"/>
       <c r="F39"/>
@@ -3184,7 +4630,7 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E40"/>
       <c r="F40"/>
@@ -3210,7 +4656,7 @@
         <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E41"/>
       <c r="F41"/>
@@ -3236,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E42"/>
       <c r="F42"/>
@@ -3262,7 +4708,7 @@
         <v>21</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E43"/>
       <c r="F43"/>
@@ -3288,7 +4734,7 @@
         <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E44"/>
       <c r="F44"/>
@@ -3314,7 +4760,7 @@
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E45"/>
       <c r="F45"/>
@@ -3340,7 +4786,7 @@
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E46"/>
       <c r="F46"/>
@@ -3366,7 +4812,7 @@
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E47"/>
       <c r="F47"/>
@@ -3392,7 +4838,7 @@
         <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E48"/>
       <c r="F48"/>
@@ -3418,7 +4864,7 @@
         <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E49"/>
       <c r="F49"/>
@@ -3444,7 +4890,7 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E50"/>
       <c r="F50"/>
@@ -3470,7 +4916,7 @@
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E51"/>
       <c r="F51"/>
@@ -3496,7 +4942,7 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E52"/>
       <c r="F52"/>
@@ -3522,7 +4968,7 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E53"/>
       <c r="F53"/>
@@ -3548,7 +4994,7 @@
         <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E54"/>
       <c r="F54"/>
@@ -3574,7 +5020,7 @@
         <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E55"/>
       <c r="F55"/>
@@ -3600,7 +5046,7 @@
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E56"/>
       <c r="F56"/>
@@ -3626,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E57"/>
       <c r="F57"/>
@@ -3652,15 +5098,15 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58" t="n">
-        <v>0.000514871623255834</v>
+        <v>0.000204477549479361</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0163596111610899</v>
+        <v>0.0107627178522824</v>
       </c>
       <c r="I58"/>
       <c r="J58" t="n">
@@ -3678,15 +5124,15 @@
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59" t="n">
-        <v>0.000515581267172311</v>
+        <v>0.000204794760109707</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0162963363513796</v>
+        <v>0.0108327762813775</v>
       </c>
       <c r="I59"/>
       <c r="J59" t="n">
@@ -3704,15 +5150,15 @@
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60" t="n">
-        <v>0.000510962126007053</v>
+        <v>0.000203998056045439</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0163684629636016</v>
+        <v>0.0107727702070823</v>
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
@@ -3730,15 +5176,15 @@
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61" t="n">
-        <v>0.000518031264874855</v>
+        <v>0.000206145114469156</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0164481290485706</v>
+        <v>0.0108343877162128</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
@@ -3756,15 +5202,15 @@
         <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="n">
-        <v>0.000260188711618463</v>
+        <v>0.0000853300212224403</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0121258593927602</v>
+        <v>0.00716451993225171</v>
       </c>
       <c r="I62"/>
       <c r="J62" t="n">
@@ -3782,15 +5228,15 @@
         <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63" t="n">
-        <v>0.000259065133200994</v>
+        <v>0.0000891594849130703</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0121220291895014</v>
+        <v>0.00725702641978685</v>
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
@@ -3808,15 +5254,15 @@
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64" t="n">
-        <v>0.000259318123429544</v>
+        <v>0.0000890256594307911</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0121009912602446</v>
+        <v>0.00725832853819443</v>
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
@@ -3834,15 +5280,15 @@
         <v>16</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65" t="n">
-        <v>0.000256894238556425</v>
+        <v>0.0000877492029714677</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0120941920059368</v>
+        <v>0.00724297882010669</v>
       </c>
       <c r="I65"/>
       <c r="J65" t="n">
@@ -3860,15 +5306,15 @@
         <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66" t="n">
-        <v>0.000162586279202364</v>
+        <v>0.0000975295196124737</v>
       </c>
       <c r="H66" t="n">
-        <v>0.00770558800555955</v>
+        <v>0.00438457969549617</v>
       </c>
       <c r="I66"/>
       <c r="J66" t="n">
@@ -3886,15 +5332,15 @@
         <v>19</v>
       </c>
       <c r="D67" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67" t="n">
-        <v>1213.74285915808</v>
+        <v>0.0000978275673492674</v>
       </c>
       <c r="H67" t="n">
-        <v>7.76426077312173</v>
+        <v>0.00440253615086676</v>
       </c>
       <c r="I67"/>
       <c r="J67" t="n">
@@ -3912,15 +5358,15 @@
         <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68" t="n">
-        <v>0.000162611247765157</v>
+        <v>0.0000974489342915572</v>
       </c>
       <c r="H68" t="n">
-        <v>0.00772844257661858</v>
+        <v>0.0043908045303298</v>
       </c>
       <c r="I68"/>
       <c r="J68" t="n">
@@ -3938,15 +5384,15 @@
         <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69" t="n">
-        <v>0.000164737133869094</v>
+        <v>0.0000975890001536484</v>
       </c>
       <c r="H69" t="n">
-        <v>0.00778915638572289</v>
+        <v>0.00438319191959264</v>
       </c>
       <c r="I69"/>
       <c r="J69" t="n">
@@ -3964,15 +5410,15 @@
         <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70" t="n">
-        <v>0.000281960284267101</v>
+        <v>0.000215340147769813</v>
       </c>
       <c r="H70" t="n">
-        <v>0.00783862267199919</v>
+        <v>0.00452966053124237</v>
       </c>
       <c r="I70"/>
       <c r="J70" t="n">
@@ -3990,15 +5436,15 @@
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71" t="n">
-        <v>1305.59381848702</v>
+        <v>0.000215556168251757</v>
       </c>
       <c r="H71" t="n">
-        <v>8.42261251279047</v>
+        <v>0.00453570776047664</v>
       </c>
       <c r="I71"/>
       <c r="J71" t="n">
@@ -4016,15 +5462,15 @@
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72" t="n">
-        <v>0.000282410295172309</v>
+        <v>0.000215374002673483</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0078770578332271</v>
+        <v>0.00453313031474187</v>
       </c>
       <c r="I72"/>
       <c r="J72" t="n">
@@ -4042,15 +5488,15 @@
         <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73" t="n">
-        <v>0.000280795607591805</v>
+        <v>0.000215445593774553</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00787537753172</v>
+        <v>0.00453283735310416</v>
       </c>
       <c r="I73"/>
       <c r="J73" t="n">
@@ -4068,15 +5514,15 @@
         <v>23</v>
       </c>
       <c r="D74" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74" t="n">
-        <v>0.0000940433060653965</v>
+        <v>0.0000318118942234263</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00750967045408458</v>
+        <v>0.00415521407984866</v>
       </c>
       <c r="I74"/>
       <c r="J74" t="n">
@@ -4094,15 +5540,15 @@
         <v>23</v>
       </c>
       <c r="D75" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75" t="n">
-        <v>1309.0573790592</v>
+        <v>0.0000321306949171509</v>
       </c>
       <c r="H75" t="n">
-        <v>8.50789169517494</v>
+        <v>0.00419317456169534</v>
       </c>
       <c r="I75"/>
       <c r="J75" t="n">
@@ -4120,15 +5566,15 @@
         <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76" t="n">
-        <v>0.0000938119979712337</v>
+        <v>0.0000318888667872478</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00752160542967396</v>
+        <v>0.00417427107221481</v>
       </c>
       <c r="I76"/>
       <c r="J76" t="n">
@@ -4146,15 +5592,15 @@
         <v>23</v>
       </c>
       <c r="D77" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77" t="n">
-        <v>0.0000948789136557377</v>
+        <v>0.0000320279226998038</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00758009648366493</v>
+        <v>0.00417352911220678</v>
       </c>
       <c r="I77"/>
       <c r="J77" t="n">
@@ -4172,15 +5618,15 @@
         <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78" t="n">
-        <v>0.0000937679823806852</v>
+        <v>0.0000317811801026438</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00748359730946349</v>
+        <v>0.00415939282327691</v>
       </c>
       <c r="I78"/>
       <c r="J78" t="n">
@@ -4198,15 +5644,15 @@
         <v>25</v>
       </c>
       <c r="D79" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79" t="n">
-        <v>988.789718931182</v>
+        <v>0.0000323496780513232</v>
       </c>
       <c r="H79" t="n">
-        <v>6.80298988814467</v>
+        <v>0.00420027660038074</v>
       </c>
       <c r="I79"/>
       <c r="J79" t="n">
@@ -4224,15 +5670,15 @@
         <v>25</v>
       </c>
       <c r="D80" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80" t="n">
-        <v>0.0000940730250249333</v>
+        <v>0.0000319862418180184</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00750398603015387</v>
+        <v>0.00416413792655207</v>
       </c>
       <c r="I80"/>
       <c r="J80" t="n">
@@ -4250,15 +5696,15 @@
         <v>25</v>
       </c>
       <c r="D81" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81" t="n">
-        <v>0.0000950396415045482</v>
+        <v>0.0000319391744816449</v>
       </c>
       <c r="H81" t="n">
-        <v>0.00757004383527859</v>
+        <v>0.00417033730399493</v>
       </c>
       <c r="I81"/>
       <c r="J81" t="n">
@@ -4276,15 +5722,15 @@
         <v>27</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82" t="n">
-        <v>0.000206902778904061</v>
+        <v>0.000129757594988749</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0119538641845173</v>
+        <v>0.01018812056695</v>
       </c>
       <c r="I82"/>
       <c r="J82" t="n">
@@ -4302,15 +5748,15 @@
         <v>27</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83" t="n">
-        <v>0.000213787473182652</v>
+        <v>0.000129119339041479</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0121913586574552</v>
+        <v>0.0101499013079248</v>
       </c>
       <c r="I83"/>
       <c r="J83" t="n">
@@ -4328,15 +5774,15 @@
         <v>27</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84" t="n">
-        <v>0.000213071141908161</v>
+        <v>0.000130272798432306</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0121255161008157</v>
+        <v>0.010201563543119</v>
       </c>
       <c r="I84"/>
       <c r="J84" t="n">
@@ -4354,15 +5800,15 @@
         <v>27</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85" t="n">
-        <v>0.000216909117864017</v>
+        <v>0.000128318153841272</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0123069544453788</v>
+        <v>0.0101167248579192</v>
       </c>
       <c r="I85"/>
       <c r="J85" t="n">
@@ -4380,15 +5826,15 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86" t="n">
-        <v>0.00356709287518203</v>
+        <v>0.000518065622707725</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0492007849855877</v>
+        <v>0.0164423010105302</v>
       </c>
       <c r="I86"/>
       <c r="J86" t="n">
@@ -4406,15 +5852,15 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87" t="n">
-        <v>0.00361467683447758</v>
+        <v>0.000518633117452987</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0496728683521829</v>
+        <v>0.0165357997451221</v>
       </c>
       <c r="I87"/>
       <c r="J87" t="n">
@@ -4432,15 +5878,15 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88" t="n">
-        <v>0.00359154994380956</v>
+        <v>0.000515766381516243</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0491321379267671</v>
+        <v>0.0163978440251566</v>
       </c>
       <c r="I88"/>
       <c r="J88" t="n">
@@ -4458,15 +5904,15 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89" t="n">
-        <v>0.00357367400960657</v>
+        <v>0.000504361550207652</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0494550331160037</v>
+        <v>0.016299066004747</v>
       </c>
       <c r="I89"/>
       <c r="J89" t="n">
@@ -4484,15 +5930,15 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90" t="n">
-        <v>0.00347343413176563</v>
+        <v>0.000258982380856436</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0455677016188068</v>
+        <v>0.0120424019258245</v>
       </c>
       <c r="I90"/>
       <c r="J90" t="n">
@@ -4510,15 +5956,15 @@
         <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>0.00349043678651564</v>
+        <v>0.000257514705647565</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0456121639974128</v>
+        <v>0.012092621213791</v>
       </c>
       <c r="I91"/>
       <c r="J91" t="n">
@@ -4536,15 +5982,15 @@
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>0.0034556929213981</v>
+        <v>0.000255740042688118</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0452045464056649</v>
+        <v>0.0121311325837106</v>
       </c>
       <c r="I92"/>
       <c r="J92" t="n">
@@ -4562,15 +6008,15 @@
         <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>0.00350824349449575</v>
+        <v>0.000254324321676988</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0455409538236593</v>
+        <v>0.0121304687938613</v>
       </c>
       <c r="I93"/>
       <c r="J93" t="n">
@@ -4588,15 +6034,15 @@
         <v>19</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>0.00126524291543443</v>
+        <v>0.000162196838138077</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0253375134652221</v>
+        <v>0.00769909727074466</v>
       </c>
       <c r="I94"/>
       <c r="J94" t="n">
@@ -4614,15 +6060,15 @@
         <v>19</v>
       </c>
       <c r="D95" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>0.00127711952409654</v>
+        <v>1195.97087214223</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0254814280930115</v>
+        <v>7.67863105524868</v>
       </c>
       <c r="I95"/>
       <c r="J95" t="n">
@@ -4640,15 +6086,15 @@
         <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>0.00126738530947306</v>
+        <v>0.000162983900177599</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0253654245953917</v>
+        <v>0.00775958032400913</v>
       </c>
       <c r="I96"/>
       <c r="J96" t="n">
@@ -4666,15 +6112,15 @@
         <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97" t="n">
-        <v>0.00126866914403079</v>
+        <v>0.000162806779451155</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0253719531646511</v>
+        <v>0.007793787550423</v>
       </c>
       <c r="I97"/>
       <c r="J97" t="n">
@@ -4692,15 +6138,15 @@
         <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98" t="n">
-        <v>0.00139699309507506</v>
+        <v>0.000282111586509824</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0255469344955213</v>
+        <v>0.00786693799790825</v>
       </c>
       <c r="I98"/>
       <c r="J98" t="n">
@@ -4718,15 +6164,15 @@
         <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99" t="n">
-        <v>0.00139789893744094</v>
+        <v>1106.99308339223</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0255180572916646</v>
+        <v>7.49552139523906</v>
       </c>
       <c r="I99"/>
       <c r="J99" t="n">
@@ -4744,15 +6190,15 @@
         <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100" t="n">
-        <v>0.00139856072290935</v>
+        <v>0.000280948337007677</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0255102068619735</v>
+        <v>0.00787600991726175</v>
       </c>
       <c r="I100"/>
       <c r="J100" t="n">
@@ -4770,15 +6216,15 @@
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101" t="n">
-        <v>0.0013970158963728</v>
+        <v>0.000285168819193373</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0254483740475441</v>
+        <v>0.0079517220472381</v>
       </c>
       <c r="I101"/>
       <c r="J101" t="n">
@@ -4796,15 +6242,15 @@
         <v>23</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102" t="n">
-        <v>0.00118888995517411</v>
+        <v>0.0000936553758320833</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0251469497211458</v>
+        <v>0.00747803777491874</v>
       </c>
       <c r="I102"/>
       <c r="J102" t="n">
@@ -4822,15 +6268,15 @@
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103" t="n">
-        <v>0.0011922663691207</v>
+        <v>1189.5793131102</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0252102347187435</v>
+        <v>7.80984690026167</v>
       </c>
       <c r="I103"/>
       <c r="J103" t="n">
@@ -4848,15 +6294,15 @@
         <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104" t="n">
-        <v>0.00119073380143728</v>
+        <v>0.0000944596043489018</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0251662408435151</v>
+        <v>0.00755419216415687</v>
       </c>
       <c r="I104"/>
       <c r="J104" t="n">
@@ -4874,15 +6320,15 @@
         <v>23</v>
       </c>
       <c r="D105" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105" t="n">
-        <v>0.00119554228152484</v>
+        <v>0.0000951687785575479</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0252196956628167</v>
+        <v>0.00755162652088153</v>
       </c>
       <c r="I105"/>
       <c r="J105" t="n">
@@ -4900,15 +6346,15 @@
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106" t="n">
-        <v>0.00119266728566019</v>
+        <v>0.0000940274343706836</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0251880273764967</v>
+        <v>0.00750416366650368</v>
       </c>
       <c r="I106"/>
       <c r="J106" t="n">
@@ -4926,15 +6372,15 @@
         <v>25</v>
       </c>
       <c r="D107" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107" t="n">
-        <v>0.00119907927963404</v>
+        <v>1076.3627939052</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0252650970235112</v>
+        <v>7.32351020769527</v>
       </c>
       <c r="I107"/>
       <c r="J107" t="n">
@@ -4952,15 +6398,15 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108" t="n">
-        <v>0.00119286974617785</v>
+        <v>0.0000946782346434687</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0251750369276858</v>
+        <v>0.00755218117541335</v>
       </c>
       <c r="I108"/>
       <c r="J108" t="n">
@@ -4978,15 +6424,15 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109" t="n">
-        <v>0.00119224520621769</v>
+        <v>0.0000950628782447814</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0251990886329344</v>
+        <v>0.0075672084287267</v>
       </c>
       <c r="I109"/>
       <c r="J109" t="n">
@@ -5004,15 +6450,15 @@
         <v>27</v>
       </c>
       <c r="D110" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110" t="n">
-        <v>0.00105190919406783</v>
+        <v>0.000207193015401097</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0226437487805914</v>
+        <v>0.0119257266313408</v>
       </c>
       <c r="I110"/>
       <c r="J110" t="n">
@@ -5030,15 +6476,15 @@
         <v>27</v>
       </c>
       <c r="D111" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>0.00104880333000164</v>
+        <v>0.000212948608541644</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0225643052973476</v>
+        <v>0.0121338185861415</v>
       </c>
       <c r="I111"/>
       <c r="J111" t="n">
@@ -5056,15 +6502,15 @@
         <v>27</v>
       </c>
       <c r="D112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112" t="n">
-        <v>0.00105118426391401</v>
+        <v>0.000213542021951181</v>
       </c>
       <c r="H112" t="n">
-        <v>0.0226355189916163</v>
+        <v>0.0121770159417138</v>
       </c>
       <c r="I112"/>
       <c r="J112" t="n">
@@ -5082,15 +6528,15 @@
         <v>27</v>
       </c>
       <c r="D113" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113" t="n">
-        <v>0.00105929170646389</v>
+        <v>0.000216089532220706</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0227374738466541</v>
+        <v>0.0122794969145519</v>
       </c>
       <c r="I113"/>
       <c r="J113" t="n">
@@ -5108,15 +6554,15 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114" t="n">
-        <v>0.00166657826440175</v>
+        <v>0.000410879616765388</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0306961695852543</v>
+        <v>0.0149890258624776</v>
       </c>
       <c r="I114"/>
       <c r="J114" t="n">
@@ -5134,15 +6580,15 @@
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115" t="n">
-        <v>0.00167355487426778</v>
+        <v>0.000411599072831447</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0308007466693071</v>
+        <v>0.0150412253941229</v>
       </c>
       <c r="I115"/>
       <c r="J115" t="n">
@@ -5160,15 +6606,15 @@
         <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116" t="n">
-        <v>0.0016679229279071</v>
+        <v>0.000415052893191876</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0306488592878618</v>
+        <v>0.0150508867393071</v>
       </c>
       <c r="I116"/>
       <c r="J116" t="n">
@@ -5186,15 +6632,15 @@
         <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117" t="n">
-        <v>0.00166336609497293</v>
+        <v>0.000412926602546874</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0306152304432491</v>
+        <v>0.0150110225971682</v>
       </c>
       <c r="I117"/>
       <c r="J117" t="n">
@@ -5212,15 +6658,15 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>0.0022097436548237</v>
+        <v>0.000237877700866366</v>
       </c>
       <c r="H118" t="n">
-        <v>0.035050748939306</v>
+        <v>0.0110942590815885</v>
       </c>
       <c r="I118"/>
       <c r="J118" t="n">
@@ -5238,15 +6684,15 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>0.00221710847752892</v>
+        <v>0.000236789389916103</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0350879420045787</v>
+        <v>0.0109503832765895</v>
       </c>
       <c r="I119"/>
       <c r="J119" t="n">
@@ -5264,15 +6710,15 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120" t="n">
-        <v>0.00223248760201288</v>
+        <v>0.000239333093598082</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0352798684248624</v>
+        <v>0.0111351893555681</v>
       </c>
       <c r="I120"/>
       <c r="J120" t="n">
@@ -5290,15 +6736,15 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121" t="n">
-        <v>0.00220302886527406</v>
+        <v>0.000237144251026504</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0349619618279106</v>
+        <v>0.0111387812566376</v>
       </c>
       <c r="I121"/>
       <c r="J121" t="n">
@@ -5316,15 +6762,15 @@
         <v>19</v>
       </c>
       <c r="D122" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122" t="n">
-        <v>0.00044022273608923</v>
+        <v>0.000146565375608219</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0138252451802776</v>
+        <v>0.00690848672760358</v>
       </c>
       <c r="I122"/>
       <c r="J122" t="n">
@@ -5342,15 +6788,15 @@
         <v>19</v>
       </c>
       <c r="D123" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123" t="n">
-        <v>0.000439897445163341</v>
+        <v>0.000146622517705153</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0138770372669694</v>
+        <v>0.00693661302704114</v>
       </c>
       <c r="I123"/>
       <c r="J123" t="n">
@@ -5368,15 +6814,15 @@
         <v>19</v>
       </c>
       <c r="D124" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124" t="n">
-        <v>0.000440413564673099</v>
+        <v>0.000145971960039479</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0138447314947511</v>
+        <v>0.0069078270849286</v>
       </c>
       <c r="I124"/>
       <c r="J124" t="n">
@@ -5394,15 +6840,15 @@
         <v>19</v>
       </c>
       <c r="D125" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125" t="n">
-        <v>0.000438793509147836</v>
+        <v>0.000146680705587266</v>
       </c>
       <c r="H125" t="n">
-        <v>0.0138041252317179</v>
+        <v>0.0069548721591661</v>
       </c>
       <c r="I125"/>
       <c r="J125" t="n">
@@ -5420,15 +6866,15 @@
         <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126" t="n">
-        <v>0.000561507988559075</v>
+        <v>0.000264993539013037</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0140052168487452</v>
+        <v>0.00704535503251569</v>
       </c>
       <c r="I126"/>
       <c r="J126" t="n">
@@ -5446,15 +6892,15 @@
         <v>21</v>
       </c>
       <c r="D127" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127" t="n">
-        <v>0.000561454361354745</v>
+        <v>0.000268411179586345</v>
       </c>
       <c r="H127" t="n">
-        <v>0.014025753891243</v>
+        <v>0.00713452803021518</v>
       </c>
       <c r="I127"/>
       <c r="J127" t="n">
@@ -5472,15 +6918,15 @@
         <v>21</v>
       </c>
       <c r="D128" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128" t="n">
-        <v>0.000557896256776269</v>
+        <v>0.000265554584344468</v>
       </c>
       <c r="H128" t="n">
-        <v>0.0139729587331149</v>
+        <v>0.00704284804852973</v>
       </c>
       <c r="I128"/>
       <c r="J128" t="n">
@@ -5498,15 +6944,15 @@
         <v>21</v>
       </c>
       <c r="D129" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129" t="n">
-        <v>0.000556402491690548</v>
+        <v>0.000266822304619512</v>
       </c>
       <c r="H129" t="n">
-        <v>0.013994148780252</v>
+        <v>0.00709565252580932</v>
       </c>
       <c r="I129"/>
       <c r="J129" t="n">
@@ -5524,15 +6970,15 @@
         <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130" t="n">
-        <v>0.000372328070510838</v>
+        <v>0.0000774770248919929</v>
       </c>
       <c r="H130" t="n">
-        <v>0.013628839874028</v>
+        <v>0.00668935270351218</v>
       </c>
       <c r="I130"/>
       <c r="J130" t="n">
@@ -5550,15 +6996,15 @@
         <v>23</v>
       </c>
       <c r="D131" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131" t="n">
-        <v>0.000372776889516162</v>
+        <v>0.0000771819862423975</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0136249609336273</v>
+        <v>0.00668262428647748</v>
       </c>
       <c r="I131"/>
       <c r="J131" t="n">
@@ -5576,15 +7022,15 @@
         <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132" t="n">
-        <v>0.000373195497273434</v>
+        <v>0.0000772277795077095</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0136120071781038</v>
+        <v>0.00668506939996752</v>
       </c>
       <c r="I132"/>
       <c r="J132" t="n">
@@ -5602,15 +7048,15 @@
         <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133" t="n">
-        <v>0.000373069837619335</v>
+        <v>0.0000792612845702449</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0136225126161665</v>
+        <v>0.00680881716352029</v>
       </c>
       <c r="I133"/>
       <c r="J133" t="n">
@@ -5628,15 +7074,15 @@
         <v>25</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134" t="n">
-        <v>0.000372794714475328</v>
+        <v>0.0000771812323997239</v>
       </c>
       <c r="H134" t="n">
-        <v>0.0136085662090615</v>
+        <v>0.00666514081081627</v>
       </c>
       <c r="I134"/>
       <c r="J134" t="n">
@@ -5654,15 +7100,15 @@
         <v>25</v>
       </c>
       <c r="D135" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135" t="n">
-        <v>0.000375706967440677</v>
+        <v>0.0000780816290306126</v>
       </c>
       <c r="H135" t="n">
-        <v>0.0136523246886673</v>
+        <v>0.00672149128104696</v>
       </c>
       <c r="I135"/>
       <c r="J135" t="n">
@@ -5680,15 +7126,15 @@
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136" t="n">
-        <v>0.000371812999795075</v>
+        <v>0.0000775542388248838</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0136239618090333</v>
+        <v>0.00671836699459022</v>
       </c>
       <c r="I136"/>
       <c r="J136" t="n">
@@ -5706,15 +7152,15 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137" t="n">
-        <v>0.000373071949175921</v>
+        <v>0.0000789809024583931</v>
       </c>
       <c r="H137" t="n">
-        <v>0.013642436151581</v>
+        <v>0.00677917635642502</v>
       </c>
       <c r="I137"/>
       <c r="J137" t="n">
@@ -5732,15 +7178,15 @@
         <v>27</v>
       </c>
       <c r="D138" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138" t="n">
-        <v>0.000426298441099335</v>
+        <v>0.000196817960842603</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0143954509505574</v>
+        <v>0.0117161968411401</v>
       </c>
       <c r="I138"/>
       <c r="J138" t="n">
@@ -5758,15 +7204,15 @@
         <v>27</v>
       </c>
       <c r="D139" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139" t="n">
-        <v>0.000426961747789713</v>
+        <v>0.000200140920957103</v>
       </c>
       <c r="H139" t="n">
-        <v>0.0144382224623116</v>
+        <v>0.0118206775293174</v>
       </c>
       <c r="I139"/>
       <c r="J139" t="n">
@@ -5784,15 +7230,15 @@
         <v>27</v>
       </c>
       <c r="D140" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140" t="n">
-        <v>0.00042556844247673</v>
+        <v>0.000201710053226512</v>
       </c>
       <c r="H140" t="n">
-        <v>0.0143859614426913</v>
+        <v>0.0118925919330219</v>
       </c>
       <c r="I140"/>
       <c r="J140" t="n">
@@ -5810,15 +7256,15 @@
         <v>27</v>
       </c>
       <c r="D141" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141" t="n">
-        <v>0.000426453714080303</v>
+        <v>0.000203509153149215</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0143987429518154</v>
+        <v>0.0119427732974345</v>
       </c>
       <c r="I141"/>
       <c r="J141" t="n">
@@ -5836,15 +7282,15 @@
         <v>14</v>
       </c>
       <c r="D142" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142" t="n">
-        <v>0.00266189274448004</v>
+        <v>0.00034497170288116</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0395332494639327</v>
+        <v>0.0134813186192203</v>
       </c>
       <c r="I142"/>
       <c r="J142" t="n">
@@ -5862,15 +7308,15 @@
         <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143" t="n">
-        <v>0.00264407450488645</v>
+        <v>0.000343018680562633</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0395308620255686</v>
+        <v>0.0134510178732504</v>
       </c>
       <c r="I143"/>
       <c r="J143" t="n">
@@ -5888,15 +7334,15 @@
         <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144" t="n">
-        <v>0.00264094073260641</v>
+        <v>0.000343970465595456</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0395708532395442</v>
+        <v>0.013499658571087</v>
       </c>
       <c r="I144"/>
       <c r="J144" t="n">
@@ -5914,15 +7360,15 @@
         <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145" t="n">
-        <v>0.00264900354608587</v>
+        <v>0.000343310658705423</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0397517171495199</v>
+        <v>0.013412627825418</v>
       </c>
       <c r="I145"/>
       <c r="J145" t="n">
@@ -5940,15 +7386,15 @@
         <v>16</v>
       </c>
       <c r="D146" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146" t="n">
-        <v>0.00109660996556027</v>
+        <v>0.000263811707142936</v>
       </c>
       <c r="H146" t="n">
-        <v>0.0250020115801956</v>
+        <v>0.0122601584242954</v>
       </c>
       <c r="I146"/>
       <c r="J146" t="n">
@@ -5966,15 +7412,15 @@
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147" t="n">
-        <v>0.00109240580509464</v>
+        <v>0.00026972161988931</v>
       </c>
       <c r="H147" t="n">
-        <v>0.0251838339596461</v>
+        <v>0.0123442885350847</v>
       </c>
       <c r="I147"/>
       <c r="J147" t="n">
@@ -5992,15 +7438,15 @@
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148" t="n">
-        <v>0.00110657037146525</v>
+        <v>0.000263347463835664</v>
       </c>
       <c r="H148" t="n">
-        <v>0.025247114266781</v>
+        <v>0.0121160750185186</v>
       </c>
       <c r="I148"/>
       <c r="J148" t="n">
@@ -6018,15 +7464,15 @@
         <v>16</v>
       </c>
       <c r="D149" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149" t="n">
-        <v>0.00109186411368117</v>
+        <v>0.000265659920104038</v>
       </c>
       <c r="H149" t="n">
-        <v>0.0250789892918997</v>
+        <v>0.0122712797486374</v>
       </c>
       <c r="I149"/>
       <c r="J149" t="n">
@@ -6044,15 +7490,15 @@
         <v>19</v>
       </c>
       <c r="D150" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150" t="n">
-        <v>0.00058163298147872</v>
+        <v>0.000143157849761406</v>
       </c>
       <c r="H150" t="n">
-        <v>0.016436389149377</v>
+        <v>0.00672001805746283</v>
       </c>
       <c r="I150"/>
       <c r="J150" t="n">
@@ -6070,15 +7516,15 @@
         <v>19</v>
       </c>
       <c r="D151" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151" t="n">
-        <v>0.000581864447813023</v>
+        <v>0.000142852599289543</v>
       </c>
       <c r="H151" t="n">
-        <v>0.016404261896359</v>
+        <v>0.0067601891238118</v>
       </c>
       <c r="I151"/>
       <c r="J151" t="n">
@@ -6096,15 +7542,15 @@
         <v>19</v>
       </c>
       <c r="D152" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152" t="n">
-        <v>0.000584543883198312</v>
+        <v>0.000142161107529618</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0163803862295117</v>
+        <v>0.00672252165740435</v>
       </c>
       <c r="I152"/>
       <c r="J152" t="n">
@@ -6122,15 +7568,15 @@
         <v>19</v>
       </c>
       <c r="D153" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153" t="n">
-        <v>0.000581818645006164</v>
+        <v>0.000143484591449859</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0164240756376304</v>
+        <v>0.00677893871264257</v>
       </c>
       <c r="I153"/>
       <c r="J153" t="n">
@@ -6148,15 +7594,15 @@
         <v>21</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154" t="n">
-        <v>0.000704502166220318</v>
+        <v>0.00026272403043062</v>
       </c>
       <c r="H154" t="n">
-        <v>0.0165653600492239</v>
+        <v>0.00688869919008294</v>
       </c>
       <c r="I154"/>
       <c r="J154" t="n">
@@ -6174,15 +7620,15 @@
         <v>21</v>
       </c>
       <c r="D155" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155" t="n">
-        <v>0.000700754734122636</v>
+        <v>0.000261497324333154</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0165200377477486</v>
+        <v>0.00691872013168776</v>
       </c>
       <c r="I155"/>
       <c r="J155" t="n">
@@ -6200,15 +7646,15 @@
         <v>21</v>
       </c>
       <c r="D156" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156" t="n">
-        <v>0.000702709578892673</v>
+        <v>0.000263868327505296</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0165307045727206</v>
+        <v>0.00687864889401414</v>
       </c>
       <c r="I156"/>
       <c r="J156" t="n">
@@ -6226,15 +7672,15 @@
         <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157" t="n">
-        <v>0.000704768889545307</v>
+        <v>0.000264013140884187</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0165235072709543</v>
+        <v>0.00692848099922221</v>
       </c>
       <c r="I157"/>
       <c r="J157" t="n">
@@ -6252,15 +7698,15 @@
         <v>23</v>
       </c>
       <c r="D158" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158" t="n">
-        <v>0.000514879860652079</v>
+        <v>0.0000734338823940795</v>
       </c>
       <c r="H158" t="n">
-        <v>0.016186575928726</v>
+        <v>0.00653564485904514</v>
       </c>
       <c r="I158"/>
       <c r="J158" t="n">
@@ -6278,15 +7724,15 @@
         <v>23</v>
       </c>
       <c r="D159" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159" t="n">
-        <v>0.0005174780349884</v>
+        <v>0.00007391798020678</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0161996287580614</v>
+        <v>0.00655684348846129</v>
       </c>
       <c r="I159"/>
       <c r="J159" t="n">
@@ -6304,15 +7750,15 @@
         <v>23</v>
       </c>
       <c r="D160" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160" t="n">
-        <v>0.000515251300566603</v>
+        <v>0.0000732985981708617</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0161738179102516</v>
+        <v>0.00653937536792915</v>
       </c>
       <c r="I160"/>
       <c r="J160" t="n">
@@ -6330,15 +7776,15 @@
         <v>23</v>
       </c>
       <c r="D161" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161" t="n">
-        <v>0.00051515569079851</v>
+        <v>0.0000734264303983529</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0162050688203587</v>
+        <v>0.00652336812434081</v>
       </c>
       <c r="I161"/>
       <c r="J161" t="n">
@@ -6356,15 +7802,15 @@
         <v>25</v>
       </c>
       <c r="D162" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162" t="n">
-        <v>0.000515975483538925</v>
+        <v>0.0000731819835975405</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0162143467350227</v>
+        <v>0.006509531930357</v>
       </c>
       <c r="I162"/>
       <c r="J162" t="n">
@@ -6382,15 +7828,15 @@
         <v>25</v>
       </c>
       <c r="D163" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163" t="n">
-        <v>0.000515249399204647</v>
+        <v>0.0000731887357022909</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0161837631667627</v>
+        <v>0.00654187053592133</v>
       </c>
       <c r="I163"/>
       <c r="J163" t="n">
@@ -6408,15 +7854,15 @@
         <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164" t="n">
-        <v>0.000517974044082233</v>
+        <v>0.000072969938697962</v>
       </c>
       <c r="H164" t="n">
-        <v>0.0162550329107774</v>
+        <v>0.00650971844263463</v>
       </c>
       <c r="I164"/>
       <c r="J164" t="n">
@@ -6434,15 +7880,15 @@
         <v>25</v>
       </c>
       <c r="D165" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165" t="n">
-        <v>0.000514517663048894</v>
+        <v>0.000073378602873691</v>
       </c>
       <c r="H165" t="n">
-        <v>0.0161573997755607</v>
+        <v>0.00652764121502774</v>
       </c>
       <c r="I165"/>
       <c r="J165" t="n">
@@ -6460,15 +7906,15 @@
         <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166" t="n">
-        <v>0.000472414088593065</v>
+        <v>0.000188541415835181</v>
       </c>
       <c r="H166" t="n">
-        <v>0.0158472107195783</v>
+        <v>0.0115621741316753</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -6486,15 +7932,15 @@
         <v>27</v>
       </c>
       <c r="D167" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167" t="n">
-        <v>0.000474557244125652</v>
+        <v>0.00019416455185569</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0159164374511597</v>
+        <v>0.0117604717317418</v>
       </c>
       <c r="I167"/>
       <c r="J167" t="n">
@@ -6512,15 +7958,15 @@
         <v>27</v>
       </c>
       <c r="D168" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168" t="n">
-        <v>0.000473096321388058</v>
+        <v>0.000192506257707072</v>
       </c>
       <c r="H168" t="n">
-        <v>0.0158568789536106</v>
+        <v>0.011724336473991</v>
       </c>
       <c r="I168"/>
       <c r="J168" t="n">
@@ -6538,18 +7984,4386 @@
         <v>27</v>
       </c>
       <c r="D169" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169" t="n">
-        <v>0.000498501614556952</v>
+        <v>0.000193549326953702</v>
       </c>
       <c r="H169" t="n">
-        <v>0.0163844868958091</v>
+        <v>0.0117509450371835</v>
       </c>
       <c r="I169"/>
       <c r="J169" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>34</v>
+      </c>
+      <c r="B170" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" t="s">
+        <v>51</v>
+      </c>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170" t="n">
+        <v>0.0036381251932954</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.0496627782816975</v>
+      </c>
+      <c r="I170"/>
+      <c r="J170" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>14</v>
+      </c>
+      <c r="D171" t="s">
+        <v>52</v>
+      </c>
+      <c r="E171"/>
+      <c r="F171"/>
+      <c r="G171" t="n">
+        <v>0.00359753499313843</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.0492627632143011</v>
+      </c>
+      <c r="I171"/>
+      <c r="J171" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>34</v>
+      </c>
+      <c r="B172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>53</v>
+      </c>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172" t="n">
+        <v>0.00356913047144924</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.0491878082832575</v>
+      </c>
+      <c r="I172"/>
+      <c r="J172" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>34</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
+        <v>14</v>
+      </c>
+      <c r="D173" t="s">
+        <v>54</v>
+      </c>
+      <c r="E173"/>
+      <c r="F173"/>
+      <c r="G173" t="n">
+        <v>0.00355649884683804</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.0492404317010501</v>
+      </c>
+      <c r="I173"/>
+      <c r="J173" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>16</v>
+      </c>
+      <c r="D174" t="s">
+        <v>51</v>
+      </c>
+      <c r="E174"/>
+      <c r="F174"/>
+      <c r="G174" t="n">
+        <v>0.003484147184224</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.0456744783807424</v>
+      </c>
+      <c r="I174"/>
+      <c r="J174" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>34</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" t="s">
+        <v>16</v>
+      </c>
+      <c r="D175" t="s">
+        <v>52</v>
+      </c>
+      <c r="E175"/>
+      <c r="F175"/>
+      <c r="G175" t="n">
+        <v>0.00346671876821047</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.0454312913928589</v>
+      </c>
+      <c r="I175"/>
+      <c r="J175" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>34</v>
+      </c>
+      <c r="B176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" t="s">
+        <v>16</v>
+      </c>
+      <c r="D176" t="s">
+        <v>53</v>
+      </c>
+      <c r="E176"/>
+      <c r="F176"/>
+      <c r="G176" t="n">
+        <v>0.00347494934703716</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.0455330620067754</v>
+      </c>
+      <c r="I176"/>
+      <c r="J176" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>34</v>
+      </c>
+      <c r="B177" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" t="s">
+        <v>16</v>
+      </c>
+      <c r="D177" t="s">
+        <v>54</v>
+      </c>
+      <c r="E177"/>
+      <c r="F177"/>
+      <c r="G177" t="n">
+        <v>0.00343491348207355</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.045148527161354</v>
+      </c>
+      <c r="I177"/>
+      <c r="J177" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>34</v>
+      </c>
+      <c r="B178" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" t="s">
+        <v>19</v>
+      </c>
+      <c r="D178" t="s">
+        <v>51</v>
+      </c>
+      <c r="E178"/>
+      <c r="F178"/>
+      <c r="G178" t="n">
+        <v>0.00126811630646402</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.0253392636435161</v>
+      </c>
+      <c r="I178"/>
+      <c r="J178" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>34</v>
+      </c>
+      <c r="B179" t="s">
+        <v>18</v>
+      </c>
+      <c r="C179" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" t="s">
+        <v>52</v>
+      </c>
+      <c r="E179"/>
+      <c r="F179"/>
+      <c r="G179" t="n">
+        <v>0.00126467456649125</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.0252829822768248</v>
+      </c>
+      <c r="I179"/>
+      <c r="J179" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>34</v>
+      </c>
+      <c r="B180" t="s">
+        <v>18</v>
+      </c>
+      <c r="C180" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180" t="s">
+        <v>53</v>
+      </c>
+      <c r="E180"/>
+      <c r="F180"/>
+      <c r="G180" t="n">
+        <v>0.00126652800386674</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.0253548640203161</v>
+      </c>
+      <c r="I180"/>
+      <c r="J180" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>34</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" t="s">
+        <v>54</v>
+      </c>
+      <c r="E181"/>
+      <c r="F181"/>
+      <c r="G181" t="n">
+        <v>0.00127149271360507</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.0253687821943387</v>
+      </c>
+      <c r="I181"/>
+      <c r="J181" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>34</v>
+      </c>
+      <c r="B182" t="s">
+        <v>18</v>
+      </c>
+      <c r="C182" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" t="s">
+        <v>51</v>
+      </c>
+      <c r="E182"/>
+      <c r="F182"/>
+      <c r="G182" t="n">
+        <v>0.00139008761376244</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.0254564334547203</v>
+      </c>
+      <c r="I182"/>
+      <c r="J182" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>34</v>
+      </c>
+      <c r="B183" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" t="s">
+        <v>21</v>
+      </c>
+      <c r="D183" t="s">
+        <v>52</v>
+      </c>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183" t="n">
+        <v>0.00140563663457442</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.0256035458764409</v>
+      </c>
+      <c r="I183"/>
+      <c r="J183" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>34</v>
+      </c>
+      <c r="B184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" t="s">
+        <v>21</v>
+      </c>
+      <c r="D184" t="s">
+        <v>53</v>
+      </c>
+      <c r="E184"/>
+      <c r="F184"/>
+      <c r="G184" t="n">
+        <v>0.00140626405337989</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.0255539501141129</v>
+      </c>
+      <c r="I184"/>
+      <c r="J184" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>34</v>
+      </c>
+      <c r="B185" t="s">
+        <v>18</v>
+      </c>
+      <c r="C185" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185" t="s">
+        <v>54</v>
+      </c>
+      <c r="E185"/>
+      <c r="F185"/>
+      <c r="G185" t="n">
+        <v>0.00139952562483402</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.025505927283977</v>
+      </c>
+      <c r="I185"/>
+      <c r="J185" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>34</v>
+      </c>
+      <c r="B186" t="s">
+        <v>18</v>
+      </c>
+      <c r="C186" t="s">
+        <v>23</v>
+      </c>
+      <c r="D186" t="s">
+        <v>51</v>
+      </c>
+      <c r="E186"/>
+      <c r="F186"/>
+      <c r="G186" t="n">
+        <v>0.00118673619053998</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.0251371443190089</v>
+      </c>
+      <c r="I186"/>
+      <c r="J186" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>34</v>
+      </c>
+      <c r="B187" t="s">
+        <v>18</v>
+      </c>
+      <c r="C187" t="s">
+        <v>23</v>
+      </c>
+      <c r="D187" t="s">
+        <v>52</v>
+      </c>
+      <c r="E187"/>
+      <c r="F187"/>
+      <c r="G187" t="n">
+        <v>0.00119518407752138</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.0252434532782093</v>
+      </c>
+      <c r="I187"/>
+      <c r="J187" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>34</v>
+      </c>
+      <c r="B188" t="s">
+        <v>18</v>
+      </c>
+      <c r="C188" t="s">
+        <v>23</v>
+      </c>
+      <c r="D188" t="s">
+        <v>53</v>
+      </c>
+      <c r="E188"/>
+      <c r="F188"/>
+      <c r="G188" t="n">
+        <v>0.00118875819928141</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.0251762043851933</v>
+      </c>
+      <c r="I188"/>
+      <c r="J188" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>34</v>
+      </c>
+      <c r="B189" t="s">
+        <v>18</v>
+      </c>
+      <c r="C189" t="s">
+        <v>23</v>
+      </c>
+      <c r="D189" t="s">
+        <v>54</v>
+      </c>
+      <c r="E189"/>
+      <c r="F189"/>
+      <c r="G189" t="n">
+        <v>0.00118893327256391</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.0251902640642417</v>
+      </c>
+      <c r="I189"/>
+      <c r="J189" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>34</v>
+      </c>
+      <c r="B190" t="s">
+        <v>18</v>
+      </c>
+      <c r="C190" t="s">
+        <v>25</v>
+      </c>
+      <c r="D190" t="s">
+        <v>51</v>
+      </c>
+      <c r="E190"/>
+      <c r="F190"/>
+      <c r="G190" t="n">
+        <v>0.00119410125441484</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.0251864726074049</v>
+      </c>
+      <c r="I190"/>
+      <c r="J190" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>34</v>
+      </c>
+      <c r="B191" t="s">
+        <v>18</v>
+      </c>
+      <c r="C191" t="s">
+        <v>25</v>
+      </c>
+      <c r="D191" t="s">
+        <v>52</v>
+      </c>
+      <c r="E191"/>
+      <c r="F191"/>
+      <c r="G191" t="n">
+        <v>0.00119640199819336</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.0252607591360278</v>
+      </c>
+      <c r="I191"/>
+      <c r="J191" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>34</v>
+      </c>
+      <c r="B192" t="s">
+        <v>18</v>
+      </c>
+      <c r="C192" t="s">
+        <v>25</v>
+      </c>
+      <c r="D192" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192"/>
+      <c r="F192"/>
+      <c r="G192" t="n">
+        <v>0.00119618925707479</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.025190633289234</v>
+      </c>
+      <c r="I192"/>
+      <c r="J192" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>34</v>
+      </c>
+      <c r="B193" t="s">
+        <v>18</v>
+      </c>
+      <c r="C193" t="s">
+        <v>25</v>
+      </c>
+      <c r="D193" t="s">
+        <v>54</v>
+      </c>
+      <c r="E193"/>
+      <c r="F193"/>
+      <c r="G193" t="n">
+        <v>0.00119173597115386</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.0252014567648417</v>
+      </c>
+      <c r="I193"/>
+      <c r="J193" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>34</v>
+      </c>
+      <c r="B194" t="s">
+        <v>18</v>
+      </c>
+      <c r="C194" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" t="s">
+        <v>51</v>
+      </c>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194" t="n">
+        <v>0.00105300999455119</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.0226724565262974</v>
+      </c>
+      <c r="I194"/>
+      <c r="J194" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>34</v>
+      </c>
+      <c r="B195" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195" t="s">
+        <v>52</v>
+      </c>
+      <c r="E195"/>
+      <c r="F195"/>
+      <c r="G195" t="n">
+        <v>0.00105452814360453</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.0227335739794848</v>
+      </c>
+      <c r="I195"/>
+      <c r="J195" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>34</v>
+      </c>
+      <c r="B196" t="s">
+        <v>18</v>
+      </c>
+      <c r="C196" t="s">
+        <v>27</v>
+      </c>
+      <c r="D196" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196"/>
+      <c r="F196"/>
+      <c r="G196" t="n">
+        <v>0.00105572271240952</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.0226091064656082</v>
+      </c>
+      <c r="I196"/>
+      <c r="J196" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>34</v>
+      </c>
+      <c r="B197" t="s">
+        <v>18</v>
+      </c>
+      <c r="C197" t="s">
+        <v>27</v>
+      </c>
+      <c r="D197" t="s">
+        <v>54</v>
+      </c>
+      <c r="E197"/>
+      <c r="F197"/>
+      <c r="G197" t="n">
+        <v>0.00105491878662831</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.0227101736023227</v>
+      </c>
+      <c r="I197"/>
+      <c r="J197" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>35</v>
+      </c>
+      <c r="B198" t="s">
+        <v>13</v>
+      </c>
+      <c r="C198" t="s">
+        <v>14</v>
+      </c>
+      <c r="D198" t="s">
+        <v>51</v>
+      </c>
+      <c r="E198"/>
+      <c r="F198"/>
+      <c r="G198" t="n">
+        <v>0.00166761224042229</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.030724183590473</v>
+      </c>
+      <c r="I198"/>
+      <c r="J198" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>35</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" t="s">
+        <v>14</v>
+      </c>
+      <c r="D199" t="s">
+        <v>52</v>
+      </c>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199" t="n">
+        <v>0.00166615778386249</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.0306570479449885</v>
+      </c>
+      <c r="I199"/>
+      <c r="J199" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>35</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
+        <v>14</v>
+      </c>
+      <c r="D200" t="s">
+        <v>53</v>
+      </c>
+      <c r="E200"/>
+      <c r="F200"/>
+      <c r="G200" t="n">
+        <v>0.00166219447105923</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.0306077709655781</v>
+      </c>
+      <c r="I200"/>
+      <c r="J200" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>35</v>
+      </c>
+      <c r="B201" t="s">
+        <v>13</v>
+      </c>
+      <c r="C201" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" t="s">
+        <v>54</v>
+      </c>
+      <c r="E201"/>
+      <c r="F201"/>
+      <c r="G201" t="n">
+        <v>0.00166821539143441</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.0306519330343691</v>
+      </c>
+      <c r="I201"/>
+      <c r="J201" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>35</v>
+      </c>
+      <c r="B202" t="s">
+        <v>13</v>
+      </c>
+      <c r="C202" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" t="s">
+        <v>51</v>
+      </c>
+      <c r="E202"/>
+      <c r="F202"/>
+      <c r="G202" t="n">
+        <v>0.00221371667149343</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.0352095752699077</v>
+      </c>
+      <c r="I202"/>
+      <c r="J202" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>35</v>
+      </c>
+      <c r="B203" t="s">
+        <v>13</v>
+      </c>
+      <c r="C203" t="s">
+        <v>16</v>
+      </c>
+      <c r="D203" t="s">
+        <v>52</v>
+      </c>
+      <c r="E203"/>
+      <c r="F203"/>
+      <c r="G203" t="n">
+        <v>0.00219838629557541</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.0349687425776701</v>
+      </c>
+      <c r="I203"/>
+      <c r="J203" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>35</v>
+      </c>
+      <c r="B204" t="s">
+        <v>13</v>
+      </c>
+      <c r="C204" t="s">
+        <v>16</v>
+      </c>
+      <c r="D204" t="s">
+        <v>53</v>
+      </c>
+      <c r="E204"/>
+      <c r="F204"/>
+      <c r="G204" t="n">
+        <v>0.00221137378612753</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.0350618290264087</v>
+      </c>
+      <c r="I204"/>
+      <c r="J204" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>35</v>
+      </c>
+      <c r="B205" t="s">
+        <v>13</v>
+      </c>
+      <c r="C205" t="s">
+        <v>16</v>
+      </c>
+      <c r="D205" t="s">
+        <v>54</v>
+      </c>
+      <c r="E205"/>
+      <c r="F205"/>
+      <c r="G205" t="n">
+        <v>0.00221390122567555</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.0351408377698628</v>
+      </c>
+      <c r="I205"/>
+      <c r="J205" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>35</v>
+      </c>
+      <c r="B206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C206" t="s">
+        <v>19</v>
+      </c>
+      <c r="D206" t="s">
+        <v>51</v>
+      </c>
+      <c r="E206"/>
+      <c r="F206"/>
+      <c r="G206" t="n">
+        <v>0.000440927315547278</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.0138415879749341</v>
+      </c>
+      <c r="I206"/>
+      <c r="J206" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>35</v>
+      </c>
+      <c r="B207" t="s">
+        <v>18</v>
+      </c>
+      <c r="C207" t="s">
+        <v>19</v>
+      </c>
+      <c r="D207" t="s">
+        <v>52</v>
+      </c>
+      <c r="E207"/>
+      <c r="F207"/>
+      <c r="G207" t="n">
+        <v>0.000441080002849877</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.0139009122504683</v>
+      </c>
+      <c r="I207"/>
+      <c r="J207" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>35</v>
+      </c>
+      <c r="B208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D208" t="s">
+        <v>53</v>
+      </c>
+      <c r="E208"/>
+      <c r="F208"/>
+      <c r="G208" t="n">
+        <v>0.000439957125230199</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.0138355216301009</v>
+      </c>
+      <c r="I208"/>
+      <c r="J208" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>35</v>
+      </c>
+      <c r="B209" t="s">
+        <v>18</v>
+      </c>
+      <c r="C209" t="s">
+        <v>19</v>
+      </c>
+      <c r="D209" t="s">
+        <v>54</v>
+      </c>
+      <c r="E209"/>
+      <c r="F209"/>
+      <c r="G209" t="n">
+        <v>0.000440116962759475</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.0138249395722329</v>
+      </c>
+      <c r="I209"/>
+      <c r="J209" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>35</v>
+      </c>
+      <c r="B210" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" t="s">
+        <v>21</v>
+      </c>
+      <c r="D210" t="s">
+        <v>51</v>
+      </c>
+      <c r="E210"/>
+      <c r="F210"/>
+      <c r="G210" t="n">
+        <v>0.00055798623368306</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.0139583157606297</v>
+      </c>
+      <c r="I210"/>
+      <c r="J210" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>35</v>
+      </c>
+      <c r="B211" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211" t="s">
+        <v>52</v>
+      </c>
+      <c r="E211"/>
+      <c r="F211"/>
+      <c r="G211" t="n">
+        <v>0.000560572567196004</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.0140433847165795</v>
+      </c>
+      <c r="I211"/>
+      <c r="J211" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>35</v>
+      </c>
+      <c r="B212" t="s">
+        <v>18</v>
+      </c>
+      <c r="C212" t="s">
+        <v>21</v>
+      </c>
+      <c r="D212" t="s">
+        <v>53</v>
+      </c>
+      <c r="E212"/>
+      <c r="F212"/>
+      <c r="G212" t="n">
+        <v>0.000558105379367882</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.0139865066720216</v>
+      </c>
+      <c r="I212"/>
+      <c r="J212" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>35</v>
+      </c>
+      <c r="B213" t="s">
+        <v>18</v>
+      </c>
+      <c r="C213" t="s">
+        <v>21</v>
+      </c>
+      <c r="D213" t="s">
+        <v>54</v>
+      </c>
+      <c r="E213"/>
+      <c r="F213"/>
+      <c r="G213" t="n">
+        <v>0.000559993134889333</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.0140057993117563</v>
+      </c>
+      <c r="I213"/>
+      <c r="J213" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>35</v>
+      </c>
+      <c r="B214" t="s">
+        <v>18</v>
+      </c>
+      <c r="C214" t="s">
+        <v>23</v>
+      </c>
+      <c r="D214" t="s">
+        <v>51</v>
+      </c>
+      <c r="E214"/>
+      <c r="F214"/>
+      <c r="G214" t="n">
+        <v>0.000371930517654909</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.0136237968162459</v>
+      </c>
+      <c r="I214"/>
+      <c r="J214" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>35</v>
+      </c>
+      <c r="B215" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" t="s">
+        <v>23</v>
+      </c>
+      <c r="D215" t="s">
+        <v>52</v>
+      </c>
+      <c r="E215"/>
+      <c r="F215"/>
+      <c r="G215" t="n">
+        <v>0.000371053408017486</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.0136361008685899</v>
+      </c>
+      <c r="I215"/>
+      <c r="J215" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>35</v>
+      </c>
+      <c r="B216" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216" t="s">
+        <v>23</v>
+      </c>
+      <c r="D216" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216" t="n">
+        <v>0.0003720898846319</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.0136145728273155</v>
+      </c>
+      <c r="I216"/>
+      <c r="J216" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>35</v>
+      </c>
+      <c r="B217" t="s">
+        <v>18</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
+      </c>
+      <c r="D217" t="s">
+        <v>54</v>
+      </c>
+      <c r="E217"/>
+      <c r="F217"/>
+      <c r="G217" t="n">
+        <v>0.00037403354880693</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.0136783889142282</v>
+      </c>
+      <c r="I217"/>
+      <c r="J217" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>35</v>
+      </c>
+      <c r="B218" t="s">
+        <v>18</v>
+      </c>
+      <c r="C218" t="s">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>51</v>
+      </c>
+      <c r="E218"/>
+      <c r="F218"/>
+      <c r="G218" t="n">
+        <v>0.000372673174011669</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.0136185851814476</v>
+      </c>
+      <c r="I218"/>
+      <c r="J218" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>35</v>
+      </c>
+      <c r="B219" t="s">
+        <v>18</v>
+      </c>
+      <c r="C219" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219" t="s">
+        <v>52</v>
+      </c>
+      <c r="E219"/>
+      <c r="F219"/>
+      <c r="G219" t="n">
+        <v>0.000371869402349157</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.0136414182944271</v>
+      </c>
+      <c r="I219"/>
+      <c r="J219" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>35</v>
+      </c>
+      <c r="B220" t="s">
+        <v>18</v>
+      </c>
+      <c r="C220" t="s">
+        <v>25</v>
+      </c>
+      <c r="D220" t="s">
+        <v>53</v>
+      </c>
+      <c r="E220"/>
+      <c r="F220"/>
+      <c r="G220" t="n">
+        <v>0.000372621800908681</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.0136283067210671</v>
+      </c>
+      <c r="I220"/>
+      <c r="J220" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>35</v>
+      </c>
+      <c r="B221" t="s">
+        <v>18</v>
+      </c>
+      <c r="C221" t="s">
+        <v>25</v>
+      </c>
+      <c r="D221" t="s">
+        <v>54</v>
+      </c>
+      <c r="E221"/>
+      <c r="F221"/>
+      <c r="G221" t="n">
+        <v>0.000371485561165672</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.0136066516801793</v>
+      </c>
+      <c r="I221"/>
+      <c r="J221" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>35</v>
+      </c>
+      <c r="B222" t="s">
+        <v>18</v>
+      </c>
+      <c r="C222" t="s">
+        <v>27</v>
+      </c>
+      <c r="D222" t="s">
+        <v>51</v>
+      </c>
+      <c r="E222"/>
+      <c r="F222"/>
+      <c r="G222" t="n">
+        <v>0.000426716702573042</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.0144062298899832</v>
+      </c>
+      <c r="I222"/>
+      <c r="J222" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>35</v>
+      </c>
+      <c r="B223" t="s">
+        <v>18</v>
+      </c>
+      <c r="C223" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223" t="s">
+        <v>52</v>
+      </c>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223" t="n">
+        <v>0.000426270269863009</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.014367787948999</v>
+      </c>
+      <c r="I223"/>
+      <c r="J223" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>35</v>
+      </c>
+      <c r="B224" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" t="s">
+        <v>27</v>
+      </c>
+      <c r="D224" t="s">
+        <v>53</v>
+      </c>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224" t="n">
+        <v>0.000426437348226608</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.0143911833197185</v>
+      </c>
+      <c r="I224"/>
+      <c r="J224" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>35</v>
+      </c>
+      <c r="B225" t="s">
+        <v>18</v>
+      </c>
+      <c r="C225" t="s">
+        <v>27</v>
+      </c>
+      <c r="D225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E225"/>
+      <c r="F225"/>
+      <c r="G225" t="n">
+        <v>0.00042725573166905</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.0143829478503235</v>
+      </c>
+      <c r="I225"/>
+      <c r="J225" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>36</v>
+      </c>
+      <c r="B226" t="s">
+        <v>13</v>
+      </c>
+      <c r="C226" t="s">
+        <v>14</v>
+      </c>
+      <c r="D226" t="s">
+        <v>51</v>
+      </c>
+      <c r="E226"/>
+      <c r="F226"/>
+      <c r="G226" t="n">
+        <v>0.000676683744102551</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.0195906323295824</v>
+      </c>
+      <c r="I226"/>
+      <c r="J226" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>36</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
+        <v>14</v>
+      </c>
+      <c r="D227" t="s">
+        <v>52</v>
+      </c>
+      <c r="E227"/>
+      <c r="F227"/>
+      <c r="G227" t="n">
+        <v>0.000672402641346374</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.0195516649985889</v>
+      </c>
+      <c r="I227"/>
+      <c r="J227" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>36</v>
+      </c>
+      <c r="B228" t="s">
+        <v>13</v>
+      </c>
+      <c r="C228" t="s">
+        <v>14</v>
+      </c>
+      <c r="D228" t="s">
+        <v>53</v>
+      </c>
+      <c r="E228"/>
+      <c r="F228"/>
+      <c r="G228" t="n">
+        <v>0.000674521843369174</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.0195509382881051</v>
+      </c>
+      <c r="I228"/>
+      <c r="J228" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>36</v>
+      </c>
+      <c r="B229" t="s">
+        <v>13</v>
+      </c>
+      <c r="C229" t="s">
+        <v>14</v>
+      </c>
+      <c r="D229" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229" t="n">
+        <v>0.000665178613114765</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.0193356982556131</v>
+      </c>
+      <c r="I229"/>
+      <c r="J229" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>36</v>
+      </c>
+      <c r="B230" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" t="s">
+        <v>16</v>
+      </c>
+      <c r="D230" t="s">
+        <v>51</v>
+      </c>
+      <c r="E230"/>
+      <c r="F230"/>
+      <c r="G230" t="n">
+        <v>0.00147293009676902</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.0273294773216034</v>
+      </c>
+      <c r="I230"/>
+      <c r="J230" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>36</v>
+      </c>
+      <c r="B231" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" t="s">
+        <v>16</v>
+      </c>
+      <c r="D231" t="s">
+        <v>52</v>
+      </c>
+      <c r="E231"/>
+      <c r="F231"/>
+      <c r="G231" t="n">
+        <v>0.00145338176945918</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.0272582267288296</v>
+      </c>
+      <c r="I231"/>
+      <c r="J231" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>36</v>
+      </c>
+      <c r="B232" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" t="s">
+        <v>16</v>
+      </c>
+      <c r="D232" t="s">
+        <v>53</v>
+      </c>
+      <c r="E232"/>
+      <c r="F232"/>
+      <c r="G232" t="n">
+        <v>0.00147087175869145</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.0272912291793638</v>
+      </c>
+      <c r="I232"/>
+      <c r="J232" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>36</v>
+      </c>
+      <c r="B233" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233" t="s">
+        <v>16</v>
+      </c>
+      <c r="D233" t="s">
+        <v>54</v>
+      </c>
+      <c r="E233"/>
+      <c r="F233"/>
+      <c r="G233" t="n">
+        <v>0.00147326533405407</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.0274111584470025</v>
+      </c>
+      <c r="I233"/>
+      <c r="J233" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>36</v>
+      </c>
+      <c r="B234" t="s">
+        <v>18</v>
+      </c>
+      <c r="C234" t="s">
+        <v>19</v>
+      </c>
+      <c r="D234" t="s">
+        <v>51</v>
+      </c>
+      <c r="E234"/>
+      <c r="F234"/>
+      <c r="G234" t="n">
+        <v>0.000245667043006321</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.00909560831095478</v>
+      </c>
+      <c r="I234"/>
+      <c r="J234" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>36</v>
+      </c>
+      <c r="B235" t="s">
+        <v>18</v>
+      </c>
+      <c r="C235" t="s">
+        <v>19</v>
+      </c>
+      <c r="D235" t="s">
+        <v>52</v>
+      </c>
+      <c r="E235"/>
+      <c r="F235"/>
+      <c r="G235" t="n">
+        <v>0.000245508666508611</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.00912011750501952</v>
+      </c>
+      <c r="I235"/>
+      <c r="J235" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>36</v>
+      </c>
+      <c r="B236" t="s">
+        <v>18</v>
+      </c>
+      <c r="C236" t="s">
+        <v>19</v>
+      </c>
+      <c r="D236" t="s">
+        <v>53</v>
+      </c>
+      <c r="E236"/>
+      <c r="F236"/>
+      <c r="G236" t="n">
+        <v>0.000245235604131072</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.00908388898596218</v>
+      </c>
+      <c r="I236"/>
+      <c r="J236" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>36</v>
+      </c>
+      <c r="B237" t="s">
+        <v>18</v>
+      </c>
+      <c r="C237" t="s">
+        <v>19</v>
+      </c>
+      <c r="D237" t="s">
+        <v>54</v>
+      </c>
+      <c r="E237"/>
+      <c r="F237"/>
+      <c r="G237" t="n">
+        <v>0.000245926109953433</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.00909287451772852</v>
+      </c>
+      <c r="I237"/>
+      <c r="J237" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>36</v>
+      </c>
+      <c r="B238" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238" t="s">
+        <v>21</v>
+      </c>
+      <c r="D238" t="s">
+        <v>51</v>
+      </c>
+      <c r="E238"/>
+      <c r="F238"/>
+      <c r="G238" t="n">
+        <v>0.000363177944662373</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.00922513747043332</v>
+      </c>
+      <c r="I238"/>
+      <c r="J238" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>36</v>
+      </c>
+      <c r="B239" t="s">
+        <v>18</v>
+      </c>
+      <c r="C239" t="s">
+        <v>21</v>
+      </c>
+      <c r="D239" t="s">
+        <v>52</v>
+      </c>
+      <c r="E239"/>
+      <c r="F239"/>
+      <c r="G239" t="n">
+        <v>0.00036313233845448</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.00927155021217419</v>
+      </c>
+      <c r="I239"/>
+      <c r="J239" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>36</v>
+      </c>
+      <c r="B240" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" t="s">
+        <v>21</v>
+      </c>
+      <c r="D240" t="s">
+        <v>53</v>
+      </c>
+      <c r="E240"/>
+      <c r="F240"/>
+      <c r="G240" t="n">
+        <v>0.000362668495333134</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.00922304700864093</v>
+      </c>
+      <c r="I240"/>
+      <c r="J240" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>36</v>
+      </c>
+      <c r="B241" t="s">
+        <v>18</v>
+      </c>
+      <c r="C241" t="s">
+        <v>21</v>
+      </c>
+      <c r="D241" t="s">
+        <v>54</v>
+      </c>
+      <c r="E241"/>
+      <c r="F241"/>
+      <c r="G241" t="n">
+        <v>0.000363574019713251</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.00924680370269485</v>
+      </c>
+      <c r="I241"/>
+      <c r="J241" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>36</v>
+      </c>
+      <c r="B242" t="s">
+        <v>18</v>
+      </c>
+      <c r="C242" t="s">
+        <v>23</v>
+      </c>
+      <c r="D242" t="s">
+        <v>51</v>
+      </c>
+      <c r="E242"/>
+      <c r="F242"/>
+      <c r="G242" t="n">
+        <v>0.000179094086592131</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.00885470430626591</v>
+      </c>
+      <c r="I242"/>
+      <c r="J242" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>36</v>
+      </c>
+      <c r="B243" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" t="s">
+        <v>23</v>
+      </c>
+      <c r="D243" t="s">
+        <v>52</v>
+      </c>
+      <c r="E243"/>
+      <c r="F243"/>
+      <c r="G243" t="n">
+        <v>0.0001790992604672</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.00885761398843889</v>
+      </c>
+      <c r="I243"/>
+      <c r="J243" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>36</v>
+      </c>
+      <c r="B244" t="s">
+        <v>18</v>
+      </c>
+      <c r="C244" t="s">
+        <v>23</v>
+      </c>
+      <c r="D244" t="s">
+        <v>53</v>
+      </c>
+      <c r="E244"/>
+      <c r="F244"/>
+      <c r="G244" t="n">
+        <v>0.000179014583527614</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.00885171109735738</v>
+      </c>
+      <c r="I244"/>
+      <c r="J244" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>36</v>
+      </c>
+      <c r="B245" t="s">
+        <v>18</v>
+      </c>
+      <c r="C245" t="s">
+        <v>23</v>
+      </c>
+      <c r="D245" t="s">
+        <v>54</v>
+      </c>
+      <c r="E245"/>
+      <c r="F245"/>
+      <c r="G245" t="n">
+        <v>0.000179209259230544</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.0088790851912377</v>
+      </c>
+      <c r="I245"/>
+      <c r="J245" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>36</v>
+      </c>
+      <c r="B246" t="s">
+        <v>18</v>
+      </c>
+      <c r="C246" t="s">
+        <v>25</v>
+      </c>
+      <c r="D246" t="s">
+        <v>51</v>
+      </c>
+      <c r="E246"/>
+      <c r="F246"/>
+      <c r="G246" t="n">
+        <v>0.000179093081742157</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0.00887060083092503</v>
+      </c>
+      <c r="I246"/>
+      <c r="J246" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>36</v>
+      </c>
+      <c r="B247" t="s">
+        <v>18</v>
+      </c>
+      <c r="C247" t="s">
+        <v>25</v>
+      </c>
+      <c r="D247" t="s">
+        <v>52</v>
+      </c>
+      <c r="E247"/>
+      <c r="F247"/>
+      <c r="G247" t="n">
+        <v>0.000180414799340363</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0.00892036372936892</v>
+      </c>
+      <c r="I247"/>
+      <c r="J247" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>36</v>
+      </c>
+      <c r="B248" t="s">
+        <v>18</v>
+      </c>
+      <c r="C248" t="s">
+        <v>25</v>
+      </c>
+      <c r="D248" t="s">
+        <v>53</v>
+      </c>
+      <c r="E248"/>
+      <c r="F248"/>
+      <c r="G248" t="n">
+        <v>0.000179241201890083</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0.00886856355378329</v>
+      </c>
+      <c r="I248"/>
+      <c r="J248" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>36</v>
+      </c>
+      <c r="B249" t="s">
+        <v>18</v>
+      </c>
+      <c r="C249" t="s">
+        <v>25</v>
+      </c>
+      <c r="D249" t="s">
+        <v>54</v>
+      </c>
+      <c r="E249"/>
+      <c r="F249"/>
+      <c r="G249" t="n">
+        <v>0.000179336892160008</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0.00888984575206539</v>
+      </c>
+      <c r="I249"/>
+      <c r="J249" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>36</v>
+      </c>
+      <c r="B250" t="s">
+        <v>18</v>
+      </c>
+      <c r="C250" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250" t="s">
+        <v>51</v>
+      </c>
+      <c r="E250"/>
+      <c r="F250"/>
+      <c r="G250" t="n">
+        <v>0.000284230183519138</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0.0123020558685505</v>
+      </c>
+      <c r="I250"/>
+      <c r="J250" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>36</v>
+      </c>
+      <c r="B251" t="s">
+        <v>18</v>
+      </c>
+      <c r="C251" t="s">
+        <v>27</v>
+      </c>
+      <c r="D251" t="s">
+        <v>52</v>
+      </c>
+      <c r="E251"/>
+      <c r="F251"/>
+      <c r="G251" t="n">
+        <v>0.000283976912124149</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0.0122938512280727</v>
+      </c>
+      <c r="I251"/>
+      <c r="J251" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>36</v>
+      </c>
+      <c r="B252" t="s">
+        <v>18</v>
+      </c>
+      <c r="C252" t="s">
+        <v>27</v>
+      </c>
+      <c r="D252" t="s">
+        <v>53</v>
+      </c>
+      <c r="E252"/>
+      <c r="F252"/>
+      <c r="G252" t="n">
+        <v>0.000283700990828039</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0.0122857668185328</v>
+      </c>
+      <c r="I252"/>
+      <c r="J252" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>36</v>
+      </c>
+      <c r="B253" t="s">
+        <v>18</v>
+      </c>
+      <c r="C253" t="s">
+        <v>27</v>
+      </c>
+      <c r="D253" t="s">
+        <v>54</v>
+      </c>
+      <c r="E253"/>
+      <c r="F253"/>
+      <c r="G253" t="n">
+        <v>0.000281795679579258</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0.0122357680340678</v>
+      </c>
+      <c r="I253"/>
+      <c r="J253" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>37</v>
+      </c>
+      <c r="B254" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" t="s">
+        <v>14</v>
+      </c>
+      <c r="D254" t="s">
+        <v>51</v>
+      </c>
+      <c r="E254"/>
+      <c r="F254"/>
+      <c r="G254" t="n">
+        <v>0.00222034506693136</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0.0375667427686673</v>
+      </c>
+      <c r="I254"/>
+      <c r="J254" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>37</v>
+      </c>
+      <c r="B255" t="s">
+        <v>13</v>
+      </c>
+      <c r="C255" t="s">
+        <v>14</v>
+      </c>
+      <c r="D255" t="s">
+        <v>52</v>
+      </c>
+      <c r="E255"/>
+      <c r="F255"/>
+      <c r="G255" t="n">
+        <v>0.00222974486755562</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0.0376444479794247</v>
+      </c>
+      <c r="I255"/>
+      <c r="J255" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>37</v>
+      </c>
+      <c r="B256" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" t="s">
+        <v>14</v>
+      </c>
+      <c r="D256" t="s">
+        <v>53</v>
+      </c>
+      <c r="E256"/>
+      <c r="F256"/>
+      <c r="G256" t="n">
+        <v>0.00222396599139518</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0.0375180818321421</v>
+      </c>
+      <c r="I256"/>
+      <c r="J256" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>37</v>
+      </c>
+      <c r="B257" t="s">
+        <v>13</v>
+      </c>
+      <c r="C257" t="s">
+        <v>14</v>
+      </c>
+      <c r="D257" t="s">
+        <v>54</v>
+      </c>
+      <c r="E257"/>
+      <c r="F257"/>
+      <c r="G257" t="n">
+        <v>0.00221853823235073</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0.0374711375783015</v>
+      </c>
+      <c r="I257"/>
+      <c r="J257" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>37</v>
+      </c>
+      <c r="B258" t="s">
+        <v>13</v>
+      </c>
+      <c r="C258" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" t="s">
+        <v>51</v>
+      </c>
+      <c r="E258"/>
+      <c r="F258"/>
+      <c r="G258" t="n">
+        <v>0.0018889546955675</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.0330648105518514</v>
+      </c>
+      <c r="I258"/>
+      <c r="J258" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>37</v>
+      </c>
+      <c r="B259" t="s">
+        <v>13</v>
+      </c>
+      <c r="C259" t="s">
+        <v>16</v>
+      </c>
+      <c r="D259" t="s">
+        <v>52</v>
+      </c>
+      <c r="E259"/>
+      <c r="F259"/>
+      <c r="G259" t="n">
+        <v>0.00187455642187341</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0.0330824322389803</v>
+      </c>
+      <c r="I259"/>
+      <c r="J259" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>37</v>
+      </c>
+      <c r="B260" t="s">
+        <v>13</v>
+      </c>
+      <c r="C260" t="s">
+        <v>16</v>
+      </c>
+      <c r="D260" t="s">
+        <v>53</v>
+      </c>
+      <c r="E260"/>
+      <c r="F260"/>
+      <c r="G260" t="n">
+        <v>0.00190037166372581</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.0333650463944738</v>
+      </c>
+      <c r="I260"/>
+      <c r="J260" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>37</v>
+      </c>
+      <c r="B261" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" t="s">
+        <v>16</v>
+      </c>
+      <c r="D261" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261"/>
+      <c r="F261"/>
+      <c r="G261" t="n">
+        <v>0.00188641551977872</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.0331862106513104</v>
+      </c>
+      <c r="I261"/>
+      <c r="J261" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>37</v>
+      </c>
+      <c r="B262" t="s">
+        <v>18</v>
+      </c>
+      <c r="C262" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" t="s">
+        <v>51</v>
+      </c>
+      <c r="E262"/>
+      <c r="F262"/>
+      <c r="G262" t="n">
+        <v>0.000514533718051439</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0.0151166361185263</v>
+      </c>
+      <c r="I262"/>
+      <c r="J262" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>37</v>
+      </c>
+      <c r="B263" t="s">
+        <v>18</v>
+      </c>
+      <c r="C263" t="s">
+        <v>19</v>
+      </c>
+      <c r="D263" t="s">
+        <v>52</v>
+      </c>
+      <c r="E263"/>
+      <c r="F263"/>
+      <c r="G263" t="n">
+        <v>0.000515440328913552</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0.0151339042580849</v>
+      </c>
+      <c r="I263"/>
+      <c r="J263" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>37</v>
+      </c>
+      <c r="B264" t="s">
+        <v>18</v>
+      </c>
+      <c r="C264" t="s">
+        <v>19</v>
+      </c>
+      <c r="D264" t="s">
+        <v>53</v>
+      </c>
+      <c r="E264"/>
+      <c r="F264"/>
+      <c r="G264" t="n">
+        <v>0.000514905484997201</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0.0151514742124416</v>
+      </c>
+      <c r="I264"/>
+      <c r="J264" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>37</v>
+      </c>
+      <c r="B265" t="s">
+        <v>18</v>
+      </c>
+      <c r="C265" t="s">
+        <v>19</v>
+      </c>
+      <c r="D265" t="s">
+        <v>54</v>
+      </c>
+      <c r="E265"/>
+      <c r="F265"/>
+      <c r="G265" t="n">
+        <v>0.000515239765876212</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0.0151179041015629</v>
+      </c>
+      <c r="I265"/>
+      <c r="J265" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>37</v>
+      </c>
+      <c r="B266" t="s">
+        <v>18</v>
+      </c>
+      <c r="C266" t="s">
+        <v>21</v>
+      </c>
+      <c r="D266" t="s">
+        <v>51</v>
+      </c>
+      <c r="E266"/>
+      <c r="F266"/>
+      <c r="G266" t="n">
+        <v>0.000640830207937886</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.0152817485280177</v>
+      </c>
+      <c r="I266"/>
+      <c r="J266" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>37</v>
+      </c>
+      <c r="B267" t="s">
+        <v>18</v>
+      </c>
+      <c r="C267" t="s">
+        <v>21</v>
+      </c>
+      <c r="D267" t="s">
+        <v>52</v>
+      </c>
+      <c r="E267"/>
+      <c r="F267"/>
+      <c r="G267" t="n">
+        <v>0.000640258379930802</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.0152913933628545</v>
+      </c>
+      <c r="I267"/>
+      <c r="J267" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>37</v>
+      </c>
+      <c r="B268" t="s">
+        <v>18</v>
+      </c>
+      <c r="C268" t="s">
+        <v>21</v>
+      </c>
+      <c r="D268" t="s">
+        <v>53</v>
+      </c>
+      <c r="E268"/>
+      <c r="F268"/>
+      <c r="G268" t="n">
+        <v>0.000642016778103838</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.015293282567136</v>
+      </c>
+      <c r="I268"/>
+      <c r="J268" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269" t="s">
+        <v>18</v>
+      </c>
+      <c r="C269" t="s">
+        <v>21</v>
+      </c>
+      <c r="D269" t="s">
+        <v>54</v>
+      </c>
+      <c r="E269"/>
+      <c r="F269"/>
+      <c r="G269" t="n">
+        <v>0.000645805505998343</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.0153264316435137</v>
+      </c>
+      <c r="I269"/>
+      <c r="J269" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>37</v>
+      </c>
+      <c r="B270" t="s">
+        <v>18</v>
+      </c>
+      <c r="C270" t="s">
+        <v>23</v>
+      </c>
+      <c r="D270" t="s">
+        <v>51</v>
+      </c>
+      <c r="E270"/>
+      <c r="F270"/>
+      <c r="G270" t="n">
+        <v>0.000436907508801859</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.0149200441915959</v>
+      </c>
+      <c r="I270"/>
+      <c r="J270" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>37</v>
+      </c>
+      <c r="B271" t="s">
+        <v>18</v>
+      </c>
+      <c r="C271" t="s">
+        <v>23</v>
+      </c>
+      <c r="D271" t="s">
+        <v>52</v>
+      </c>
+      <c r="E271"/>
+      <c r="F271"/>
+      <c r="G271" t="n">
+        <v>0.000437400990245494</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.0149021126991485</v>
+      </c>
+      <c r="I271"/>
+      <c r="J271" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272" t="s">
+        <v>18</v>
+      </c>
+      <c r="C272" t="s">
+        <v>23</v>
+      </c>
+      <c r="D272" t="s">
+        <v>53</v>
+      </c>
+      <c r="E272"/>
+      <c r="F272"/>
+      <c r="G272" t="n">
+        <v>0.000438974027144353</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.0149692419247107</v>
+      </c>
+      <c r="I272"/>
+      <c r="J272" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273" t="s">
+        <v>18</v>
+      </c>
+      <c r="C273" t="s">
+        <v>23</v>
+      </c>
+      <c r="D273" t="s">
+        <v>54</v>
+      </c>
+      <c r="E273"/>
+      <c r="F273"/>
+      <c r="G273" t="n">
+        <v>0.000439562419615105</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.0149611573815002</v>
+      </c>
+      <c r="I273"/>
+      <c r="J273" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>37</v>
+      </c>
+      <c r="B274" t="s">
+        <v>18</v>
+      </c>
+      <c r="C274" t="s">
+        <v>25</v>
+      </c>
+      <c r="D274" t="s">
+        <v>51</v>
+      </c>
+      <c r="E274"/>
+      <c r="F274"/>
+      <c r="G274" t="n">
+        <v>0.000440239772668997</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.0149475624463968</v>
+      </c>
+      <c r="I274"/>
+      <c r="J274" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>37</v>
+      </c>
+      <c r="B275" t="s">
+        <v>18</v>
+      </c>
+      <c r="C275" t="s">
+        <v>25</v>
+      </c>
+      <c r="D275" t="s">
+        <v>52</v>
+      </c>
+      <c r="E275"/>
+      <c r="F275"/>
+      <c r="G275" t="n">
+        <v>0.000440801401507655</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.0149916547717679</v>
+      </c>
+      <c r="I275"/>
+      <c r="J275" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>37</v>
+      </c>
+      <c r="B276" t="s">
+        <v>18</v>
+      </c>
+      <c r="C276" t="s">
+        <v>25</v>
+      </c>
+      <c r="D276" t="s">
+        <v>53</v>
+      </c>
+      <c r="E276"/>
+      <c r="F276"/>
+      <c r="G276" t="n">
+        <v>0.000442869623975716</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0.014981017447499</v>
+      </c>
+      <c r="I276"/>
+      <c r="J276" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>37</v>
+      </c>
+      <c r="B277" t="s">
+        <v>18</v>
+      </c>
+      <c r="C277" t="s">
+        <v>25</v>
+      </c>
+      <c r="D277" t="s">
+        <v>54</v>
+      </c>
+      <c r="E277"/>
+      <c r="F277"/>
+      <c r="G277" t="n">
+        <v>0.000439274651804825</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0.0149516270836447</v>
+      </c>
+      <c r="I277"/>
+      <c r="J277" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>37</v>
+      </c>
+      <c r="B278" t="s">
+        <v>18</v>
+      </c>
+      <c r="C278" t="s">
+        <v>27</v>
+      </c>
+      <c r="D278" t="s">
+        <v>51</v>
+      </c>
+      <c r="E278"/>
+      <c r="F278"/>
+      <c r="G278" t="n">
+        <v>0.000528522689644326</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0.0166735460634388</v>
+      </c>
+      <c r="I278"/>
+      <c r="J278" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>37</v>
+      </c>
+      <c r="B279" t="s">
+        <v>18</v>
+      </c>
+      <c r="C279" t="s">
+        <v>27</v>
+      </c>
+      <c r="D279" t="s">
+        <v>52</v>
+      </c>
+      <c r="E279"/>
+      <c r="F279"/>
+      <c r="G279" t="n">
+        <v>0.000527247019961752</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.016649749741123</v>
+      </c>
+      <c r="I279"/>
+      <c r="J279" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>37</v>
+      </c>
+      <c r="B280" t="s">
+        <v>18</v>
+      </c>
+      <c r="C280" t="s">
+        <v>27</v>
+      </c>
+      <c r="D280" t="s">
+        <v>53</v>
+      </c>
+      <c r="E280"/>
+      <c r="F280"/>
+      <c r="G280" t="n">
+        <v>0.000524877128533772</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.0166054349794582</v>
+      </c>
+      <c r="I280"/>
+      <c r="J280" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>37</v>
+      </c>
+      <c r="B281" t="s">
+        <v>18</v>
+      </c>
+      <c r="C281" t="s">
+        <v>27</v>
+      </c>
+      <c r="D281" t="s">
+        <v>54</v>
+      </c>
+      <c r="E281"/>
+      <c r="F281"/>
+      <c r="G281" t="n">
+        <v>0.000527821145493357</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.0166312672261733</v>
+      </c>
+      <c r="I281"/>
+      <c r="J281" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>38</v>
+      </c>
+      <c r="B282" t="s">
+        <v>13</v>
+      </c>
+      <c r="C282" t="s">
+        <v>14</v>
+      </c>
+      <c r="D282" t="s">
+        <v>51</v>
+      </c>
+      <c r="E282"/>
+      <c r="F282"/>
+      <c r="G282" t="n">
+        <v>0.00070411440216239</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0.0196794423566483</v>
+      </c>
+      <c r="I282"/>
+      <c r="J282" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>38</v>
+      </c>
+      <c r="B283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C283" t="s">
+        <v>14</v>
+      </c>
+      <c r="D283" t="s">
+        <v>52</v>
+      </c>
+      <c r="E283"/>
+      <c r="F283"/>
+      <c r="G283" t="n">
+        <v>0.000707769054580787</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.0197841079457453</v>
+      </c>
+      <c r="I283"/>
+      <c r="J283" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>38</v>
+      </c>
+      <c r="B284" t="s">
+        <v>13</v>
+      </c>
+      <c r="C284" t="s">
+        <v>14</v>
+      </c>
+      <c r="D284" t="s">
+        <v>53</v>
+      </c>
+      <c r="E284"/>
+      <c r="F284"/>
+      <c r="G284" t="n">
+        <v>0.000705675444861752</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.0197220483991037</v>
+      </c>
+      <c r="I284"/>
+      <c r="J284" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>38</v>
+      </c>
+      <c r="B285" t="s">
+        <v>13</v>
+      </c>
+      <c r="C285" t="s">
+        <v>14</v>
+      </c>
+      <c r="D285" t="s">
+        <v>54</v>
+      </c>
+      <c r="E285"/>
+      <c r="F285"/>
+      <c r="G285" t="n">
+        <v>0.000695121189078302</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0.0194886958785798</v>
+      </c>
+      <c r="I285"/>
+      <c r="J285" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>38</v>
+      </c>
+      <c r="B286" t="s">
+        <v>13</v>
+      </c>
+      <c r="C286" t="s">
+        <v>16</v>
+      </c>
+      <c r="D286" t="s">
+        <v>51</v>
+      </c>
+      <c r="E286"/>
+      <c r="F286"/>
+      <c r="G286" t="n">
+        <v>0.00117788518234075</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.0232288802362696</v>
+      </c>
+      <c r="I286"/>
+      <c r="J286" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>38</v>
+      </c>
+      <c r="B287" t="s">
+        <v>13</v>
+      </c>
+      <c r="C287" t="s">
+        <v>16</v>
+      </c>
+      <c r="D287" t="s">
+        <v>52</v>
+      </c>
+      <c r="E287"/>
+      <c r="F287"/>
+      <c r="G287" t="n">
+        <v>0.00117303493704195</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.0231616501701721</v>
+      </c>
+      <c r="I287"/>
+      <c r="J287" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>38</v>
+      </c>
+      <c r="B288" t="s">
+        <v>13</v>
+      </c>
+      <c r="C288" t="s">
+        <v>16</v>
+      </c>
+      <c r="D288" t="s">
+        <v>53</v>
+      </c>
+      <c r="E288"/>
+      <c r="F288"/>
+      <c r="G288" t="n">
+        <v>0.00117005142071227</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0.0232863371780439</v>
+      </c>
+      <c r="I288"/>
+      <c r="J288" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>38</v>
+      </c>
+      <c r="B289" t="s">
+        <v>13</v>
+      </c>
+      <c r="C289" t="s">
+        <v>16</v>
+      </c>
+      <c r="D289" t="s">
+        <v>54</v>
+      </c>
+      <c r="E289"/>
+      <c r="F289"/>
+      <c r="G289" t="n">
+        <v>0.00119066653109012</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.0233782537376481</v>
+      </c>
+      <c r="I289"/>
+      <c r="J289" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>38</v>
+      </c>
+      <c r="B290" t="s">
+        <v>18</v>
+      </c>
+      <c r="C290" t="s">
+        <v>19</v>
+      </c>
+      <c r="D290" t="s">
+        <v>51</v>
+      </c>
+      <c r="E290"/>
+      <c r="F290"/>
+      <c r="G290" t="n">
+        <v>0.000267010375005786</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0.00940153435834409</v>
+      </c>
+      <c r="I290"/>
+      <c r="J290" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>38</v>
+      </c>
+      <c r="B291" t="s">
+        <v>18</v>
+      </c>
+      <c r="C291" t="s">
+        <v>19</v>
+      </c>
+      <c r="D291" t="s">
+        <v>52</v>
+      </c>
+      <c r="E291"/>
+      <c r="F291"/>
+      <c r="G291" t="n">
+        <v>0.0002661307046103</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0.00937078107353905</v>
+      </c>
+      <c r="I291"/>
+      <c r="J291" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>38</v>
+      </c>
+      <c r="B292" t="s">
+        <v>18</v>
+      </c>
+      <c r="C292" t="s">
+        <v>19</v>
+      </c>
+      <c r="D292" t="s">
+        <v>53</v>
+      </c>
+      <c r="E292"/>
+      <c r="F292"/>
+      <c r="G292" t="n">
+        <v>0.000267080134588328</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0.00938632489551913</v>
+      </c>
+      <c r="I292"/>
+      <c r="J292" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>38</v>
+      </c>
+      <c r="B293" t="s">
+        <v>18</v>
+      </c>
+      <c r="C293" t="s">
+        <v>19</v>
+      </c>
+      <c r="D293" t="s">
+        <v>54</v>
+      </c>
+      <c r="E293"/>
+      <c r="F293"/>
+      <c r="G293" t="n">
+        <v>0.000268782673121551</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.00941393563579777</v>
+      </c>
+      <c r="I293"/>
+      <c r="J293" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>38</v>
+      </c>
+      <c r="B294" t="s">
+        <v>18</v>
+      </c>
+      <c r="C294" t="s">
+        <v>21</v>
+      </c>
+      <c r="D294" t="s">
+        <v>51</v>
+      </c>
+      <c r="E294"/>
+      <c r="F294"/>
+      <c r="G294" t="n">
+        <v>0.000381651812090491</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.00950991135700453</v>
+      </c>
+      <c r="I294"/>
+      <c r="J294" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>38</v>
+      </c>
+      <c r="B295" t="s">
+        <v>18</v>
+      </c>
+      <c r="C295" t="s">
+        <v>21</v>
+      </c>
+      <c r="D295" t="s">
+        <v>52</v>
+      </c>
+      <c r="E295"/>
+      <c r="F295"/>
+      <c r="G295" t="n">
+        <v>0.000384637421848706</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0.00958194764415019</v>
+      </c>
+      <c r="I295"/>
+      <c r="J295" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>38</v>
+      </c>
+      <c r="B296" t="s">
+        <v>18</v>
+      </c>
+      <c r="C296" t="s">
+        <v>21</v>
+      </c>
+      <c r="D296" t="s">
+        <v>53</v>
+      </c>
+      <c r="E296"/>
+      <c r="F296"/>
+      <c r="G296" t="n">
+        <v>0.000382977512560856</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.00952928113782215</v>
+      </c>
+      <c r="I296"/>
+      <c r="J296" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>38</v>
+      </c>
+      <c r="B297" t="s">
+        <v>18</v>
+      </c>
+      <c r="C297" t="s">
+        <v>21</v>
+      </c>
+      <c r="D297" t="s">
+        <v>54</v>
+      </c>
+      <c r="E297"/>
+      <c r="F297"/>
+      <c r="G297" t="n">
+        <v>0.000384151550277469</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.00958593436865354</v>
+      </c>
+      <c r="I297"/>
+      <c r="J297" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>38</v>
+      </c>
+      <c r="B298" t="s">
+        <v>18</v>
+      </c>
+      <c r="C298" t="s">
+        <v>23</v>
+      </c>
+      <c r="D298" t="s">
+        <v>51</v>
+      </c>
+      <c r="E298"/>
+      <c r="F298"/>
+      <c r="G298" t="n">
+        <v>0.000203079140737354</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0.00918072600219778</v>
+      </c>
+      <c r="I298"/>
+      <c r="J298" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>38</v>
+      </c>
+      <c r="B299" t="s">
+        <v>18</v>
+      </c>
+      <c r="C299" t="s">
+        <v>23</v>
+      </c>
+      <c r="D299" t="s">
+        <v>52</v>
+      </c>
+      <c r="E299"/>
+      <c r="F299"/>
+      <c r="G299" t="n">
+        <v>0.000203975252866073</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0.00920397260927467</v>
+      </c>
+      <c r="I299"/>
+      <c r="J299" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>38</v>
+      </c>
+      <c r="B300" t="s">
+        <v>18</v>
+      </c>
+      <c r="C300" t="s">
+        <v>23</v>
+      </c>
+      <c r="D300" t="s">
+        <v>53</v>
+      </c>
+      <c r="E300"/>
+      <c r="F300"/>
+      <c r="G300" t="n">
+        <v>0.000202054082550471</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0.00916177081136317</v>
+      </c>
+      <c r="I300"/>
+      <c r="J300" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>38</v>
+      </c>
+      <c r="B301" t="s">
+        <v>18</v>
+      </c>
+      <c r="C301" t="s">
+        <v>23</v>
+      </c>
+      <c r="D301" t="s">
+        <v>54</v>
+      </c>
+      <c r="E301"/>
+      <c r="F301"/>
+      <c r="G301" t="n">
+        <v>0.000203819966730454</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0.00919849175452202</v>
+      </c>
+      <c r="I301"/>
+      <c r="J301" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>38</v>
+      </c>
+      <c r="B302" t="s">
+        <v>18</v>
+      </c>
+      <c r="C302" t="s">
+        <v>25</v>
+      </c>
+      <c r="D302" t="s">
+        <v>51</v>
+      </c>
+      <c r="E302"/>
+      <c r="F302"/>
+      <c r="G302" t="n">
+        <v>0.00020229645644614</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0.00917672302291868</v>
+      </c>
+      <c r="I302"/>
+      <c r="J302" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>38</v>
+      </c>
+      <c r="B303" t="s">
+        <v>18</v>
+      </c>
+      <c r="C303" t="s">
+        <v>25</v>
+      </c>
+      <c r="D303" t="s">
+        <v>52</v>
+      </c>
+      <c r="E303"/>
+      <c r="F303"/>
+      <c r="G303" t="n">
+        <v>0.00020373007730466</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0.00921828681196115</v>
+      </c>
+      <c r="I303"/>
+      <c r="J303" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>38</v>
+      </c>
+      <c r="B304" t="s">
+        <v>18</v>
+      </c>
+      <c r="C304" t="s">
+        <v>25</v>
+      </c>
+      <c r="D304" t="s">
+        <v>53</v>
+      </c>
+      <c r="E304"/>
+      <c r="F304"/>
+      <c r="G304" t="n">
+        <v>0.000202890710948747</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0.00917617232216271</v>
+      </c>
+      <c r="I304"/>
+      <c r="J304" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>38</v>
+      </c>
+      <c r="B305" t="s">
+        <v>18</v>
+      </c>
+      <c r="C305" t="s">
+        <v>25</v>
+      </c>
+      <c r="D305" t="s">
+        <v>54</v>
+      </c>
+      <c r="E305"/>
+      <c r="F305"/>
+      <c r="G305" t="n">
+        <v>0.000202763208249227</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0.00919822767957409</v>
+      </c>
+      <c r="I305"/>
+      <c r="J305" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>38</v>
+      </c>
+      <c r="B306" t="s">
+        <v>18</v>
+      </c>
+      <c r="C306" t="s">
+        <v>27</v>
+      </c>
+      <c r="D306" t="s">
+        <v>51</v>
+      </c>
+      <c r="E306"/>
+      <c r="F306"/>
+      <c r="G306" t="n">
+        <v>0.000315033808339458</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.0129531707253145</v>
+      </c>
+      <c r="I306"/>
+      <c r="J306" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>38</v>
+      </c>
+      <c r="B307" t="s">
+        <v>18</v>
+      </c>
+      <c r="C307" t="s">
+        <v>27</v>
+      </c>
+      <c r="D307" t="s">
+        <v>52</v>
+      </c>
+      <c r="E307"/>
+      <c r="F307"/>
+      <c r="G307" t="n">
+        <v>0.000314830321269798</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0.0129224656595199</v>
+      </c>
+      <c r="I307"/>
+      <c r="J307" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>38</v>
+      </c>
+      <c r="B308" t="s">
+        <v>18</v>
+      </c>
+      <c r="C308" t="s">
+        <v>27</v>
+      </c>
+      <c r="D308" t="s">
+        <v>53</v>
+      </c>
+      <c r="E308"/>
+      <c r="F308"/>
+      <c r="G308" t="n">
+        <v>0.000314769139770439</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0.0129234500292938</v>
+      </c>
+      <c r="I308"/>
+      <c r="J308" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>38</v>
+      </c>
+      <c r="B309" t="s">
+        <v>18</v>
+      </c>
+      <c r="C309" t="s">
+        <v>27</v>
+      </c>
+      <c r="D309" t="s">
+        <v>54</v>
+      </c>
+      <c r="E309"/>
+      <c r="F309"/>
+      <c r="G309" t="n">
+        <v>0.000316640054414869</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0.0129641190031284</v>
+      </c>
+      <c r="I309"/>
+      <c r="J309" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>39</v>
+      </c>
+      <c r="B310" t="s">
+        <v>13</v>
+      </c>
+      <c r="C310" t="s">
+        <v>14</v>
+      </c>
+      <c r="D310" t="s">
+        <v>51</v>
+      </c>
+      <c r="E310"/>
+      <c r="F310"/>
+      <c r="G310" t="n">
+        <v>0.00264908621603129</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0.0395380211134714</v>
+      </c>
+      <c r="I310"/>
+      <c r="J310" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>39</v>
+      </c>
+      <c r="B311" t="s">
+        <v>13</v>
+      </c>
+      <c r="C311" t="s">
+        <v>14</v>
+      </c>
+      <c r="D311" t="s">
+        <v>52</v>
+      </c>
+      <c r="E311"/>
+      <c r="F311"/>
+      <c r="G311" t="n">
+        <v>0.00265368151762362</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0.0396173482857403</v>
+      </c>
+      <c r="I311"/>
+      <c r="J311" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>39</v>
+      </c>
+      <c r="B312" t="s">
+        <v>13</v>
+      </c>
+      <c r="C312" t="s">
+        <v>14</v>
+      </c>
+      <c r="D312" t="s">
+        <v>53</v>
+      </c>
+      <c r="E312"/>
+      <c r="F312"/>
+      <c r="G312" t="n">
+        <v>0.00263829428268923</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.0394877944442211</v>
+      </c>
+      <c r="I312"/>
+      <c r="J312" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>39</v>
+      </c>
+      <c r="B313" t="s">
+        <v>13</v>
+      </c>
+      <c r="C313" t="s">
+        <v>14</v>
+      </c>
+      <c r="D313" t="s">
+        <v>54</v>
+      </c>
+      <c r="E313"/>
+      <c r="F313"/>
+      <c r="G313" t="n">
+        <v>0.00266680163467614</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0.0398686205905827</v>
+      </c>
+      <c r="I313"/>
+      <c r="J313" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>39</v>
+      </c>
+      <c r="B314" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" t="s">
+        <v>16</v>
+      </c>
+      <c r="D314" t="s">
+        <v>51</v>
+      </c>
+      <c r="E314"/>
+      <c r="F314"/>
+      <c r="G314" t="n">
+        <v>0.00109361025451632</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0.0251284767636314</v>
+      </c>
+      <c r="I314"/>
+      <c r="J314" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>39</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>16</v>
+      </c>
+      <c r="D315" t="s">
+        <v>52</v>
+      </c>
+      <c r="E315"/>
+      <c r="F315"/>
+      <c r="G315" t="n">
+        <v>0.0010987841194942</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.0250568515967064</v>
+      </c>
+      <c r="I315"/>
+      <c r="J315" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>39</v>
+      </c>
+      <c r="B316" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" t="s">
+        <v>16</v>
+      </c>
+      <c r="D316" t="s">
+        <v>53</v>
+      </c>
+      <c r="E316"/>
+      <c r="F316"/>
+      <c r="G316" t="n">
+        <v>0.00109943898237892</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0.0253935864123892</v>
+      </c>
+      <c r="I316"/>
+      <c r="J316" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>39</v>
+      </c>
+      <c r="B317" t="s">
+        <v>13</v>
+      </c>
+      <c r="C317" t="s">
+        <v>16</v>
+      </c>
+      <c r="D317" t="s">
+        <v>54</v>
+      </c>
+      <c r="E317"/>
+      <c r="F317"/>
+      <c r="G317" t="n">
+        <v>0.00109919167580229</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.0252153462937176</v>
+      </c>
+      <c r="I317"/>
+      <c r="J317" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>39</v>
+      </c>
+      <c r="B318" t="s">
+        <v>18</v>
+      </c>
+      <c r="C318" t="s">
+        <v>19</v>
+      </c>
+      <c r="D318" t="s">
+        <v>51</v>
+      </c>
+      <c r="E318"/>
+      <c r="F318"/>
+      <c r="G318" t="n">
+        <v>0.000582332833114269</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.0163983845440508</v>
+      </c>
+      <c r="I318"/>
+      <c r="J318" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>39</v>
+      </c>
+      <c r="B319" t="s">
+        <v>18</v>
+      </c>
+      <c r="C319" t="s">
+        <v>19</v>
+      </c>
+      <c r="D319" t="s">
+        <v>52</v>
+      </c>
+      <c r="E319"/>
+      <c r="F319"/>
+      <c r="G319" t="n">
+        <v>0.000581350924409201</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0.0164257639698158</v>
+      </c>
+      <c r="I319"/>
+      <c r="J319" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>39</v>
+      </c>
+      <c r="B320" t="s">
+        <v>18</v>
+      </c>
+      <c r="C320" t="s">
+        <v>19</v>
+      </c>
+      <c r="D320" t="s">
+        <v>53</v>
+      </c>
+      <c r="E320"/>
+      <c r="F320"/>
+      <c r="G320" t="n">
+        <v>0.000582494628436274</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0.0164309395323363</v>
+      </c>
+      <c r="I320"/>
+      <c r="J320" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>39</v>
+      </c>
+      <c r="B321" t="s">
+        <v>18</v>
+      </c>
+      <c r="C321" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321" t="s">
+        <v>54</v>
+      </c>
+      <c r="E321"/>
+      <c r="F321"/>
+      <c r="G321" t="n">
+        <v>0.000582846251377214</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0.0164117970227086</v>
+      </c>
+      <c r="I321"/>
+      <c r="J321" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>39</v>
+      </c>
+      <c r="B322" t="s">
+        <v>18</v>
+      </c>
+      <c r="C322" t="s">
+        <v>21</v>
+      </c>
+      <c r="D322" t="s">
+        <v>51</v>
+      </c>
+      <c r="E322"/>
+      <c r="F322"/>
+      <c r="G322" t="n">
+        <v>0.000704045661935989</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0.0165742922810511</v>
+      </c>
+      <c r="I322"/>
+      <c r="J322" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>39</v>
+      </c>
+      <c r="B323" t="s">
+        <v>18</v>
+      </c>
+      <c r="C323" t="s">
+        <v>21</v>
+      </c>
+      <c r="D323" t="s">
+        <v>52</v>
+      </c>
+      <c r="E323"/>
+      <c r="F323"/>
+      <c r="G323" t="n">
+        <v>0.000698666394060779</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0.0165534995761449</v>
+      </c>
+      <c r="I323"/>
+      <c r="J323" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>39</v>
+      </c>
+      <c r="B324" t="s">
+        <v>18</v>
+      </c>
+      <c r="C324" t="s">
+        <v>21</v>
+      </c>
+      <c r="D324" t="s">
+        <v>53</v>
+      </c>
+      <c r="E324"/>
+      <c r="F324"/>
+      <c r="G324" t="n">
+        <v>0.000703156717183897</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0.0165429703438941</v>
+      </c>
+      <c r="I324"/>
+      <c r="J324" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>39</v>
+      </c>
+      <c r="B325" t="s">
+        <v>18</v>
+      </c>
+      <c r="C325" t="s">
+        <v>21</v>
+      </c>
+      <c r="D325" t="s">
+        <v>54</v>
+      </c>
+      <c r="E325"/>
+      <c r="F325"/>
+      <c r="G325" t="n">
+        <v>0.000703096841472074</v>
+      </c>
+      <c r="H325" t="n">
+        <v>0.0165296594022499</v>
+      </c>
+      <c r="I325"/>
+      <c r="J325" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>39</v>
+      </c>
+      <c r="B326" t="s">
+        <v>18</v>
+      </c>
+      <c r="C326" t="s">
+        <v>23</v>
+      </c>
+      <c r="D326" t="s">
+        <v>51</v>
+      </c>
+      <c r="E326"/>
+      <c r="F326"/>
+      <c r="G326" t="n">
+        <v>0.000516610233084458</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0.016207231896124</v>
+      </c>
+      <c r="I326"/>
+      <c r="J326" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>39</v>
+      </c>
+      <c r="B327" t="s">
+        <v>18</v>
+      </c>
+      <c r="C327" t="s">
+        <v>23</v>
+      </c>
+      <c r="D327" t="s">
+        <v>52</v>
+      </c>
+      <c r="E327"/>
+      <c r="F327"/>
+      <c r="G327" t="n">
+        <v>0.000516594746054939</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0.0162158535756479</v>
+      </c>
+      <c r="I327"/>
+      <c r="J327" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>39</v>
+      </c>
+      <c r="B328" t="s">
+        <v>18</v>
+      </c>
+      <c r="C328" t="s">
+        <v>23</v>
+      </c>
+      <c r="D328" t="s">
+        <v>53</v>
+      </c>
+      <c r="E328"/>
+      <c r="F328"/>
+      <c r="G328" t="n">
+        <v>0.000513262261743514</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0.0161382927968462</v>
+      </c>
+      <c r="I328"/>
+      <c r="J328" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>39</v>
+      </c>
+      <c r="B329" t="s">
+        <v>18</v>
+      </c>
+      <c r="C329" t="s">
+        <v>23</v>
+      </c>
+      <c r="D329" t="s">
+        <v>54</v>
+      </c>
+      <c r="E329"/>
+      <c r="F329"/>
+      <c r="G329" t="n">
+        <v>0.000515760320382338</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0.0161686910394189</v>
+      </c>
+      <c r="I329"/>
+      <c r="J329" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>39</v>
+      </c>
+      <c r="B330" t="s">
+        <v>18</v>
+      </c>
+      <c r="C330" t="s">
+        <v>25</v>
+      </c>
+      <c r="D330" t="s">
+        <v>51</v>
+      </c>
+      <c r="E330"/>
+      <c r="F330"/>
+      <c r="G330" t="n">
+        <v>0.000516258147487233</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0.016184083399079</v>
+      </c>
+      <c r="I330"/>
+      <c r="J330" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>39</v>
+      </c>
+      <c r="B331" t="s">
+        <v>18</v>
+      </c>
+      <c r="C331" t="s">
+        <v>25</v>
+      </c>
+      <c r="D331" t="s">
+        <v>52</v>
+      </c>
+      <c r="E331"/>
+      <c r="F331"/>
+      <c r="G331" t="n">
+        <v>0.000514770195512859</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0.0161854871931729</v>
+      </c>
+      <c r="I331"/>
+      <c r="J331" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>39</v>
+      </c>
+      <c r="B332" t="s">
+        <v>18</v>
+      </c>
+      <c r="C332" t="s">
+        <v>25</v>
+      </c>
+      <c r="D332" t="s">
+        <v>53</v>
+      </c>
+      <c r="E332"/>
+      <c r="F332"/>
+      <c r="G332" t="n">
+        <v>0.000517292357147806</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0.0162066221381579</v>
+      </c>
+      <c r="I332"/>
+      <c r="J332" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>39</v>
+      </c>
+      <c r="B333" t="s">
+        <v>18</v>
+      </c>
+      <c r="C333" t="s">
+        <v>25</v>
+      </c>
+      <c r="D333" t="s">
+        <v>54</v>
+      </c>
+      <c r="E333"/>
+      <c r="F333"/>
+      <c r="G333" t="n">
+        <v>0.000513457611305057</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0.0161762135502516</v>
+      </c>
+      <c r="I333"/>
+      <c r="J333" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>39</v>
+      </c>
+      <c r="B334" t="s">
+        <v>18</v>
+      </c>
+      <c r="C334" t="s">
+        <v>27</v>
+      </c>
+      <c r="D334" t="s">
+        <v>51</v>
+      </c>
+      <c r="E334"/>
+      <c r="F334"/>
+      <c r="G334" t="n">
+        <v>0.000473090273945446</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0.0158824979442953</v>
+      </c>
+      <c r="I334"/>
+      <c r="J334" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>39</v>
+      </c>
+      <c r="B335" t="s">
+        <v>18</v>
+      </c>
+      <c r="C335" t="s">
+        <v>27</v>
+      </c>
+      <c r="D335" t="s">
+        <v>52</v>
+      </c>
+      <c r="E335"/>
+      <c r="F335"/>
+      <c r="G335" t="n">
+        <v>0.000475307077472086</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0.0159183925724936</v>
+      </c>
+      <c r="I335"/>
+      <c r="J335" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>39</v>
+      </c>
+      <c r="B336" t="s">
+        <v>18</v>
+      </c>
+      <c r="C336" t="s">
+        <v>27</v>
+      </c>
+      <c r="D336" t="s">
+        <v>53</v>
+      </c>
+      <c r="E336"/>
+      <c r="F336"/>
+      <c r="G336" t="n">
+        <v>0.000470733480231767</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0.0158365255178594</v>
+      </c>
+      <c r="I336"/>
+      <c r="J336" t="n">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>39</v>
+      </c>
+      <c r="B337" t="s">
+        <v>18</v>
+      </c>
+      <c r="C337" t="s">
+        <v>27</v>
+      </c>
+      <c r="D337" t="s">
+        <v>54</v>
+      </c>
+      <c r="E337"/>
+      <c r="F337"/>
+      <c r="G337" t="n">
+        <v>0.00048581664370594</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0.0161947088315407</v>
+      </c>
+      <c r="I337"/>
+      <c r="J337" t="n">
         <v>904</v>
       </c>
     </row>
@@ -6569,19 +12383,19 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
@@ -6589,16 +12403,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D2" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00119809867253835</v>
+        <v>0.00102575218626251</v>
       </c>
       <c r="F2" t="e">
         <v>#NUM!</v>
@@ -6609,16 +12423,16 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D3" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001199111891896</v>
+        <v>0.00102114188842137</v>
       </c>
       <c r="F3" t="e">
         <v>#NUM!</v>
@@ -6629,16 +12443,16 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00119954088899831</v>
+        <v>0.00102337050718631</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -6649,16 +12463,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0011959589624099</v>
+        <v>0.00102608526714088</v>
       </c>
       <c r="F5" t="e">
         <v>#NUM!</v>
@@ -6669,16 +12483,16 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D6" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00146957614366458</v>
+        <v>0.00111322095273585</v>
       </c>
       <c r="F6" t="e">
         <v>#NUM!</v>
@@ -6689,16 +12503,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00147559748199105</v>
+        <v>0.00111758615835052</v>
       </c>
       <c r="F7" t="e">
         <v>#NUM!</v>
@@ -6709,16 +12523,16 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00146812549072999</v>
+        <v>0.00111181465518843</v>
       </c>
       <c r="F8" t="e">
         <v>#NUM!</v>
@@ -6729,16 +12543,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D9" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0014690332222688</v>
+        <v>0.00111984376508934</v>
       </c>
       <c r="F9" t="e">
         <v>#NUM!</v>
@@ -6749,16 +12563,16 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000402160896320226</v>
+        <v>0.000338693094962634</v>
       </c>
       <c r="F10" t="e">
         <v>#NUM!</v>
@@ -6769,16 +12583,16 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D11" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000404571293534656</v>
+        <v>0.000340154260899959</v>
       </c>
       <c r="F11" t="e">
         <v>#NUM!</v>
@@ -6789,16 +12603,16 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D12" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000408737426099211</v>
+        <v>0.000340581884273816</v>
       </c>
       <c r="F12" t="e">
         <v>#NUM!</v>
@@ -6809,16 +12623,16 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000401469279908919</v>
+        <v>0.000337850401369121</v>
       </c>
       <c r="F13" t="e">
         <v>#NUM!</v>
@@ -6829,16 +12643,16 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D14" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000441462183266898</v>
+        <v>0.000338215498148319</v>
       </c>
       <c r="F14" t="e">
         <v>#NUM!</v>
@@ -6849,16 +12663,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D15" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E15" t="n">
-        <v>202.290892146031</v>
+        <v>99.6645640388995</v>
       </c>
       <c r="F15" t="e">
         <v>#NUM!</v>
@@ -6869,16 +12683,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D16" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000441530167018193</v>
+        <v>0.000339177343615847</v>
       </c>
       <c r="F16" t="e">
         <v>#NUM!</v>
@@ -6889,16 +12703,16 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D17" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000440679610808023</v>
+        <v>0.000338535827246057</v>
       </c>
       <c r="F17" t="e">
         <v>#NUM!</v>
@@ -6909,16 +12723,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D18" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0005625495594148</v>
+        <v>0.000459554557516552</v>
       </c>
       <c r="F18" t="e">
         <v>#NUM!</v>
@@ -6929,16 +12743,16 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E19" t="n">
-        <v>217.599485462393</v>
+        <v>92.2498596616622</v>
       </c>
       <c r="F19" t="e">
         <v>#NUM!</v>
@@ -6949,16 +12763,16 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D20" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000562132201910548</v>
+        <v>0.000460117238493245</v>
       </c>
       <c r="F20" t="e">
         <v>#NUM!</v>
@@ -6969,16 +12783,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D21" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E21" t="n">
-        <v>0.000563038312353689</v>
+        <v>0.00045801792648301</v>
       </c>
       <c r="F21" t="e">
         <v>#NUM!</v>
@@ -6989,16 +12803,16 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D22" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000371729895957673</v>
+        <v>0.000269034555515956</v>
       </c>
       <c r="F22" t="e">
         <v>#NUM!</v>
@@ -7009,16 +12823,16 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D23" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E23" t="n">
-        <v>218.176586542214</v>
+        <v>99.1318714434489</v>
       </c>
       <c r="F23" t="e">
         <v>#NUM!</v>
@@ -7029,16 +12843,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D24" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00037277928184426</v>
+        <v>0.000269936014251864</v>
       </c>
       <c r="F24" t="e">
         <v>#NUM!</v>
@@ -7049,16 +12863,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000371235313507152</v>
+        <v>0.00026900054528273</v>
       </c>
       <c r="F25" t="e">
         <v>#NUM!</v>
@@ -7069,16 +12883,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D26" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000372377998551685</v>
+        <v>0.000270485981846681</v>
       </c>
       <c r="F26" t="e">
         <v>#NUM!</v>
@@ -7089,16 +12903,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D27" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E27" t="n">
-        <v>164.798644452561</v>
+        <v>89.6971619384713</v>
       </c>
       <c r="F27" t="e">
         <v>#NUM!</v>
@@ -7109,16 +12923,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D28" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E28" t="n">
-        <v>0.000372188689967515</v>
+        <v>0.000269639427812933</v>
       </c>
       <c r="F28" t="e">
         <v>#NUM!</v>
@@ -7129,16 +12943,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D29" t="e">
         <v>#NUM!</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000372127472085542</v>
+        <v>0.000269866090308313</v>
       </c>
       <c r="F29" t="e">
         <v>#NUM!</v>
